--- a/Översikt BODEN.xlsx
+++ b/Översikt BODEN.xlsx
@@ -601,7 +601,7 @@
         <v>45152</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45506</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>45152</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45068</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>45075</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45152</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>44853</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>46168</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>46247</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>44964</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45105</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>45212</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>45790</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>46149</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>44889</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45771</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>45684</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>44859</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44853</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>45295</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>46210</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>45049</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>44869</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>46195</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>45418</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>45463</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>44489</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>44795</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>45964</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>45912</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>45912</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>45893</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>44904</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>45512</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46209</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>45835</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45428</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>45832</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>45980</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>46148</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         <v>45307</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>45645</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>45988</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>46196</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>46261</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>45818</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>45980</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v>45791</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>45933</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>45952</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>45981</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>45077</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>44833</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>45155</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>45698</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>46181</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>46073</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>46184</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         <v>44755</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>46190</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>46205</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>46258</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>46217</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>46240</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>45818</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>44487</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>44648</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>44804</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>44796</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>44735</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>45341</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>45517</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>45701</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>44573</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>45803</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>45594</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>45645</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         <v>45910</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>45910</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>45834</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>45922</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>45943</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>46149</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>45714</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>45526</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>46164</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>45137</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>45638</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>46066</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>46066</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>46184</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>46184</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>44830</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11430,7 +11430,7 @@
         <v>46245</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>45999</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>46205</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>46247</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>46205</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>46205</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>44573</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>45072</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
         <v>45301</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>46258</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>46261</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>46217</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>46261</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>44678</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>46225</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>46270</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>45820</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>45875</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>45376</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>44648</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>44840</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>45313</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>45763</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44529</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>44463</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>44529</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>45448</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>44648</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>45211</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>45901</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45905</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>44735</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>46147</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>45538</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         <v>45944</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>45947</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>45950</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>45949</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>45952</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>45513</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>45958</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>45960</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>45965</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>45966</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16277,7 +16277,7 @@
         <v>44925</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45975</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>45994</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>44642</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>45999</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>46003</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>46168</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>45559</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>46048</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>46178</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>46178</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>45884</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>46178</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>46183</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>46184</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>46100</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>44692</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>46134</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>46205</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>46251</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18452,7 +18452,7 @@
         <v>46255</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>46261</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18671,7 +18671,7 @@
         <v>46261</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>46261</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>46261</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>46272</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>46272</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         <v>46267</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
         <v>46236</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19443,7 +19443,7 @@
         <v>45406</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>46037</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>46240</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19772,7 +19772,7 @@
         <v>46241</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>46282</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>44944</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20106,7 +20106,7 @@
         <v>45418</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>45028</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>45643</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>45799</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>45901</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>45952</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20765,7 +20765,7 @@
         <v>44509</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>44677</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>44577</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>44659</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>44671</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>44489</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>44852</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>44463</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>44815</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>44648</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>44462</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>44617</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>44648</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>44464</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44865</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>44609</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>44609</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>44671</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>44461</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>44887</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>44721</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22338,7 +22338,7 @@
         <v>44543</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44530</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22484,7 +22484,7 @@
         <v>44648</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         <v>44473</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>44734</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>44566</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44566</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>44600</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22937,7 +22937,7 @@
         <v>44749</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -23010,7 +23010,7 @@
         <v>44722</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>44480</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>44530</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>44565</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>44573</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>44566</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>44617</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>44820</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>44625</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>44596</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>44831</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>44799</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23911,7 +23911,7 @@
         <v>44799</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>44743</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24062,7 +24062,7 @@
         <v>44480</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>44529</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24208,7 +24208,7 @@
         <v>44565</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24281,7 +24281,7 @@
         <v>44635</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24359,7 +24359,7 @@
         <v>44797</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>44796</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>44796</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44484</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>44489</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>44795</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>44812</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>44671</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>45310</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>44463</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25109,7 +25109,7 @@
         <v>44552</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25182,7 +25182,7 @@
         <v>45022</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>45411</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25328,7 +25328,7 @@
         <v>44833</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>44880</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>44609</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>44881</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>45238</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25693,7 +25693,7 @@
         <v>44783</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>45125</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>45210</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>45635</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>45763</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>45419</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>44489</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26214,7 +26214,7 @@
         <v>45600</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>45600</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>45254</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>45161</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>45537</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>44881</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>45762</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>45237</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>45345</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>45512</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>44558</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -27027,7 +27027,7 @@
         <v>45539</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>44529</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>44970</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45766</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>45285</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27397,7 +27397,7 @@
         <v>45604</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27470,7 +27470,7 @@
         <v>45397</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>45397</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>45764</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27689,7 +27689,7 @@
         <v>44983</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27762,7 +27762,7 @@
         <v>44474</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>45758</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>45260</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>45527</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>44484</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>45264</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>45264</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28288,7 +28288,7 @@
         <v>44935</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>45516</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>45516</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28517,7 +28517,7 @@
         <v>45589</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>45543</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>45560</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28746,7 +28746,7 @@
         <v>45709</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>45246</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>45194</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28975,7 +28975,7 @@
         <v>45244</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>45748</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>45110</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45103</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29277,7 +29277,7 @@
         <v>45070</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29350,7 +29350,7 @@
         <v>45672</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>45254</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>45764</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>45463</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>45667</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>44628</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>45246</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>45161</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>45161</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>45718</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>45358</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>45356</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30236,7 +30236,7 @@
         <v>45770</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30309,7 +30309,7 @@
         <v>44648</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>44529</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>45102</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30533,7 +30533,7 @@
         <v>45212</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30606,7 +30606,7 @@
         <v>45316</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30679,7 +30679,7 @@
         <v>45643</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30757,7 +30757,7 @@
         <v>45476</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30830,7 +30830,7 @@
         <v>45884</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>45764</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>44474</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -31054,7 +31054,7 @@
         <v>44566</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31127,7 +31127,7 @@
         <v>45999</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>45551</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31278,7 +31278,7 @@
         <v>45707</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31351,7 +31351,7 @@
         <v>46003</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31429,7 +31429,7 @@
         <v>44477</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31502,7 +31502,7 @@
         <v>45884</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>45132</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31653,7 +31653,7 @@
         <v>45649</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>45649</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31799,7 +31799,7 @@
         <v>45408</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31872,7 +31872,7 @@
         <v>45944</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>45105</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>45764</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>45201</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>45099</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32237,7 +32237,7 @@
         <v>45649</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32310,7 +32310,7 @@
         <v>45446</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32383,7 +32383,7 @@
         <v>44994</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>45860</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>44486</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>45728</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>45891</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32758,7 +32758,7 @@
         <v>45649</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32831,7 +32831,7 @@
         <v>45894</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32909,7 +32909,7 @@
         <v>45583</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32987,7 +32987,7 @@
         <v>45764</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>45341</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33138,7 +33138,7 @@
         <v>45561</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33211,7 +33211,7 @@
         <v>45897</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33284,7 +33284,7 @@
         <v>45897</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>45935</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33430,7 +33430,7 @@
         <v>45257</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>44522</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33576,7 +33576,7 @@
         <v>45596</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33649,7 +33649,7 @@
         <v>45901</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33727,7 +33727,7 @@
         <v>45587</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>45902</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>45839</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33951,7 +33951,7 @@
         <v>45685</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -34024,7 +34024,7 @@
         <v>46029</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34097,7 +34097,7 @@
         <v>45907</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>45911</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>45586</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>45910</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
         <v>45910</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34482,7 +34482,7 @@
         <v>44994</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>45912</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>45915</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34711,7 +34711,7 @@
         <v>45915</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>45912</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34857,7 +34857,7 @@
         <v>45912</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34930,7 +34930,7 @@
         <v>45915</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -35008,7 +35008,7 @@
         <v>46084</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>45512</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35154,7 +35154,7 @@
         <v>45919</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35232,7 +35232,7 @@
         <v>45919</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35310,7 +35310,7 @@
         <v>44889</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>46076</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>45832</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35529,7 +35529,7 @@
         <v>45922</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35602,7 +35602,7 @@
         <v>45406</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -35675,7 +35675,7 @@
         <v>45922</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35748,7 +35748,7 @@
         <v>45922</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35821,7 +35821,7 @@
         <v>45771</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>45925</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35967,7 +35967,7 @@
         <v>45925</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -36040,7 +36040,7 @@
         <v>45818</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>44881</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>45645</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36269,7 +36269,7 @@
         <v>45924</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36342,7 +36342,7 @@
         <v>45924</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36415,7 +36415,7 @@
         <v>45926</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>45926</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36566,7 +36566,7 @@
         <v>45926</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36639,7 +36639,7 @@
         <v>45587</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36712,7 +36712,7 @@
         <v>45248</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45931</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36863,7 +36863,7 @@
         <v>45930</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45930</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -37019,7 +37019,7 @@
         <v>45691</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -37097,7 +37097,7 @@
         <v>44648</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37175,7 +37175,7 @@
         <v>45933</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37253,7 +37253,7 @@
         <v>45906</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>44565</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37399,7 +37399,7 @@
         <v>45933</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>45933</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37555,7 +37555,7 @@
         <v>45649</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37628,7 +37628,7 @@
         <v>45936</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -37701,7 +37701,7 @@
         <v>46147</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37774,7 +37774,7 @@
         <v>45893</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37852,7 +37852,7 @@
         <v>45938</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37930,7 +37930,7 @@
         <v>45937</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -38003,7 +38003,7 @@
         <v>45574</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -38081,7 +38081,7 @@
         <v>45841</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38154,7 +38154,7 @@
         <v>45301</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38232,7 +38232,7 @@
         <v>45938</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38305,7 +38305,7 @@
         <v>45761</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38378,7 +38378,7 @@
         <v>45938</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>45939</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38534,7 +38534,7 @@
         <v>45750</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38612,7 +38612,7 @@
         <v>45943</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38685,7 +38685,7 @@
         <v>46148</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>46149</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>45945</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         <v>45945</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>45944</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39065,7 +39065,7 @@
         <v>45944</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -39138,7 +39138,7 @@
         <v>45944</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39216,7 +39216,7 @@
         <v>45944</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45945</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39362,7 +39362,7 @@
         <v>45944</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39440,7 +39440,7 @@
         <v>45264</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39513,7 +39513,7 @@
         <v>46149</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39586,7 +39586,7 @@
         <v>46149</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39659,7 +39659,7 @@
         <v>45947</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -39737,7 +39737,7 @@
         <v>45950</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>46150</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>45692</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39956,7 +39956,7 @@
         <v>46150</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>44490</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -40107,7 +40107,7 @@
         <v>45953</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40185,7 +40185,7 @@
         <v>45953</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40258,7 +40258,7 @@
         <v>45953</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40336,7 +40336,7 @@
         <v>45957</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40414,7 +40414,7 @@
         <v>44903</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40487,7 +40487,7 @@
         <v>45770</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>45672</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40633,7 +40633,7 @@
         <v>45950</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -40706,7 +40706,7 @@
         <v>45955</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>45955</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40852,7 +40852,7 @@
         <v>46150</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40925,7 +40925,7 @@
         <v>45590</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -41003,7 +41003,7 @@
         <v>45591</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>45591</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>45960</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>45425</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45408</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41383,7 +41383,7 @@
         <v>45961</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>45965</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45965</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41602,7 +41602,7 @@
         <v>45965</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>44657</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41748,7 +41748,7 @@
         <v>46154</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41821,7 +41821,7 @@
         <v>45965</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>45646</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41967,7 +41967,7 @@
         <v>45964</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>45966</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>46155</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>45639</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42259,7 +42259,7 @@
         <v>44847</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>46154</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45210</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>45971</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42561,7 +42561,7 @@
         <v>45988</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42634,7 +42634,7 @@
         <v>44573</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>44859</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>45972</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>45544</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>45314</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -43009,7 +43009,7 @@
         <v>45429</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43082,7 +43082,7 @@
         <v>45975</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>45975</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43238,7 +43238,7 @@
         <v>45427</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45975</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45978</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43462,7 +43462,7 @@
         <v>45978</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43540,7 +43540,7 @@
         <v>45440</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43613,7 +43613,7 @@
         <v>44963</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43686,7 +43686,7 @@
         <v>45981</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43764,7 +43764,7 @@
         <v>45981</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43842,7 +43842,7 @@
         <v>45505</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>44979</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>45984</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45985</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>45985</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44222,7 +44222,7 @@
         <v>45470</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44300,7 +44300,7 @@
         <v>45818</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44378,7 +44378,7 @@
         <v>45744</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45986</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>45691</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
         <v>45988</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44670,7 +44670,7 @@
         <v>45988</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -44743,7 +44743,7 @@
         <v>45988</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44816,7 +44816,7 @@
         <v>45988</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>44529</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44962,7 +44962,7 @@
         <v>45574</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45875</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45113,7 +45113,7 @@
         <v>45764</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45186,7 +45186,7 @@
         <v>45014</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45259,7 +45259,7 @@
         <v>45995</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45995</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45405,7 +45405,7 @@
         <v>45994</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45478,7 +45478,7 @@
         <v>45994</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45551,7 +45551,7 @@
         <v>45995</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45995</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -45697,7 +45697,7 @@
         <v>45995</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45770,7 +45770,7 @@
         <v>45994</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>45994</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45916,7 +45916,7 @@
         <v>45994</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45996</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46062,7 +46062,7 @@
         <v>44964</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46140,7 +46140,7 @@
         <v>45674</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46213,7 +46213,7 @@
         <v>45999</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46286,7 +46286,7 @@
         <v>45770</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46359,7 +46359,7 @@
         <v>45254</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46432,7 +46432,7 @@
         <v>45906</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46505,7 +46505,7 @@
         <v>46000</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46578,7 +46578,7 @@
         <v>45894</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>46001</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>44796</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         <v>46001</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>46003</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>46164</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -47026,7 +47026,7 @@
         <v>46164</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -47104,7 +47104,7 @@
         <v>46003</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>46001</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47250,7 +47250,7 @@
         <v>46164</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>45694</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47406,7 +47406,7 @@
         <v>46164</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47484,7 +47484,7 @@
         <v>46009</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47557,7 +47557,7 @@
         <v>46009</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47630,7 +47630,7 @@
         <v>46008</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47703,7 +47703,7 @@
         <v>45994</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47776,7 +47776,7 @@
         <v>45523</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47854,7 +47854,7 @@
         <v>45149</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>45054</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>45429</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -48073,7 +48073,7 @@
         <v>46009</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>45085</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>45902</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48297,7 +48297,7 @@
         <v>46012</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>46012</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -48443,7 +48443,7 @@
         <v>46012</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -48516,7 +48516,7 @@
         <v>46168</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>46168</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45281</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -48740,7 +48740,7 @@
         <v>46168</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>46168</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48886,7 +48886,7 @@
         <v>46168</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48959,7 +48959,7 @@
         <v>44903</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -49032,7 +49032,7 @@
         <v>46020</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -49105,7 +49105,7 @@
         <v>46066</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -49178,7 +49178,7 @@
         <v>46066</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -49251,7 +49251,7 @@
         <v>45210</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>46029</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -49402,7 +49402,7 @@
         <v>46030</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -49480,7 +49480,7 @@
         <v>46030</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -49558,7 +49558,7 @@
         <v>46030</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -49636,7 +49636,7 @@
         <v>44524</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -49709,7 +49709,7 @@
         <v>46172</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -49787,7 +49787,7 @@
         <v>46020</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45212</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49938,7 +49938,7 @@
         <v>46171</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -50011,7 +50011,7 @@
         <v>44706</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -50084,7 +50084,7 @@
         <v>44747</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -50157,7 +50157,7 @@
         <v>46174</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -50230,7 +50230,7 @@
         <v>44673</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45548</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -50376,7 +50376,7 @@
         <v>46042</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -50449,7 +50449,7 @@
         <v>44657</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>44657</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -50595,7 +50595,7 @@
         <v>46042</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -50668,7 +50668,7 @@
         <v>44966</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>46048</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -50819,7 +50819,7 @@
         <v>46050</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>46175</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50965,7 +50965,7 @@
         <v>46052</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -51038,7 +51038,7 @@
         <v>45593</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -51116,7 +51116,7 @@
         <v>46178</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -51194,7 +51194,7 @@
         <v>46056</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -51267,7 +51267,7 @@
         <v>46056</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -51340,7 +51340,7 @@
         <v>45356</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -51413,7 +51413,7 @@
         <v>46177</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -51491,7 +51491,7 @@
         <v>46057</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -51564,7 +51564,7 @@
         <v>46059</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -51637,7 +51637,7 @@
         <v>46058</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -51710,7 +51710,7 @@
         <v>45429</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -51783,7 +51783,7 @@
         <v>45429</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51856,7 +51856,7 @@
         <v>46062</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51929,7 +51929,7 @@
         <v>45085</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -52002,7 +52002,7 @@
         <v>46063</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -52075,7 +52075,7 @@
         <v>46177</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -52153,7 +52153,7 @@
         <v>46063</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -52226,7 +52226,7 @@
         <v>46065</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -52304,7 +52304,7 @@
         <v>46170</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -52382,7 +52382,7 @@
         <v>46181</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -52460,7 +52460,7 @@
         <v>45483</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -52533,7 +52533,7 @@
         <v>45153</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -52606,7 +52606,7 @@
         <v>46182</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -52684,7 +52684,7 @@
         <v>46181</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -52762,7 +52762,7 @@
         <v>45509</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45256</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>45562</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52986,7 +52986,7 @@
         <v>45653</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -53059,7 +53059,7 @@
         <v>46078</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -53132,7 +53132,7 @@
         <v>46076</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -53205,7 +53205,7 @@
         <v>46183</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -53278,7 +53278,7 @@
         <v>46076</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>46076</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -53424,7 +53424,7 @@
         <v>45247</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -53497,7 +53497,7 @@
         <v>46184</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -53575,7 +53575,7 @@
         <v>46184</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -53673,7 +53673,7 @@
         <v>46183</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53746,7 +53746,7 @@
         <v>46183</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>46084</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53897,7 +53897,7 @@
         <v>46084</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53970,7 +53970,7 @@
         <v>46084</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -54043,7 +54043,7 @@
         <v>46184</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -54121,7 +54121,7 @@
         <v>45499</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -54194,7 +54194,7 @@
         <v>46084</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -54267,7 +54267,7 @@
         <v>46084</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -54340,7 +54340,7 @@
         <v>46086</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -54413,7 +54413,7 @@
         <v>45156</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -54486,7 +54486,7 @@
         <v>46087</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -54564,7 +54564,7 @@
         <v>44642</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -54642,7 +54642,7 @@
         <v>45070</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -54715,7 +54715,7 @@
         <v>44901</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -54788,7 +54788,7 @@
         <v>46185</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54861,7 +54861,7 @@
         <v>45195</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54939,7 +54939,7 @@
         <v>46092</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -55017,7 +55017,7 @@
         <v>45649</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -55090,7 +55090,7 @@
         <v>46097</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>45589</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -55246,7 +55246,7 @@
         <v>45589</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -55324,7 +55324,7 @@
         <v>45922</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>46100</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -55470,7 +55470,7 @@
         <v>45761</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -55548,7 +55548,7 @@
         <v>46099</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -55626,7 +55626,7 @@
         <v>46191</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -55699,7 +55699,7 @@
         <v>46196</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55772,7 +55772,7 @@
         <v>45460</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -55850,7 +55850,7 @@
         <v>46104</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55923,7 +55923,7 @@
         <v>45643</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -55996,7 +55996,7 @@
         <v>46197</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -56074,7 +56074,7 @@
         <v>46105</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -56147,7 +56147,7 @@
         <v>45350</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -56220,7 +56220,7 @@
         <v>46198</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -56293,7 +56293,7 @@
         <v>44732</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -56366,7 +56366,7 @@
         <v>46197</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -56439,7 +56439,7 @@
         <v>45677</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -56517,7 +56517,7 @@
         <v>46197</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -56590,7 +56590,7 @@
         <v>44908</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -56663,7 +56663,7 @@
         <v>46197</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -56736,7 +56736,7 @@
         <v>46197</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -56809,7 +56809,7 @@
         <v>45216</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56887,7 +56887,7 @@
         <v>44726</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -56960,7 +56960,7 @@
         <v>44566</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -57033,7 +57033,7 @@
         <v>46197</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -57106,7 +57106,7 @@
         <v>44841</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -57184,7 +57184,7 @@
         <v>45356</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -57257,7 +57257,7 @@
         <v>46202</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -57335,7 +57335,7 @@
         <v>46202</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -57413,7 +57413,7 @@
         <v>45980</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -57486,7 +57486,7 @@
         <v>46202</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -57559,7 +57559,7 @@
         <v>46122</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -57637,7 +57637,7 @@
         <v>46122</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -57710,7 +57710,7 @@
         <v>46126</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -57783,7 +57783,7 @@
         <v>46126</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57856,7 +57856,7 @@
         <v>44734</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57929,7 +57929,7 @@
         <v>46202</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -58007,7 +58007,7 @@
         <v>45653</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -58080,7 +58080,7 @@
         <v>46127</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -58153,7 +58153,7 @@
         <v>45770</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -58226,7 +58226,7 @@
         <v>45544</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -58299,7 +58299,7 @@
         <v>44795</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -58372,7 +58372,7 @@
         <v>45161</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -58445,7 +58445,7 @@
         <v>46203</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -58518,7 +58518,7 @@
         <v>46132</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -58596,7 +58596,7 @@
         <v>46132</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -58669,7 +58669,7 @@
         <v>46132</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58747,7 +58747,7 @@
         <v>46132</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -58825,7 +58825,7 @@
         <v>46204</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58898,7 +58898,7 @@
         <v>46203</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58971,7 +58971,7 @@
         <v>46246</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -59044,7 +59044,7 @@
         <v>46007</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -59117,7 +59117,7 @@
         <v>45194</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -59195,7 +59195,7 @@
         <v>46136</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -59273,7 +59273,7 @@
         <v>44908</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -59346,7 +59346,7 @@
         <v>46076</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -59419,7 +59419,7 @@
         <v>45358</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59492,7 +59492,7 @@
         <v>46204</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -59565,7 +59565,7 @@
         <v>46204</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -59638,7 +59638,7 @@
         <v>45680</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>46003</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -59789,7 +59789,7 @@
         <v>44484</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59862,7 +59862,7 @@
         <v>46029</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59935,7 +59935,7 @@
         <v>45187</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -60013,7 +60013,7 @@
         <v>44887</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -60091,7 +60091,7 @@
         <v>45166</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -60169,7 +60169,7 @@
         <v>45653</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -60242,7 +60242,7 @@
         <v>45174</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -60315,7 +60315,7 @@
         <v>45323</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -60388,7 +60388,7 @@
         <v>44931</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -60461,7 +60461,7 @@
         <v>45001</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -60534,7 +60534,7 @@
         <v>46251</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -60607,7 +60607,7 @@
         <v>45772</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60680,7 +60680,7 @@
         <v>45770</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -60753,7 +60753,7 @@
         <v>45708</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60831,7 +60831,7 @@
         <v>46206</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60909,7 +60909,7 @@
         <v>44964</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60987,7 +60987,7 @@
         <v>46251</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -61065,7 +61065,7 @@
         <v>46206</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -61143,7 +61143,7 @@
         <v>46208</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -61216,7 +61216,7 @@
         <v>46248</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -61289,7 +61289,7 @@
         <v>46206</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -61367,7 +61367,7 @@
         <v>45035</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -61440,7 +61440,7 @@
         <v>46211</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -61513,7 +61513,7 @@
         <v>45476</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -61586,7 +61586,7 @@
         <v>45093</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -61664,7 +61664,7 @@
         <v>44883</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -61742,7 +61742,7 @@
         <v>46252</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -61820,7 +61820,7 @@
         <v>46209</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -61898,7 +61898,7 @@
         <v>46209</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -61976,7 +61976,7 @@
         <v>45529</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -62049,7 +62049,7 @@
         <v>45099</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -62122,7 +62122,7 @@
         <v>44484</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -62195,7 +62195,7 @@
         <v>46253</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -62268,7 +62268,7 @@
         <v>46209</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -62346,7 +62346,7 @@
         <v>45454</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -62419,7 +62419,7 @@
         <v>44614</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -62492,7 +62492,7 @@
         <v>45079</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -62565,7 +62565,7 @@
         <v>45762</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -62638,7 +62638,7 @@
         <v>46254</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -62716,7 +62716,7 @@
         <v>45646</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -62789,7 +62789,7 @@
         <v>45205</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -62862,7 +62862,7 @@
         <v>45233</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -62940,7 +62940,7 @@
         <v>46254</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -63013,7 +63013,7 @@
         <v>46254</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -63086,7 +63086,7 @@
         <v>46255</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -63164,7 +63164,7 @@
         <v>45379</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -63237,7 +63237,7 @@
         <v>45773</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -63315,7 +63315,7 @@
         <v>46259</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -63393,7 +63393,7 @@
         <v>44994</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -63466,7 +63466,7 @@
         <v>46259</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -63544,7 +63544,7 @@
         <v>46259</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -63622,7 +63622,7 @@
         <v>44568</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -63695,7 +63695,7 @@
         <v>45572</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -63773,7 +63773,7 @@
         <v>45764</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -63846,7 +63846,7 @@
         <v>45764</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -63919,7 +63919,7 @@
         <v>45618</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -63997,7 +63997,7 @@
         <v>45099</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -64070,7 +64070,7 @@
         <v>46261</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -64148,7 +64148,7 @@
         <v>45924</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -64221,7 +64221,7 @@
         <v>46261</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -64294,7 +64294,7 @@
         <v>46261</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -64367,7 +64367,7 @@
         <v>46261</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -64440,7 +64440,7 @@
         <v>44812</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -64513,7 +64513,7 @@
         <v>46217</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -64591,7 +64591,7 @@
         <v>45894</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -64664,7 +64664,7 @@
         <v>46261</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -64757,7 +64757,7 @@
         <v>44823</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -64835,7 +64835,7 @@
         <v>46217</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -64913,7 +64913,7 @@
         <v>46217</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -64991,7 +64991,7 @@
         <v>46217</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -65069,7 +65069,7 @@
         <v>45625</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -65147,7 +65147,7 @@
         <v>44856</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -65220,7 +65220,7 @@
         <v>45013</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -65293,7 +65293,7 @@
         <v>44585</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -65366,7 +65366,7 @@
         <v>46168</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -65439,7 +65439,7 @@
         <v>45204</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -65512,7 +65512,7 @@
         <v>45687</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -65585,7 +65585,7 @@
         <v>46266</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -65663,7 +65663,7 @@
         <v>46267</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -65736,7 +65736,7 @@
         <v>46267</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -65809,7 +65809,7 @@
         <v>46267</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -65882,7 +65882,7 @@
         <v>44935</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -65955,7 +65955,7 @@
         <v>45453</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -66028,7 +66028,7 @@
         <v>45646</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -66101,7 +66101,7 @@
         <v>46269</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -66179,7 +66179,7 @@
         <v>45478</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -66252,7 +66252,7 @@
         <v>46268</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -66325,7 +66325,7 @@
         <v>46225</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -66403,7 +66403,7 @@
         <v>46268</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -66481,7 +66481,7 @@
         <v>45391</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -66554,7 +66554,7 @@
         <v>46029</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -66627,7 +66627,7 @@
         <v>46272</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -66705,7 +66705,7 @@
         <v>45778</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -66783,7 +66783,7 @@
         <v>45782</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -66856,7 +66856,7 @@
         <v>46273</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -66934,7 +66934,7 @@
         <v>46268</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -67012,7 +67012,7 @@
         <v>46270</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -67085,7 +67085,7 @@
         <v>46274</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -67158,7 +67158,7 @@
         <v>46274</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -67231,7 +67231,7 @@
         <v>46275</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -67304,7 +67304,7 @@
         <v>46275</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -67377,7 +67377,7 @@
         <v>46274</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -67450,7 +67450,7 @@
         <v>46274</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -67528,7 +67528,7 @@
         <v>46275</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -67606,7 +67606,7 @@
         <v>46275</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -67679,7 +67679,7 @@
         <v>46275</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -67752,7 +67752,7 @@
         <v>46234</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -67830,7 +67830,7 @@
         <v>46276</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -67903,7 +67903,7 @@
         <v>46276</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -67976,7 +67976,7 @@
         <v>46234</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -68054,7 +68054,7 @@
         <v>46234</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -68132,7 +68132,7 @@
         <v>45149</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -68205,7 +68205,7 @@
         <v>45786</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -68283,7 +68283,7 @@
         <v>46281</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -68361,7 +68361,7 @@
         <v>46281</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -68439,7 +68439,7 @@
         <v>46238</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -68517,7 +68517,7 @@
         <v>46281</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -68590,7 +68590,7 @@
         <v>46238</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -68668,7 +68668,7 @@
         <v>45791</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -68746,7 +68746,7 @@
         <v>46281</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -68824,7 +68824,7 @@
         <v>45379</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -68897,7 +68897,7 @@
         <v>45793</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -68975,7 +68975,7 @@
         <v>45793</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -69053,7 +69053,7 @@
         <v>45793</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -69131,7 +69131,7 @@
         <v>46283</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -69209,7 +69209,7 @@
         <v>45590</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -69282,7 +69282,7 @@
         <v>45590</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -69355,7 +69355,7 @@
         <v>46239</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -69433,7 +69433,7 @@
         <v>46240</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -69506,7 +69506,7 @@
         <v>45797</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -69584,7 +69584,7 @@
         <v>45799</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -69662,7 +69662,7 @@
         <v>46240</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -69740,7 +69740,7 @@
         <v>46029</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -69818,7 +69818,7 @@
         <v>46283</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -69896,7 +69896,7 @@
         <v>45798</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -69974,7 +69974,7 @@
         <v>45798</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -70052,7 +70052,7 @@
         <v>44862</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -70125,7 +70125,7 @@
         <v>45798</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -70203,7 +70203,7 @@
         <v>45803</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -70276,7 +70276,7 @@
         <v>45608</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -70349,7 +70349,7 @@
         <v>45608</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -70422,7 +70422,7 @@
         <v>45590</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -70495,7 +70495,7 @@
         <v>45429</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -70568,7 +70568,7 @@
         <v>45464</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -70646,7 +70646,7 @@
         <v>45645</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -70719,7 +70719,7 @@
         <v>45763</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -70792,7 +70792,7 @@
         <v>45546</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -70870,7 +70870,7 @@
         <v>45243</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -70943,7 +70943,7 @@
         <v>45813</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -71016,7 +71016,7 @@
         <v>45813</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -71094,7 +71094,7 @@
         <v>45813</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -71172,7 +71172,7 @@
         <v>45316</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -71245,7 +71245,7 @@
         <v>45481</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -71323,7 +71323,7 @@
         <v>45766</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -71401,7 +71401,7 @@
         <v>45818</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -71479,7 +71479,7 @@
         <v>45427</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -71552,7 +71552,7 @@
         <v>45818</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -71630,7 +71630,7 @@
         <v>45574</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -71708,7 +71708,7 @@
         <v>45818</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -71786,7 +71786,7 @@
         <v>45826</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -71864,7 +71864,7 @@
         <v>45832</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -71937,7 +71937,7 @@
         <v>45833</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -72015,7 +72015,7 @@
         <v>45833</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -72093,7 +72093,7 @@
         <v>45835</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -72171,7 +72171,7 @@
         <v>45803</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -72244,7 +72244,7 @@
         <v>45840</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -72322,7 +72322,7 @@
         <v>45840</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -72400,7 +72400,7 @@
         <v>45747</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -72473,7 +72473,7 @@
         <v>45843</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -72551,7 +72551,7 @@
         <v>45603</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -72624,7 +72624,7 @@
         <v>45856</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -72702,7 +72702,7 @@
         <v>45796</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -72780,7 +72780,7 @@
         <v>45674</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -72853,7 +72853,7 @@
         <v>45596</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -72926,7 +72926,7 @@
         <v>45863</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -72999,7 +72999,7 @@
         <v>45456</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -73072,7 +73072,7 @@
         <v>45369</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -73145,7 +73145,7 @@
         <v>45838</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -73218,7 +73218,7 @@
         <v>45868</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -73296,7 +73296,7 @@
         <v>45877</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -73374,7 +73374,7 @@
         <v>45880</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -73452,7 +73452,7 @@
         <v>45881</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -73525,7 +73525,7 @@
         <v>45882</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -73598,7 +73598,7 @@
         <v>45882</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -73671,7 +73671,7 @@
         <v>45376</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -73749,7 +73749,7 @@
         <v>45013</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -73822,7 +73822,7 @@
         <v>45376</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -73900,7 +73900,7 @@
         <v>45667</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -73973,7 +73973,7 @@
         <v>44945</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -74051,7 +74051,7 @@
         <v>45743</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -74124,7 +74124,7 @@
         <v>45743</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -74197,7 +74197,7 @@
         <v>45789</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -74275,7 +74275,7 @@
         <v>45792</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -74348,7 +74348,7 @@
         <v>45799</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -74426,7 +74426,7 @@
         <v>45799</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -74504,7 +74504,7 @@
         <v>45799</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -74582,7 +74582,7 @@
         <v>45810</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -74660,7 +74660,7 @@
         <v>45818</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -74738,7 +74738,7 @@
         <v>45840</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -74816,7 +74816,7 @@
         <v>46018</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -74889,7 +74889,7 @@
         <v>46147</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -74962,7 +74962,7 @@
         <v>46147</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -75035,7 +75035,7 @@
         <v>46147</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -75113,7 +75113,7 @@
         <v>46152</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -75186,7 +75186,7 @@
         <v>46152</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -75259,7 +75259,7 @@
         <v>46148</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>

--- a/Översikt BODEN.xlsx
+++ b/Översikt BODEN.xlsx
@@ -601,7 +601,7 @@
         <v>45152</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45506</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>45152</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45068</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>45075</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>44853</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>45152</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>46168</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>46247</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>45105</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>44964</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>45212</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>45790</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>46149</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>44889</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45684</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>45771</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>44859</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44853</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>45049</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>45295</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>46210</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>46195</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>44869</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>45418</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>45463</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>44489</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>44795</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44904</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>45893</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>45912</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>45912</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>45428</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>45512</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>45964</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>45832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>46149</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>46209</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>45835</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>45988</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>45645</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>45980</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>46148</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>46196</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>46261</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>45307</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>45980</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>44833</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>45698</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>46073</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>45933</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>45952</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>45981</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>45818</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>45791</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>45077</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>45155</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>46181</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         <v>46184</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>46205</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>46258</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>46217</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7996,7 +7996,7 @@
         <v>44755</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>46267</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>46240</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>46286</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         <v>44487</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>44648</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>44804</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>44796</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>44735</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>45638</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>46066</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>46066</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>44573</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>45803</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>45910</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>45910</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>45922</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>45701</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>45526</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>45714</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>45137</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>45820</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>45999</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>45834</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>46149</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>46164</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>44678</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>46184</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>46184</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>45875</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>45645</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>44573</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>45517</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>46205</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>46205</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>46205</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>45594</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>46258</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>46217</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>46261</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>46261</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>46225</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>46267</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>46270</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>46286</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>46245</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>46247</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>45301</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>44830</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13424,7 +13424,7 @@
         <v>45072</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         <v>45341</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>45376</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>44648</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>44840</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>45763</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         <v>45211</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>45406</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>45901</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>46048</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>45448</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>45905</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>44648</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>44529</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>45884</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>45559</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>45513</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>45944</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>46100</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>45947</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         <v>45949</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>45950</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         <v>45952</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>45958</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>45960</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>45975</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>45994</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>45999</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>46003</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>44642</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>46147</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>46168</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>46178</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>46178</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>46178</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>46183</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>46184</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>46205</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>46251</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>46255</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         <v>46261</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17917,7 +17917,7 @@
         <v>46261</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>46261</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         <v>46261</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>44692</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>46272</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18469,7 +18469,7 @@
         <v>46267</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>46272</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>46236</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>46282</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>46240</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>45966</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>46241</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>46037</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>44925</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>45313</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         <v>46134</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>45538</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>44529</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>44944</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>45418</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>45028</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         <v>45643</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20320,7 +20320,7 @@
         <v>45799</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20434,7 +20434,7 @@
         <v>45901</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>45952</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44509</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>44677</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>44577</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20873,7 +20873,7 @@
         <v>44659</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>44671</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>44852</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21097,7 +21097,7 @@
         <v>44489</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>44815</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>44648</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21331,7 +21331,7 @@
         <v>44617</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>44648</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>44865</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>44609</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>44609</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21706,7 +21706,7 @@
         <v>44671</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>44887</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>44721</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>44543</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>44530</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22076,7 +22076,7 @@
         <v>44648</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>44473</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22232,7 +22232,7 @@
         <v>44734</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>44566</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44566</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22451,7 +22451,7 @@
         <v>44600</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>44749</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>44722</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>44480</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>44530</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22821,7 +22821,7 @@
         <v>44565</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22894,7 +22894,7 @@
         <v>44573</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44566</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>44617</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>44820</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>44625</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>44596</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23347,7 +23347,7 @@
         <v>44831</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>44799</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>44799</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>44743</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>44480</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>44529</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>44565</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>44635</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44797</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24024,7 +24024,7 @@
         <v>44796</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>44796</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>44484</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>44489</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>44795</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44812</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>44671</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>45572</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44734</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>45763</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>45358</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>45356</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>44935</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>45301</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>45093</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>45254</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>45463</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>44477</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>45429</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>45512</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>44558</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>44883</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>46012</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25733,7 +25733,7 @@
         <v>46012</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25806,7 +25806,7 @@
         <v>45884</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>45902</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25962,7 +25962,7 @@
         <v>46020</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>45419</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>46066</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>46066</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26254,7 +26254,7 @@
         <v>46030</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26332,7 +26332,7 @@
         <v>46030</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>45793</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26488,7 +26488,7 @@
         <v>46029</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>46030</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>45590</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         <v>45590</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         <v>45516</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26863,7 +26863,7 @@
         <v>45516</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -26941,7 +26941,7 @@
         <v>45793</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>45798</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>45798</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27175,7 +27175,7 @@
         <v>45797</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27253,7 +27253,7 @@
         <v>45798</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44862</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27404,7 +27404,7 @@
         <v>45527</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27477,7 +27477,7 @@
         <v>46020</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27550,7 +27550,7 @@
         <v>45589</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>45649</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>45649</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27774,7 +27774,7 @@
         <v>45643</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>45764</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27925,7 +27925,7 @@
         <v>45764</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>45764</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>45891</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28144,7 +28144,7 @@
         <v>46042</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28217,7 +28217,7 @@
         <v>46042</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28290,7 +28290,7 @@
         <v>45799</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28368,7 +28368,7 @@
         <v>45897</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>44908</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28514,7 +28514,7 @@
         <v>45897</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>45429</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>45429</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28733,7 +28733,7 @@
         <v>46048</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28806,7 +28806,7 @@
         <v>45902</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28884,7 +28884,7 @@
         <v>45901</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>44994</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>46050</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>45590</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>45907</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>46052</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>45910</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>45204</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>44889</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29561,7 +29561,7 @@
         <v>45910</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44901</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29712,7 +29712,7 @@
         <v>45911</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29785,7 +29785,7 @@
         <v>45912</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29858,7 +29858,7 @@
         <v>46056</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -29931,7 +29931,7 @@
         <v>46056</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>45912</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>45912</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>44903</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30228,7 +30228,7 @@
         <v>44529</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30301,7 +30301,7 @@
         <v>45803</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30374,7 +30374,7 @@
         <v>46057</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>46058</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30520,7 +30520,7 @@
         <v>46062</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30593,7 +30593,7 @@
         <v>45915</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30671,7 +30671,7 @@
         <v>45915</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>45915</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>45691</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30900,7 +30900,7 @@
         <v>46059</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30973,7 +30973,7 @@
         <v>46063</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -31046,7 +31046,7 @@
         <v>46063</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31119,7 +31119,7 @@
         <v>44881</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31192,7 +31192,7 @@
         <v>44966</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>45919</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31348,7 +31348,7 @@
         <v>45919</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31426,7 +31426,7 @@
         <v>46065</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31504,7 +31504,7 @@
         <v>45922</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31577,7 +31577,7 @@
         <v>45922</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31650,7 +31650,7 @@
         <v>45922</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31723,7 +31723,7 @@
         <v>45750</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>45132</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31874,7 +31874,7 @@
         <v>45590</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31947,7 +31947,7 @@
         <v>45013</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -32020,7 +32020,7 @@
         <v>45924</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>45926</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>45926</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>45264</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
         <v>46076</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>45926</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>46076</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>45608</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>45925</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>45925</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32755,7 +32755,7 @@
         <v>45708</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32833,7 +32833,7 @@
         <v>46076</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45653</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>45930</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         <v>45608</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>45930</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>46078</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>45523</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33359,7 +33359,7 @@
         <v>46084</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33432,7 +33432,7 @@
         <v>45763</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>46084</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>46084</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33651,7 +33651,7 @@
         <v>46084</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33724,7 +33724,7 @@
         <v>45546</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33802,7 +33802,7 @@
         <v>45464</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33880,7 +33880,7 @@
         <v>45587</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33953,7 +33953,7 @@
         <v>45243</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -34026,7 +34026,7 @@
         <v>45583</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>45931</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>46084</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>45936</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>46086</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>45933</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>46087</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>45649</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34630,7 +34630,7 @@
         <v>45649</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>45906</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34776,7 +34776,7 @@
         <v>45645</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34849,7 +34849,7 @@
         <v>45933</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34927,7 +34927,7 @@
         <v>45933</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -35005,7 +35005,7 @@
         <v>45429</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>45937</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>45938</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35229,7 +35229,7 @@
         <v>44726</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35302,7 +35302,7 @@
         <v>45938</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>45938</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35453,7 +35453,7 @@
         <v>44642</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>45548</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35604,7 +35604,7 @@
         <v>45922</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45054</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35750,7 +35750,7 @@
         <v>45939</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35828,7 +35828,7 @@
         <v>45944</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>46097</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>45944</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -36052,7 +36052,7 @@
         <v>44963</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>46099</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36203,7 +36203,7 @@
         <v>45238</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36276,7 +36276,7 @@
         <v>45944</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>45944</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36432,7 +36432,7 @@
         <v>45761</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36510,7 +36510,7 @@
         <v>45943</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36583,7 +36583,7 @@
         <v>45944</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36661,7 +36661,7 @@
         <v>45945</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>46100</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36807,7 +36807,7 @@
         <v>45945</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36880,7 +36880,7 @@
         <v>45945</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36958,7 +36958,7 @@
         <v>45764</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -37031,7 +37031,7 @@
         <v>46105</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>45950</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>45764</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37250,7 +37250,7 @@
         <v>46104</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>45947</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37401,7 +37401,7 @@
         <v>45770</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37474,7 +37474,7 @@
         <v>44657</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>44657</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37620,7 +37620,7 @@
         <v>44490</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>44994</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>44673</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>45562</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37922,7 +37922,7 @@
         <v>45953</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>45953</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -38073,7 +38073,7 @@
         <v>45589</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38151,7 +38151,7 @@
         <v>45589</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38229,7 +38229,7 @@
         <v>45953</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38307,7 +38307,7 @@
         <v>45950</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38380,7 +38380,7 @@
         <v>45955</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38453,7 +38453,7 @@
         <v>45955</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>45980</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
         <v>45960</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38677,7 +38677,7 @@
         <v>45961</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>45964</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38823,7 +38823,7 @@
         <v>46122</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38901,7 +38901,7 @@
         <v>45965</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>46122</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39047,7 +39047,7 @@
         <v>45965</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -39120,7 +39120,7 @@
         <v>45966</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39193,7 +39193,7 @@
         <v>45625</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>45965</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>45965</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39417,7 +39417,7 @@
         <v>46126</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39490,7 +39490,7 @@
         <v>44903</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>45813</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>45813</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>45971</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39792,7 +39792,7 @@
         <v>45813</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>45766</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>45212</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -40016,7 +40016,7 @@
         <v>45972</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>46126</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>46127</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40235,7 +40235,7 @@
         <v>46132</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40308,7 +40308,7 @@
         <v>45975</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40386,7 +40386,7 @@
         <v>45818</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40464,7 +40464,7 @@
         <v>45978</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40542,7 +40542,7 @@
         <v>45818</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>45975</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -40698,7 +40698,7 @@
         <v>45161</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45316</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>45427</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40922,7 +40922,7 @@
         <v>46132</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>46132</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41078,7 +41078,7 @@
         <v>45975</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>45978</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>44994</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>46132</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>45195</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>45981</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>45981</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41614,7 +41614,7 @@
         <v>45985</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41687,7 +41687,7 @@
         <v>45986</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41760,7 +41760,7 @@
         <v>44796</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>45985</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41911,7 +41911,7 @@
         <v>45984</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41984,7 +41984,7 @@
         <v>45988</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>45988</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42130,7 +42130,7 @@
         <v>46007</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42203,7 +42203,7 @@
         <v>45574</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42281,7 +42281,7 @@
         <v>45085</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42354,7 +42354,7 @@
         <v>45153</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42427,7 +42427,7 @@
         <v>45481</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42505,7 +42505,7 @@
         <v>45994</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42578,7 +42578,7 @@
         <v>45649</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42651,7 +42651,7 @@
         <v>45994</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -42724,7 +42724,7 @@
         <v>45994</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42797,7 +42797,7 @@
         <v>45149</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42870,7 +42870,7 @@
         <v>45994</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42943,7 +42943,7 @@
         <v>45994</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -43016,7 +43016,7 @@
         <v>44484</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>45995</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -43162,7 +43162,7 @@
         <v>45995</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43235,7 +43235,7 @@
         <v>45995</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43308,7 +43308,7 @@
         <v>45995</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43381,7 +43381,7 @@
         <v>45996</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43454,7 +43454,7 @@
         <v>45995</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43527,7 +43527,7 @@
         <v>45906</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>46076</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43673,7 +43673,7 @@
         <v>45935</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43746,7 +43746,7 @@
         <v>45999</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43819,7 +43819,7 @@
         <v>44856</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43892,7 +43892,7 @@
         <v>46000</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43965,7 +43965,7 @@
         <v>46001</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44038,7 +44038,7 @@
         <v>45103</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44111,7 +44111,7 @@
         <v>45586</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44189,7 +44189,7 @@
         <v>46001</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44262,7 +44262,7 @@
         <v>44823</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44340,7 +44340,7 @@
         <v>45818</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44418,7 +44418,7 @@
         <v>46001</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44491,7 +44491,7 @@
         <v>46003</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44564,7 +44564,7 @@
         <v>44568</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>46136</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -44715,7 +44715,7 @@
         <v>45944</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44788,7 +44788,7 @@
         <v>45832</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44861,7 +44861,7 @@
         <v>46003</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44934,7 +44934,7 @@
         <v>46003</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45012,7 +45012,7 @@
         <v>45667</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45085,7 +45085,7 @@
         <v>44648</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45163,7 +45163,7 @@
         <v>46008</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45236,7 +45236,7 @@
         <v>45499</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45309,7 +45309,7 @@
         <v>45194</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>46009</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>46009</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>45649</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45606,7 +45606,7 @@
         <v>45709</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -45684,7 +45684,7 @@
         <v>45994</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45757,7 +45757,7 @@
         <v>45764</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45830,7 +45830,7 @@
         <v>46009</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45839</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45976,7 +45976,7 @@
         <v>45860</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46054,7 +46054,7 @@
         <v>45773</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46132,7 +46132,7 @@
         <v>45818</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46205,7 +46205,7 @@
         <v>45999</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46278,7 +46278,7 @@
         <v>46029</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45645</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46429,7 +46429,7 @@
         <v>46029</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46502,7 +46502,7 @@
         <v>45672</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46575,7 +46575,7 @@
         <v>45408</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -46648,7 +46648,7 @@
         <v>44474</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46721,7 +46721,7 @@
         <v>46003</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46794,7 +46794,7 @@
         <v>46076</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>45826</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46945,7 +46945,7 @@
         <v>45748</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -47018,7 +47018,7 @@
         <v>44524</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>45761</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -47164,7 +47164,7 @@
         <v>44881</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>45248</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47315,7 +47315,7 @@
         <v>46084</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47388,7 +47388,7 @@
         <v>45210</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47466,7 +47466,7 @@
         <v>45893</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47544,7 +47544,7 @@
         <v>44887</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47622,7 +47622,7 @@
         <v>44565</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47695,7 +47695,7 @@
         <v>45233</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47773,7 +47773,7 @@
         <v>45841</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45070</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47919,7 +47919,7 @@
         <v>45085</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47992,7 +47992,7 @@
         <v>44529</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -48065,7 +48065,7 @@
         <v>46148</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>45070</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -48216,7 +48216,7 @@
         <v>46147</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48289,7 +48289,7 @@
         <v>46150</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>46150</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -48435,7 +48435,7 @@
         <v>46150</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -48508,7 +48508,7 @@
         <v>46149</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -48581,7 +48581,7 @@
         <v>46149</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>45833</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -48732,7 +48732,7 @@
         <v>46154</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48810,7 +48810,7 @@
         <v>45408</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>45427</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48956,7 +48956,7 @@
         <v>45833</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -49034,7 +49034,7 @@
         <v>44812</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -49107,7 +49107,7 @@
         <v>45079</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>46154</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -49253,7 +49253,7 @@
         <v>45102</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45639</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -49399,7 +49399,7 @@
         <v>45593</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -49477,7 +49477,7 @@
         <v>45988</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -49550,7 +49550,7 @@
         <v>45646</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -49623,7 +49623,7 @@
         <v>45803</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -49696,7 +49696,7 @@
         <v>46155</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -49769,7 +49769,7 @@
         <v>45440</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>45835</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49920,7 +49920,7 @@
         <v>45840</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49998,7 +49998,7 @@
         <v>45406</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -50071,7 +50071,7 @@
         <v>45747</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -50144,7 +50144,7 @@
         <v>45840</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -50222,7 +50222,7 @@
         <v>45818</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -50300,7 +50300,7 @@
         <v>45875</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -50373,7 +50373,7 @@
         <v>44489</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -50446,7 +50446,7 @@
         <v>45744</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -50519,7 +50519,7 @@
         <v>45691</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>46164</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>46164</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -50748,7 +50748,7 @@
         <v>46164</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -50826,7 +50826,7 @@
         <v>46164</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50904,7 +50904,7 @@
         <v>45843</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50982,7 +50982,7 @@
         <v>45674</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -51055,7 +51055,7 @@
         <v>44908</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -51128,7 +51128,7 @@
         <v>45099</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -51201,7 +51201,7 @@
         <v>46168</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -51274,7 +51274,7 @@
         <v>46168</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -51347,7 +51347,7 @@
         <v>45894</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -51425,7 +51425,7 @@
         <v>45358</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -51498,7 +51498,7 @@
         <v>45603</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -51571,7 +51571,7 @@
         <v>46168</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -51644,7 +51644,7 @@
         <v>46168</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -51717,7 +51717,7 @@
         <v>46168</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -51790,7 +51790,7 @@
         <v>45674</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51863,7 +51863,7 @@
         <v>45110</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51941,7 +51941,7 @@
         <v>45596</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -52014,7 +52014,7 @@
         <v>46171</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -52087,7 +52087,7 @@
         <v>45796</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -52165,7 +52165,7 @@
         <v>45863</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -52238,7 +52238,7 @@
         <v>46172</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -52316,7 +52316,7 @@
         <v>46174</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -52389,7 +52389,7 @@
         <v>46175</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -52462,7 +52462,7 @@
         <v>45551</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -52540,7 +52540,7 @@
         <v>45544</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -52613,7 +52613,7 @@
         <v>45574</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -52691,7 +52691,7 @@
         <v>45574</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -52769,7 +52769,7 @@
         <v>45281</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52847,7 +52847,7 @@
         <v>46177</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52925,7 +52925,7 @@
         <v>46177</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -53003,7 +53003,7 @@
         <v>44529</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -53076,7 +53076,7 @@
         <v>45838</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -53149,7 +53149,7 @@
         <v>45356</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -53222,7 +53222,7 @@
         <v>46178</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -53300,7 +53300,7 @@
         <v>45456</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -53373,7 +53373,7 @@
         <v>46181</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -53451,7 +53451,7 @@
         <v>45156</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -53524,7 +53524,7 @@
         <v>44983</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -53597,7 +53597,7 @@
         <v>45618</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -53675,7 +53675,7 @@
         <v>46183</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53748,7 +53748,7 @@
         <v>46170</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -53826,7 +53826,7 @@
         <v>46183</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53904,7 +53904,7 @@
         <v>46182</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53982,7 +53982,7 @@
         <v>46183</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -54055,7 +54055,7 @@
         <v>45604</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -54128,7 +54128,7 @@
         <v>46185</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -54201,7 +54201,7 @@
         <v>46184</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -54299,7 +54299,7 @@
         <v>45772</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -54372,7 +54372,7 @@
         <v>46184</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -54450,7 +54450,7 @@
         <v>46184</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -54528,7 +54528,7 @@
         <v>44522</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -54601,7 +54601,7 @@
         <v>45591</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -54679,7 +54679,7 @@
         <v>44609</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -54752,7 +54752,7 @@
         <v>45369</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -54825,7 +54825,7 @@
         <v>45161</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54903,7 +54903,7 @@
         <v>45161</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54981,7 +54981,7 @@
         <v>45758</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -55054,7 +55054,7 @@
         <v>46191</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -55127,7 +55127,7 @@
         <v>44795</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -55200,7 +55200,7 @@
         <v>45868</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -55278,7 +55278,7 @@
         <v>46197</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -55356,7 +55356,7 @@
         <v>45216</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -55434,7 +55434,7 @@
         <v>46197</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -55507,7 +55507,7 @@
         <v>46197</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -55580,7 +55580,7 @@
         <v>45596</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -55653,7 +55653,7 @@
         <v>45600</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -55726,7 +55726,7 @@
         <v>45600</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55799,7 +55799,7 @@
         <v>44566</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -55872,7 +55872,7 @@
         <v>45877</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55950,7 +55950,7 @@
         <v>46198</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -56023,7 +56023,7 @@
         <v>46196</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -56096,7 +56096,7 @@
         <v>46197</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -56169,7 +56169,7 @@
         <v>45643</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -56242,7 +56242,7 @@
         <v>45880</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -56320,7 +56320,7 @@
         <v>45881</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -56393,7 +56393,7 @@
         <v>45478</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -56466,7 +56466,7 @@
         <v>46203</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -56539,7 +56539,7 @@
         <v>45882</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -56612,7 +56612,7 @@
         <v>45882</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -56685,7 +56685,7 @@
         <v>46204</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -56758,7 +56758,7 @@
         <v>46202</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -56836,7 +56836,7 @@
         <v>46202</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56914,7 +56914,7 @@
         <v>46202</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -56992,7 +56992,7 @@
         <v>45411</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -57065,7 +57065,7 @@
         <v>45310</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -57143,7 +57143,7 @@
         <v>45884</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -57221,7 +57221,7 @@
         <v>45446</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -57294,7 +57294,7 @@
         <v>46204</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -57367,7 +57367,7 @@
         <v>46204</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -57440,7 +57440,7 @@
         <v>44628</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -57513,7 +57513,7 @@
         <v>45561</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -57586,7 +57586,7 @@
         <v>45512</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -57659,7 +57659,7 @@
         <v>46209</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -57737,7 +57737,7 @@
         <v>46252</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -57815,7 +57815,7 @@
         <v>46206</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57893,7 +57893,7 @@
         <v>46251</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57971,7 +57971,7 @@
         <v>46251</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -58044,7 +58044,7 @@
         <v>44859</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -58122,7 +58122,7 @@
         <v>46206</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -58200,7 +58200,7 @@
         <v>46206</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -58278,7 +58278,7 @@
         <v>46208</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -58351,7 +58351,7 @@
         <v>46209</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -58429,7 +58429,7 @@
         <v>46209</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -58507,7 +58507,7 @@
         <v>45212</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -58585,7 +58585,7 @@
         <v>45687</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -58658,7 +58658,7 @@
         <v>45560</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -58736,7 +58736,7 @@
         <v>46211</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58809,7 +58809,7 @@
         <v>45770</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -58882,7 +58882,7 @@
         <v>46253</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58955,7 +58955,7 @@
         <v>46254</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -59033,7 +59033,7 @@
         <v>46255</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>45505</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -59189,7 +59189,7 @@
         <v>46254</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -59262,7 +59262,7 @@
         <v>46254</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -59335,7 +59335,7 @@
         <v>46259</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -59413,7 +59413,7 @@
         <v>45460</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -59491,7 +59491,7 @@
         <v>46259</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59569,7 +59569,7 @@
         <v>46259</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -59647,7 +59647,7 @@
         <v>46217</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -59725,7 +59725,7 @@
         <v>46217</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59803,7 +59803,7 @@
         <v>46217</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -59881,7 +59881,7 @@
         <v>45237</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>46217</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -60032,7 +60032,7 @@
         <v>45210</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
         <v>45924</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -60183,7 +60183,7 @@
         <v>45894</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -60256,7 +60256,7 @@
         <v>46261</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -60329,7 +60329,7 @@
         <v>45194</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -60407,7 +60407,7 @@
         <v>46261</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -60480,7 +60480,7 @@
         <v>46261</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -60553,7 +60553,7 @@
         <v>46261</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -60646,7 +60646,7 @@
         <v>45161</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -60719,7 +60719,7 @@
         <v>46261</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60797,7 +60797,7 @@
         <v>44783</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -60870,7 +60870,7 @@
         <v>45201</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60943,7 +60943,7 @@
         <v>45728</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -61021,7 +61021,7 @@
         <v>45246</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -61094,7 +61094,7 @@
         <v>45762</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -61167,7 +61167,7 @@
         <v>46266</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -61245,7 +61245,7 @@
         <v>46168</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -61318,7 +61318,7 @@
         <v>45166</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -61396,7 +61396,7 @@
         <v>45718</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -61469,7 +61469,7 @@
         <v>45247</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -61542,7 +61542,7 @@
         <v>45314</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -61615,7 +61615,7 @@
         <v>45256</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -61688,7 +61688,7 @@
         <v>44484</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -61761,7 +61761,7 @@
         <v>46268</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -61834,7 +61834,7 @@
         <v>46225</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -61912,7 +61912,7 @@
         <v>45680</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -61990,7 +61990,7 @@
         <v>46268</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -62068,7 +62068,7 @@
         <v>45254</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -62141,7 +62141,7 @@
         <v>46267</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -62214,7 +62214,7 @@
         <v>45257</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -62287,7 +62287,7 @@
         <v>46029</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -62360,7 +62360,7 @@
         <v>44648</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -62438,7 +62438,7 @@
         <v>45264</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -62516,7 +62516,7 @@
         <v>46272</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -62594,7 +62594,7 @@
         <v>46269</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -62672,7 +62672,7 @@
         <v>46270</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -62745,7 +62745,7 @@
         <v>46268</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -62823,7 +62823,7 @@
         <v>46274</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -62896,7 +62896,7 @@
         <v>45356</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -62969,7 +62969,7 @@
         <v>46273</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -63047,7 +63047,7 @@
         <v>46274</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -63125,7 +63125,7 @@
         <v>46274</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -63198,7 +63198,7 @@
         <v>44474</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -63271,7 +63271,7 @@
         <v>45694</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -63349,7 +63349,7 @@
         <v>46274</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -63422,7 +63422,7 @@
         <v>45260</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -63495,7 +63495,7 @@
         <v>45022</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -63568,7 +63568,7 @@
         <v>46276</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -63641,7 +63641,7 @@
         <v>46275</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -63714,7 +63714,7 @@
         <v>46275</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -63792,7 +63792,7 @@
         <v>44573</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -63870,7 +63870,7 @@
         <v>46276</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -63943,7 +63943,7 @@
         <v>45345</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -64016,7 +64016,7 @@
         <v>46275</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -64089,7 +64089,7 @@
         <v>46275</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -64162,7 +64162,7 @@
         <v>45483</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -64235,7 +64235,7 @@
         <v>45285</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -64308,7 +64308,7 @@
         <v>46275</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -64381,7 +64381,7 @@
         <v>46234</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -64459,7 +64459,7 @@
         <v>45529</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -64532,7 +64532,7 @@
         <v>44732</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -64605,7 +64605,7 @@
         <v>45323</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -64678,7 +64678,7 @@
         <v>46234</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -64756,7 +64756,7 @@
         <v>44970</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -64829,7 +64829,7 @@
         <v>46234</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -64907,7 +64907,7 @@
         <v>45210</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -64985,7 +64985,7 @@
         <v>46281</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -65058,7 +65058,7 @@
         <v>46281</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -65136,7 +65136,7 @@
         <v>46281</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -65214,7 +65214,7 @@
         <v>46281</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -65292,7 +65292,7 @@
         <v>46238</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -65370,7 +65370,7 @@
         <v>46238</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -65448,7 +65448,7 @@
         <v>45692</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -65521,7 +65521,7 @@
         <v>46239</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -65599,7 +65599,7 @@
         <v>45509</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -65672,7 +65672,7 @@
         <v>45537</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -65750,7 +65750,7 @@
         <v>46240</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -65823,7 +65823,7 @@
         <v>46240</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -65901,7 +65901,7 @@
         <v>44964</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -65979,7 +65979,7 @@
         <v>45856</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -66057,7 +66057,7 @@
         <v>46283</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -66135,7 +66135,7 @@
         <v>45539</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -66208,7 +66208,7 @@
         <v>45832</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -66281,7 +66281,7 @@
         <v>46283</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -66359,7 +66359,7 @@
         <v>46197</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -66432,7 +66432,7 @@
         <v>45429</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -66505,7 +66505,7 @@
         <v>44747</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -66578,7 +66578,7 @@
         <v>44706</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -66651,7 +66651,7 @@
         <v>46287</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -66729,7 +66729,7 @@
         <v>44880</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -66802,7 +66802,7 @@
         <v>44979</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -66880,7 +66880,7 @@
         <v>46202</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -66953,7 +66953,7 @@
         <v>46287</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -67031,7 +67031,7 @@
         <v>44931</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -67104,7 +67104,7 @@
         <v>46029</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -67182,7 +67182,7 @@
         <v>46248</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -67255,7 +67255,7 @@
         <v>45187</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -67333,7 +67333,7 @@
         <v>45591</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -67411,7 +67411,7 @@
         <v>46290</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -67489,7 +67489,7 @@
         <v>46289</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -67562,7 +67562,7 @@
         <v>45014</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -67635,7 +67635,7 @@
         <v>45544</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -67708,7 +67708,7 @@
         <v>45001</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -67781,7 +67781,7 @@
         <v>44964</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -67859,7 +67859,7 @@
         <v>46246</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -67932,7 +67932,7 @@
         <v>45105</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -68005,7 +68005,7 @@
         <v>44585</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -68078,7 +68078,7 @@
         <v>44847</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -68151,7 +68151,7 @@
         <v>45316</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -68224,7 +68224,7 @@
         <v>44552</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -68297,7 +68297,7 @@
         <v>44614</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -68370,7 +68370,7 @@
         <v>45470</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -68448,7 +68448,7 @@
         <v>45587</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -68521,7 +68521,7 @@
         <v>44566</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -68594,7 +68594,7 @@
         <v>45685</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -68667,7 +68667,7 @@
         <v>45543</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -68740,7 +68740,7 @@
         <v>45246</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -68813,7 +68813,7 @@
         <v>44841</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -68891,7 +68891,7 @@
         <v>45762</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -68964,7 +68964,7 @@
         <v>45476</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -69037,7 +69037,7 @@
         <v>45453</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -69110,7 +69110,7 @@
         <v>45099</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -69183,7 +69183,7 @@
         <v>45646</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -69256,7 +69256,7 @@
         <v>45770</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -69329,7 +69329,7 @@
         <v>45454</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -69402,7 +69402,7 @@
         <v>45770</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -69475,7 +69475,7 @@
         <v>45677</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -69553,7 +69553,7 @@
         <v>45425</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -69626,7 +69626,7 @@
         <v>45771</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -69699,7 +69699,7 @@
         <v>45125</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -69777,7 +69777,7 @@
         <v>45646</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -69850,7 +69850,7 @@
         <v>45766</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -69928,7 +69928,7 @@
         <v>45635</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -70001,7 +70001,7 @@
         <v>45099</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -70074,7 +70074,7 @@
         <v>44657</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -70147,7 +70147,7 @@
         <v>45264</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -70225,7 +70225,7 @@
         <v>45350</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -70298,7 +70298,7 @@
         <v>45379</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -70371,7 +70371,7 @@
         <v>44484</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -70449,7 +70449,7 @@
         <v>44486</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -70522,7 +70522,7 @@
         <v>45205</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -70595,7 +70595,7 @@
         <v>45035</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -70668,7 +70668,7 @@
         <v>45341</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -70746,7 +70746,7 @@
         <v>45653</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -70819,7 +70819,7 @@
         <v>45174</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -70892,7 +70892,7 @@
         <v>44833</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -70965,7 +70965,7 @@
         <v>45254</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -71038,7 +71038,7 @@
         <v>44935</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -71111,7 +71111,7 @@
         <v>45244</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -71189,7 +71189,7 @@
         <v>45653</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -71262,7 +71262,7 @@
         <v>45672</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -71335,7 +71335,7 @@
         <v>45770</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -71408,7 +71408,7 @@
         <v>45476</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -71481,7 +71481,7 @@
         <v>45764</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -71554,7 +71554,7 @@
         <v>45764</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -71627,7 +71627,7 @@
         <v>44881</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -71700,7 +71700,7 @@
         <v>45397</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -71773,7 +71773,7 @@
         <v>45397</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -71846,7 +71846,7 @@
         <v>45391</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -71919,7 +71919,7 @@
         <v>45778</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -71997,7 +71997,7 @@
         <v>45782</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -72070,7 +72070,7 @@
         <v>45786</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -72148,7 +72148,7 @@
         <v>45149</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -72221,7 +72221,7 @@
         <v>45379</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -72294,7 +72294,7 @@
         <v>45791</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -72372,7 +72372,7 @@
         <v>45376</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -72450,7 +72450,7 @@
         <v>45013</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -72523,7 +72523,7 @@
         <v>45376</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -72601,7 +72601,7 @@
         <v>45667</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -72674,7 +72674,7 @@
         <v>44945</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -72752,7 +72752,7 @@
         <v>45743</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -72825,7 +72825,7 @@
         <v>45743</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -72898,7 +72898,7 @@
         <v>45789</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -72976,7 +72976,7 @@
         <v>45792</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -73049,7 +73049,7 @@
         <v>45799</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -73127,7 +73127,7 @@
         <v>45799</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -73205,7 +73205,7 @@
         <v>45799</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -73283,7 +73283,7 @@
         <v>45810</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -73361,7 +73361,7 @@
         <v>45818</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -73439,7 +73439,7 @@
         <v>45840</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -73517,7 +73517,7 @@
         <v>46018</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -73590,7 +73590,7 @@
         <v>46147</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -73663,7 +73663,7 @@
         <v>46147</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -73736,7 +73736,7 @@
         <v>46147</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -73814,7 +73814,7 @@
         <v>46152</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -73887,7 +73887,7 @@
         <v>46152</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -73960,7 +73960,7 @@
         <v>46148</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>

--- a/Översikt BODEN.xlsx
+++ b/Översikt BODEN.xlsx
@@ -601,7 +601,7 @@
         <v>45152</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45506</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>45152</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45068</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>45075</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45152</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>44853</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>46168</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>46247</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>44964</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45105</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>45790</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>45212</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>45237</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>46149</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>44889</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45771</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>45684</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>44859</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44853</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>45295</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>45049</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>46210</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>44869</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>46195</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>45418</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>45463</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>44489</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>44795</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>45893</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>45912</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>45912</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>45428</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>45832</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>45512</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45964</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>46149</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>46209</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>45835</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>44904</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>45988</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>45980</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>46148</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>45307</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>46196</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>46261</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>45698</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>45933</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>46073</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>45952</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>45818</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>45981</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>45791</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>46181</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>46184</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>45077</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>44833</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>46205</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45155</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>46258</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>46217</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>46267</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>44755</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>46240</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>46286</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>44487</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>44648</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>44804</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>44796</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>44735</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>45341</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>44573</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>45517</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>45638</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>46066</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>46066</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>45803</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>45910</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>45910</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>45922</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>45701</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10093,7 +10093,7 @@
         <v>45714</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>45820</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>45594</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>45999</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>45645</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>45834</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>45526</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>46149</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>45875</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>46164</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11200,7 +11200,7 @@
         <v>46184</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
         <v>46184</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>45137</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
         <v>46205</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>46205</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>46205</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>46258</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>46261</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>46217</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>46261</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>46267</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>46225</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>46270</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>46286</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>44830</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>46245</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>46247</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>45301</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>44573</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>45072</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>44678</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>45376</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>44648</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>44840</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>45313</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>45763</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>46003</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>44529</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>45901</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>45905</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>45406</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>46048</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>44529</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>45884</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>45936</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>45448</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>45944</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15287,7 +15287,7 @@
         <v>45947</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15397,7 +15397,7 @@
         <v>45950</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>45949</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         <v>45952</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>44648</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         <v>45958</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>45960</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>46100</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>45975</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>45994</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>45999</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>45538</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>46147</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>45513</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>44925</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>46168</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>46178</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>46178</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17243,7 +17243,7 @@
         <v>45211</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17353,7 +17353,7 @@
         <v>46178</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>46183</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>46184</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>44642</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         <v>46205</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17906,7 +17906,7 @@
         <v>45559</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>46261</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>46261</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18239,7 +18239,7 @@
         <v>46261</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>46261</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>46272</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>46272</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>46267</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>46236</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>46240</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>46282</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>46241</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>45966</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>44692</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19442,7 +19442,7 @@
         <v>46134</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>46251</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         <v>46255</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19767,7 +19767,7 @@
         <v>46037</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>44944</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
         <v>45418</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20101,7 +20101,7 @@
         <v>45028</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45643</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45799</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>45901</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>45952</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
         <v>44677</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>44509</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>44577</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>44489</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>44671</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>44659</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>44852</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>44815</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>44648</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>44648</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>44617</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>44865</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44609</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>44609</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44671</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>44887</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>44721</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>44543</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>44530</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44648</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44473</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22228,7 +22228,7 @@
         <v>44734</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>44566</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>44566</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22447,7 +22447,7 @@
         <v>44600</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>44749</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>44722</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>44530</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44480</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>44565</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>44573</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>44566</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>44617</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23114,7 +23114,7 @@
         <v>44820</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23192,7 +23192,7 @@
         <v>44625</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23265,7 +23265,7 @@
         <v>44596</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>44831</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>44799</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>44799</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         <v>44743</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>44480</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>44529</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23796,7 +23796,7 @@
         <v>44565</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>44635</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>44797</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>44796</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>44796</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>44484</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>44489</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24317,7 +24317,7 @@
         <v>44795</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24395,7 +24395,7 @@
         <v>44812</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44671</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>45310</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>44552</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>45411</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>44833</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24838,7 +24838,7 @@
         <v>45022</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24911,7 +24911,7 @@
         <v>44609</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>45238</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>44880</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
         <v>44881</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25203,7 +25203,7 @@
         <v>45762</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25276,7 +25276,7 @@
         <v>44783</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>45125</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25427,7 +25427,7 @@
         <v>45635</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>44489</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>45600</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>45600</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>45419</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>45210</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25870,7 +25870,7 @@
         <v>45161</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25948,7 +25948,7 @@
         <v>45537</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>45763</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>45149</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>45254</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>45786</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>44881</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>46001</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26469,7 +26469,7 @@
         <v>45237</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26542,7 +26542,7 @@
         <v>45345</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>46003</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>46003</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>46001</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26834,7 +26834,7 @@
         <v>45643</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>45884</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>45512</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>44558</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>45766</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>46009</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>46009</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>46008</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>45994</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>45539</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>46009</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>45902</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>46012</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27803,7 +27803,7 @@
         <v>46012</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>44529</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         <v>45791</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>45379</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>45764</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28173,7 +28173,7 @@
         <v>45649</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28246,7 +28246,7 @@
         <v>46020</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28319,7 +28319,7 @@
         <v>45891</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28392,7 +28392,7 @@
         <v>46066</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44970</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28538,7 +28538,7 @@
         <v>46066</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28611,7 +28611,7 @@
         <v>45764</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28684,7 +28684,7 @@
         <v>46029</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>45897</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28830,7 +28830,7 @@
         <v>45897</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>46030</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         <v>46030</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>45285</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29132,7 +29132,7 @@
         <v>46030</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29210,7 +29210,7 @@
         <v>45604</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>45901</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29361,7 +29361,7 @@
         <v>46020</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>45397</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>45397</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>45902</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29658,7 +29658,7 @@
         <v>45764</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29731,7 +29731,7 @@
         <v>44983</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29804,7 +29804,7 @@
         <v>46042</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -29877,7 +29877,7 @@
         <v>45907</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>46042</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>45793</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>45911</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>45910</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30257,7 +30257,7 @@
         <v>45590</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30330,7 +30330,7 @@
         <v>45590</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>44474</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30476,7 +30476,7 @@
         <v>45910</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>45758</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30627,7 +30627,7 @@
         <v>45797</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>45912</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>45915</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30861,7 +30861,7 @@
         <v>45915</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30934,7 +30934,7 @@
         <v>45912</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>45912</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>45915</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>45799</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31236,7 +31236,7 @@
         <v>46048</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>45798</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>45798</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31465,7 +31465,7 @@
         <v>44862</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31538,7 +31538,7 @@
         <v>45798</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31616,7 +31616,7 @@
         <v>45803</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>46050</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>45919</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>45919</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31918,7 +31918,7 @@
         <v>45608</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>45608</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>45590</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>45260</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>45922</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>45527</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>45922</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>45922</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>44484</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>46052</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45264</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>45264</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32809,7 +32809,7 @@
         <v>45925</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>45925</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>46056</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>46056</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>45924</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>45926</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33252,7 +33252,7 @@
         <v>45926</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33325,7 +33325,7 @@
         <v>45926</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>46057</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>45429</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>46059</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>45516</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33695,7 +33695,7 @@
         <v>45516</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33773,7 +33773,7 @@
         <v>45464</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>44935</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>45931</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -34002,7 +34002,7 @@
         <v>46058</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34075,7 +34075,7 @@
         <v>45930</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>45589</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34231,7 +34231,7 @@
         <v>45930</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34309,7 +34309,7 @@
         <v>46062</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34382,7 +34382,7 @@
         <v>46063</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34455,7 +34455,7 @@
         <v>46063</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34528,7 +34528,7 @@
         <v>45933</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>45906</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>46065</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34757,7 +34757,7 @@
         <v>45543</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>45933</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>45933</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34986,7 +34986,7 @@
         <v>45709</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>45645</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35137,7 +35137,7 @@
         <v>45560</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35215,7 +35215,7 @@
         <v>45246</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>45938</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35366,7 +35366,7 @@
         <v>45937</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>45938</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35512,7 +35512,7 @@
         <v>45938</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>45939</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>45763</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>45194</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>45943</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35892,7 +35892,7 @@
         <v>45244</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>45945</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>45945</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36121,7 +36121,7 @@
         <v>45748</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36194,7 +36194,7 @@
         <v>45944</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>45944</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36345,7 +36345,7 @@
         <v>46078</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36418,7 +36418,7 @@
         <v>46076</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>45944</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>45944</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36642,7 +36642,7 @@
         <v>45945</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36715,7 +36715,7 @@
         <v>46076</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>45944</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36866,7 +36866,7 @@
         <v>45546</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36944,7 +36944,7 @@
         <v>46076</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -37017,7 +37017,7 @@
         <v>45110</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>45947</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>45243</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>45950</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>45813</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>46084</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37465,7 +37465,7 @@
         <v>46084</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37538,7 +37538,7 @@
         <v>44490</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>45953</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -37694,7 +37694,7 @@
         <v>45103</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37767,7 +37767,7 @@
         <v>45953</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37840,7 +37840,7 @@
         <v>46084</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>45953</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>45070</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -38064,7 +38064,7 @@
         <v>46084</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38137,7 +38137,7 @@
         <v>46084</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>46086</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>45950</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38356,7 +38356,7 @@
         <v>45955</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>45955</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>46087</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>45960</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>45813</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38736,7 +38736,7 @@
         <v>45672</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38809,7 +38809,7 @@
         <v>45764</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38882,7 +38882,7 @@
         <v>45961</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38955,7 +38955,7 @@
         <v>45316</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39028,7 +39028,7 @@
         <v>45965</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -39101,7 +39101,7 @@
         <v>45965</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39174,7 +39174,7 @@
         <v>45254</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39247,7 +39247,7 @@
         <v>45965</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>45965</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>45481</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39471,7 +39471,7 @@
         <v>45964</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         <v>45463</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39617,7 +39617,7 @@
         <v>45966</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -39690,7 +39690,7 @@
         <v>46097</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39768,7 +39768,7 @@
         <v>45971</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>45922</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45667</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39987,7 +39987,7 @@
         <v>46100</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -40060,7 +40060,7 @@
         <v>45972</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40133,7 +40133,7 @@
         <v>45761</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>46099</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>45766</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>45975</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>45975</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40523,7 +40523,7 @@
         <v>45975</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>46104</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>44628</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>45161</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40825,7 +40825,7 @@
         <v>45161</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40903,7 +40903,7 @@
         <v>45818</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>45427</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41054,7 +41054,7 @@
         <v>45978</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>45718</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41200,7 +41200,7 @@
         <v>46105</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>45978</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41351,7 +41351,7 @@
         <v>45246</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>45818</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>45981</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
         <v>45981</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>45356</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41731,7 +41731,7 @@
         <v>45358</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45574</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>45818</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41960,7 +41960,7 @@
         <v>45102</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42033,7 +42033,7 @@
         <v>45984</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42106,7 +42106,7 @@
         <v>45985</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42179,7 +42179,7 @@
         <v>45316</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>45770</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         <v>45985</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>44529</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>44648</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42554,7 +42554,7 @@
         <v>45212</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>45986</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -42700,7 +42700,7 @@
         <v>45988</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>45988</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42846,7 +42846,7 @@
         <v>45980</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42919,7 +42919,7 @@
         <v>45476</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42992,7 +42992,7 @@
         <v>44474</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>44566</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -43138,7 +43138,7 @@
         <v>45551</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>46122</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43294,7 +43294,7 @@
         <v>46122</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43367,7 +43367,7 @@
         <v>46126</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43440,7 +43440,7 @@
         <v>45995</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>45995</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43586,7 +43586,7 @@
         <v>45994</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43659,7 +43659,7 @@
         <v>45994</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43732,7 +43732,7 @@
         <v>46126</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43805,7 +43805,7 @@
         <v>45995</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43878,7 +43878,7 @@
         <v>45995</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43951,7 +43951,7 @@
         <v>45995</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44024,7 +44024,7 @@
         <v>44477</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44097,7 +44097,7 @@
         <v>45994</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45994</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44243,7 +44243,7 @@
         <v>45994</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44316,7 +44316,7 @@
         <v>46127</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44389,7 +44389,7 @@
         <v>45996</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44462,7 +44462,7 @@
         <v>45132</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44535,7 +44535,7 @@
         <v>45826</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44613,7 +44613,7 @@
         <v>45649</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -44686,7 +44686,7 @@
         <v>45649</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44759,7 +44759,7 @@
         <v>45999</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>45906</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44905,7 +44905,7 @@
         <v>46000</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>46132</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>46001</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45129,7 +45129,7 @@
         <v>46132</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45202,7 +45202,7 @@
         <v>46132</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>46132</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>45105</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45431,7 +45431,7 @@
         <v>46007</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>45201</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45577,7 +45577,7 @@
         <v>45099</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>44994</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45723,7 +45723,7 @@
         <v>44486</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45796,7 +45796,7 @@
         <v>45728</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>45833</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45833</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46030,7 +46030,7 @@
         <v>45835</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>45583</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46186,7 +46186,7 @@
         <v>46136</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46264,7 +46264,7 @@
         <v>45803</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46337,7 +46337,7 @@
         <v>46076</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46410,7 +46410,7 @@
         <v>45341</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46488,7 +46488,7 @@
         <v>45561</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46561,7 +46561,7 @@
         <v>46003</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>44484</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46707,7 +46707,7 @@
         <v>46029</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>45257</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46853,7 +46853,7 @@
         <v>45840</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>44522</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -47004,7 +47004,7 @@
         <v>45840</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -47082,7 +47082,7 @@
         <v>45747</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -47155,7 +47155,7 @@
         <v>45596</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47228,7 +47228,7 @@
         <v>45587</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47301,7 +47301,7 @@
         <v>45843</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47379,7 +47379,7 @@
         <v>45999</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47452,7 +47452,7 @@
         <v>46003</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47530,7 +47530,7 @@
         <v>45685</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>45408</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>44994</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>45944</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47822,7 +47822,7 @@
         <v>45603</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>45860</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47973,7 +47973,7 @@
         <v>45512</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>44889</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -48119,7 +48119,7 @@
         <v>45406</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -48192,7 +48192,7 @@
         <v>45771</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>44881</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48343,7 +48343,7 @@
         <v>45935</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -48416,7 +48416,7 @@
         <v>45587</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -48489,7 +48489,7 @@
         <v>45248</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -48562,7 +48562,7 @@
         <v>45796</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>45674</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -48713,7 +48713,7 @@
         <v>45839</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48786,7 +48786,7 @@
         <v>45596</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48859,7 +48859,7 @@
         <v>45691</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48937,7 +48937,7 @@
         <v>44648</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -49015,7 +49015,7 @@
         <v>44565</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -49088,7 +49088,7 @@
         <v>46029</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -49161,7 +49161,7 @@
         <v>45863</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -49234,7 +49234,7 @@
         <v>45649</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -49307,7 +49307,7 @@
         <v>45586</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>45574</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -49463,7 +49463,7 @@
         <v>45301</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>45761</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -49614,7 +49614,7 @@
         <v>45750</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -49692,7 +49692,7 @@
         <v>46084</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>46076</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49838,7 +49838,7 @@
         <v>45832</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49911,7 +49911,7 @@
         <v>45456</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49984,7 +49984,7 @@
         <v>45818</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -50057,7 +50057,7 @@
         <v>45645</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -50135,7 +50135,7 @@
         <v>45264</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>45369</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -50281,7 +50281,7 @@
         <v>45692</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -50354,7 +50354,7 @@
         <v>46147</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45893</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -50505,7 +50505,7 @@
         <v>45841</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -50578,7 +50578,7 @@
         <v>46148</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -50656,7 +50656,7 @@
         <v>44903</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45770</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -50802,7 +50802,7 @@
         <v>45838</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50875,7 +50875,7 @@
         <v>46149</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50948,7 +50948,7 @@
         <v>45672</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>46149</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -51094,7 +51094,7 @@
         <v>46150</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -51167,7 +51167,7 @@
         <v>45590</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -51245,7 +51245,7 @@
         <v>45591</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -51323,7 +51323,7 @@
         <v>45591</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -51401,7 +51401,7 @@
         <v>46150</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -51474,7 +51474,7 @@
         <v>45425</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>46150</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -51620,7 +51620,7 @@
         <v>45408</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -51693,7 +51693,7 @@
         <v>46154</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -51766,7 +51766,7 @@
         <v>45646</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51839,7 +51839,7 @@
         <v>44657</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51912,7 +51912,7 @@
         <v>46155</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51985,7 +51985,7 @@
         <v>45639</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -52058,7 +52058,7 @@
         <v>46154</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -52136,7 +52136,7 @@
         <v>45988</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>45427</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -52282,7 +52282,7 @@
         <v>45440</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -52355,7 +52355,7 @@
         <v>44847</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -52428,7 +52428,7 @@
         <v>45210</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -52506,7 +52506,7 @@
         <v>45818</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -52584,7 +52584,7 @@
         <v>45744</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -52657,7 +52657,7 @@
         <v>45691</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -52730,7 +52730,7 @@
         <v>44573</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52808,7 +52808,7 @@
         <v>45868</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52886,7 +52886,7 @@
         <v>44859</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>45544</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -53037,7 +53037,7 @@
         <v>45875</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -53110,7 +53110,7 @@
         <v>45314</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -53183,7 +53183,7 @@
         <v>45429</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -53256,7 +53256,7 @@
         <v>44963</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -53329,7 +53329,7 @@
         <v>45674</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -53402,7 +53402,7 @@
         <v>45894</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -53480,7 +53480,7 @@
         <v>45877</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -53558,7 +53558,7 @@
         <v>45505</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -53636,7 +53636,7 @@
         <v>46164</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53714,7 +53714,7 @@
         <v>46164</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -53792,7 +53792,7 @@
         <v>46164</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53870,7 +53870,7 @@
         <v>44979</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53948,7 +53948,7 @@
         <v>46164</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -54026,7 +54026,7 @@
         <v>45880</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -54104,7 +54104,7 @@
         <v>46168</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -54177,7 +54177,7 @@
         <v>46168</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -54250,7 +54250,7 @@
         <v>45470</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -54328,7 +54328,7 @@
         <v>46168</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -54401,7 +54401,7 @@
         <v>46168</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>46168</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -54547,7 +54547,7 @@
         <v>46172</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -54625,7 +54625,7 @@
         <v>46171</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -54698,7 +54698,7 @@
         <v>45881</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -54771,7 +54771,7 @@
         <v>46174</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54844,7 +54844,7 @@
         <v>44529</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54917,7 +54917,7 @@
         <v>45882</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54990,7 +54990,7 @@
         <v>45882</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -55063,7 +55063,7 @@
         <v>45574</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -55141,7 +55141,7 @@
         <v>45764</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -55214,7 +55214,7 @@
         <v>46175</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -55287,7 +55287,7 @@
         <v>45884</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -55365,7 +55365,7 @@
         <v>46178</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -55443,7 +55443,7 @@
         <v>45446</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -55516,7 +55516,7 @@
         <v>45356</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -55589,7 +55589,7 @@
         <v>46177</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -55667,7 +55667,7 @@
         <v>45649</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55740,7 +55740,7 @@
         <v>45764</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -55813,7 +55813,7 @@
         <v>46177</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55891,7 +55891,7 @@
         <v>46170</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -55969,7 +55969,7 @@
         <v>46181</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -56047,7 +56047,7 @@
         <v>46182</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -56125,7 +56125,7 @@
         <v>45014</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -56198,7 +56198,7 @@
         <v>46183</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -56271,7 +56271,7 @@
         <v>46184</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -56349,7 +56349,7 @@
         <v>46184</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -56447,7 +56447,7 @@
         <v>46183</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -56525,7 +56525,7 @@
         <v>46184</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -56603,7 +56603,7 @@
         <v>44964</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -56681,7 +56681,7 @@
         <v>45770</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -56754,7 +56754,7 @@
         <v>45254</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>46185</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56900,7 +56900,7 @@
         <v>44796</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -56973,7 +56973,7 @@
         <v>45694</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -57051,7 +57051,7 @@
         <v>45523</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -57129,7 +57129,7 @@
         <v>45149</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -57202,7 +57202,7 @@
         <v>46191</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -57275,7 +57275,7 @@
         <v>45054</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -57348,7 +57348,7 @@
         <v>45429</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -57421,7 +57421,7 @@
         <v>46196</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -57494,7 +57494,7 @@
         <v>45085</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -57567,7 +57567,7 @@
         <v>45643</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -57640,7 +57640,7 @@
         <v>46197</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -57718,7 +57718,7 @@
         <v>45281</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -57796,7 +57796,7 @@
         <v>46198</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57869,7 +57869,7 @@
         <v>46197</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57942,7 +57942,7 @@
         <v>46197</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -58015,7 +58015,7 @@
         <v>46197</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -58088,7 +58088,7 @@
         <v>46202</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -58166,7 +58166,7 @@
         <v>46202</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -58244,7 +58244,7 @@
         <v>44903</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -58317,7 +58317,7 @@
         <v>46202</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -58395,7 +58395,7 @@
         <v>45210</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -58473,7 +58473,7 @@
         <v>46203</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -58546,7 +58546,7 @@
         <v>46204</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -58619,7 +58619,7 @@
         <v>46204</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -58692,7 +58692,7 @@
         <v>46204</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58765,7 +58765,7 @@
         <v>44524</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -58838,7 +58838,7 @@
         <v>45212</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58916,7 +58916,7 @@
         <v>46206</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58994,7 +58994,7 @@
         <v>46206</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -59072,7 +59072,7 @@
         <v>44706</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -59145,7 +59145,7 @@
         <v>46208</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -59218,7 +59218,7 @@
         <v>46206</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -59296,7 +59296,7 @@
         <v>44747</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -59369,7 +59369,7 @@
         <v>46211</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -59442,7 +59442,7 @@
         <v>44673</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59515,7 +59515,7 @@
         <v>46209</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -59593,7 +59593,7 @@
         <v>46209</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -59671,7 +59671,7 @@
         <v>46209</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59749,7 +59749,7 @@
         <v>45548</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -59822,7 +59822,7 @@
         <v>44657</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59895,7 +59895,7 @@
         <v>44657</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59968,7 +59968,7 @@
         <v>46259</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -60046,7 +60046,7 @@
         <v>46259</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -60124,7 +60124,7 @@
         <v>44966</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -60202,7 +60202,7 @@
         <v>46259</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -60280,7 +60280,7 @@
         <v>46261</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -60358,7 +60358,7 @@
         <v>45924</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -60431,7 +60431,7 @@
         <v>46261</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -60504,7 +60504,7 @@
         <v>46261</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -60577,7 +60577,7 @@
         <v>46261</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -60650,7 +60650,7 @@
         <v>46217</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60728,7 +60728,7 @@
         <v>45894</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -60801,7 +60801,7 @@
         <v>46261</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60894,7 +60894,7 @@
         <v>45593</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60972,7 +60972,7 @@
         <v>46217</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -61050,7 +61050,7 @@
         <v>46217</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -61128,7 +61128,7 @@
         <v>46217</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -61206,7 +61206,7 @@
         <v>46168</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -61279,7 +61279,7 @@
         <v>45429</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -61352,7 +61352,7 @@
         <v>45429</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -61425,7 +61425,7 @@
         <v>46266</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -61503,7 +61503,7 @@
         <v>45085</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -61576,7 +61576,7 @@
         <v>46267</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -61649,7 +61649,7 @@
         <v>45483</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -61722,7 +61722,7 @@
         <v>45153</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -61795,7 +61795,7 @@
         <v>45509</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -61868,7 +61868,7 @@
         <v>46269</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -61946,7 +61946,7 @@
         <v>46268</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -62019,7 +62019,7 @@
         <v>46225</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -62097,7 +62097,7 @@
         <v>46268</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -62175,7 +62175,7 @@
         <v>46029</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -62248,7 +62248,7 @@
         <v>45256</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -62321,7 +62321,7 @@
         <v>45562</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -62399,7 +62399,7 @@
         <v>45653</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -62472,7 +62472,7 @@
         <v>46272</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -62550,7 +62550,7 @@
         <v>46273</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -62628,7 +62628,7 @@
         <v>46268</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -62706,7 +62706,7 @@
         <v>45247</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -62779,7 +62779,7 @@
         <v>46270</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -62852,7 +62852,7 @@
         <v>46274</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -62925,7 +62925,7 @@
         <v>46274</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -62998,7 +62998,7 @@
         <v>46275</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -63071,7 +63071,7 @@
         <v>46275</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -63144,7 +63144,7 @@
         <v>45499</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -63217,7 +63217,7 @@
         <v>46274</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -63290,7 +63290,7 @@
         <v>46274</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -63368,7 +63368,7 @@
         <v>46275</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -63446,7 +63446,7 @@
         <v>46275</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -63519,7 +63519,7 @@
         <v>46275</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -63592,7 +63592,7 @@
         <v>46234</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -63670,7 +63670,7 @@
         <v>46276</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -63743,7 +63743,7 @@
         <v>46276</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -63816,7 +63816,7 @@
         <v>46234</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -63894,7 +63894,7 @@
         <v>46234</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -63972,7 +63972,7 @@
         <v>45156</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -64045,7 +64045,7 @@
         <v>46281</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -64123,7 +64123,7 @@
         <v>46281</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -64201,7 +64201,7 @@
         <v>44642</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -64279,7 +64279,7 @@
         <v>45070</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -64352,7 +64352,7 @@
         <v>46238</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -64430,7 +64430,7 @@
         <v>44901</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -64503,7 +64503,7 @@
         <v>46281</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -64576,7 +64576,7 @@
         <v>46238</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -64654,7 +64654,7 @@
         <v>46281</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -64732,7 +64732,7 @@
         <v>45195</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -64810,7 +64810,7 @@
         <v>46283</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -64888,7 +64888,7 @@
         <v>45649</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -64961,7 +64961,7 @@
         <v>46239</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -65039,7 +65039,7 @@
         <v>46240</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -65112,7 +65112,7 @@
         <v>45589</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -65190,7 +65190,7 @@
         <v>45589</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -65268,7 +65268,7 @@
         <v>46240</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -65346,7 +65346,7 @@
         <v>46283</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -65424,7 +65424,7 @@
         <v>45460</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -65502,7 +65502,7 @@
         <v>45832</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -65575,7 +65575,7 @@
         <v>45350</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -65648,7 +65648,7 @@
         <v>46287</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -65726,7 +65726,7 @@
         <v>46202</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -65799,7 +65799,7 @@
         <v>44732</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -65872,7 +65872,7 @@
         <v>45856</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -65950,7 +65950,7 @@
         <v>45677</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -66028,7 +66028,7 @@
         <v>44908</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -66101,7 +66101,7 @@
         <v>45216</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -66179,7 +66179,7 @@
         <v>46197</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -66252,7 +66252,7 @@
         <v>44726</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -66325,7 +66325,7 @@
         <v>44566</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -66398,7 +66398,7 @@
         <v>46287</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -66476,7 +66476,7 @@
         <v>44841</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -66554,7 +66554,7 @@
         <v>46246</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -66627,7 +66627,7 @@
         <v>45356</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -66700,7 +66700,7 @@
         <v>46289</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -66773,7 +66773,7 @@
         <v>46293</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -66851,7 +66851,7 @@
         <v>44734</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -66924,7 +66924,7 @@
         <v>45653</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -66997,7 +66997,7 @@
         <v>45770</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -67070,7 +67070,7 @@
         <v>45544</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -67143,7 +67143,7 @@
         <v>46290</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -67221,7 +67221,7 @@
         <v>46293</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -67294,7 +67294,7 @@
         <v>44795</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -67367,7 +67367,7 @@
         <v>45161</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -67440,7 +67440,7 @@
         <v>46293</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -67518,7 +67518,7 @@
         <v>46248</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -67591,7 +67591,7 @@
         <v>46293</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -67669,7 +67669,7 @@
         <v>46252</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -67747,7 +67747,7 @@
         <v>45194</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -67825,7 +67825,7 @@
         <v>44908</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -67898,7 +67898,7 @@
         <v>45358</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -67971,7 +67971,7 @@
         <v>46251</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -68049,7 +68049,7 @@
         <v>45680</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -68127,7 +68127,7 @@
         <v>45187</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -68205,7 +68205,7 @@
         <v>46294</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -68283,7 +68283,7 @@
         <v>44887</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -68361,7 +68361,7 @@
         <v>45166</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -68439,7 +68439,7 @@
         <v>45653</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -68512,7 +68512,7 @@
         <v>45174</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -68585,7 +68585,7 @@
         <v>45323</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -68658,7 +68658,7 @@
         <v>46253</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -68731,7 +68731,7 @@
         <v>46251</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -68804,7 +68804,7 @@
         <v>44931</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -68877,7 +68877,7 @@
         <v>45001</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -68950,7 +68950,7 @@
         <v>46254</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -69023,7 +69023,7 @@
         <v>46254</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -69096,7 +69096,7 @@
         <v>45772</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -69169,7 +69169,7 @@
         <v>45770</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -69242,7 +69242,7 @@
         <v>45813</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -69320,7 +69320,7 @@
         <v>46297</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -69398,7 +69398,7 @@
         <v>44964</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -69476,7 +69476,7 @@
         <v>46254</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -69554,7 +69554,7 @@
         <v>46296</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -69632,7 +69632,7 @@
         <v>46296</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -69710,7 +69710,7 @@
         <v>46029</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -69788,7 +69788,7 @@
         <v>46255</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -69866,7 +69866,7 @@
         <v>45035</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -69939,7 +69939,7 @@
         <v>45476</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -70012,7 +70012,7 @@
         <v>45093</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -70090,7 +70090,7 @@
         <v>44883</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -70168,7 +70168,7 @@
         <v>45529</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -70241,7 +70241,7 @@
         <v>45099</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -70314,7 +70314,7 @@
         <v>44484</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -70387,7 +70387,7 @@
         <v>45454</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -70460,7 +70460,7 @@
         <v>44614</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -70533,7 +70533,7 @@
         <v>45079</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -70606,7 +70606,7 @@
         <v>45762</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -70679,7 +70679,7 @@
         <v>45646</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -70752,7 +70752,7 @@
         <v>45205</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -70825,7 +70825,7 @@
         <v>45233</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -70903,7 +70903,7 @@
         <v>45379</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -70976,7 +70976,7 @@
         <v>45773</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -71054,7 +71054,7 @@
         <v>44994</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -71127,7 +71127,7 @@
         <v>44568</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -71200,7 +71200,7 @@
         <v>45572</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -71278,7 +71278,7 @@
         <v>45764</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -71351,7 +71351,7 @@
         <v>45764</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -71424,7 +71424,7 @@
         <v>45618</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -71502,7 +71502,7 @@
         <v>45099</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -71575,7 +71575,7 @@
         <v>44812</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -71648,7 +71648,7 @@
         <v>44823</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -71726,7 +71726,7 @@
         <v>45625</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -71804,7 +71804,7 @@
         <v>44856</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -71877,7 +71877,7 @@
         <v>45013</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -71950,7 +71950,7 @@
         <v>44585</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -72023,7 +72023,7 @@
         <v>45204</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -72096,7 +72096,7 @@
         <v>45687</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -72169,7 +72169,7 @@
         <v>44935</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -72242,7 +72242,7 @@
         <v>45453</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -72315,7 +72315,7 @@
         <v>45646</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -72388,7 +72388,7 @@
         <v>45478</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -72461,7 +72461,7 @@
         <v>45391</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -72534,7 +72534,7 @@
         <v>45778</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -72612,7 +72612,7 @@
         <v>45782</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -72685,7 +72685,7 @@
         <v>45376</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -72763,7 +72763,7 @@
         <v>45013</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -72836,7 +72836,7 @@
         <v>45376</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -72914,7 +72914,7 @@
         <v>45667</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -72987,7 +72987,7 @@
         <v>44945</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -73065,7 +73065,7 @@
         <v>45743</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -73138,7 +73138,7 @@
         <v>45743</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -73211,7 +73211,7 @@
         <v>45789</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -73289,7 +73289,7 @@
         <v>45792</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -73362,7 +73362,7 @@
         <v>45799</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -73440,7 +73440,7 @@
         <v>45799</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -73518,7 +73518,7 @@
         <v>45799</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -73596,7 +73596,7 @@
         <v>45810</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -73674,7 +73674,7 @@
         <v>45818</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -73752,7 +73752,7 @@
         <v>45840</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -73830,7 +73830,7 @@
         <v>46018</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -73903,7 +73903,7 @@
         <v>46147</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -73976,7 +73976,7 @@
         <v>46147</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -74049,7 +74049,7 @@
         <v>46147</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -74127,7 +74127,7 @@
         <v>46152</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -74200,7 +74200,7 @@
         <v>46152</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -74273,7 +74273,7 @@
         <v>46148</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>

--- a/Översikt BODEN.xlsx
+++ b/Översikt BODEN.xlsx
@@ -601,7 +601,7 @@
         <v>45152</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45506</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>45152</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45068</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>45075</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45152</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>44853</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>46168</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>46247</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>44964</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45105</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>45790</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>45212</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>45237</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>46149</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>44889</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45771</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>45684</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>44859</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44853</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>45295</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>45049</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>46210</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>44869</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>46195</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>45418</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>45463</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>44489</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>44795</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>45893</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>45912</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>45912</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>45428</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>45832</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>45512</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45964</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>46149</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>46209</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>45835</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>44904</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>45988</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>45980</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>46148</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>45307</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>46196</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>46261</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>45698</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>45933</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>46073</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>45952</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>45818</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>45981</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>45791</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>46181</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>46184</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>45077</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>44833</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>46205</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45155</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>46258</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>46217</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>46267</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>44755</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>46240</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>46286</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>44487</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>44648</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>44804</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>44796</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>44735</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>45341</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>44573</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>45517</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>45638</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>46066</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>46066</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>45803</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>45910</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>45910</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>45922</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>45701</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10093,7 +10093,7 @@
         <v>45714</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>45820</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>45594</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>45999</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>45645</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>45834</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>45526</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>46149</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>45875</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>46164</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11200,7 +11200,7 @@
         <v>46184</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
         <v>46184</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>45137</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
         <v>46205</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>46205</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>46205</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>46258</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>46261</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>46217</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>46261</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>46267</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>46225</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>46270</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>46286</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>44830</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>46245</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>46247</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>45301</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>44573</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>45072</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>44678</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>45376</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>44648</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>44840</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>45313</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>45763</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>46003</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>44529</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>45901</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>45905</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>45406</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>46048</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>44529</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>45884</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>45936</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>45448</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>45944</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15287,7 +15287,7 @@
         <v>45947</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15397,7 +15397,7 @@
         <v>45950</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>45949</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         <v>45952</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>44648</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         <v>45958</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>45960</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>46100</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>45975</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>45994</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>45999</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>45538</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>46147</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>45513</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>44925</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>46168</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>46178</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>46178</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17243,7 +17243,7 @@
         <v>45211</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17353,7 +17353,7 @@
         <v>46178</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>46183</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>46184</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>44642</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         <v>46205</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17906,7 +17906,7 @@
         <v>45559</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>46261</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>46261</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18239,7 +18239,7 @@
         <v>46261</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>46261</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>46272</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>46272</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>46267</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>46236</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>46240</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>46282</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>46241</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>45966</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>44692</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19442,7 +19442,7 @@
         <v>46134</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>46251</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         <v>46255</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19767,7 +19767,7 @@
         <v>46037</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>44944</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
         <v>45418</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20101,7 +20101,7 @@
         <v>45028</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45643</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45799</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>45901</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>45952</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
         <v>44677</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>44509</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>44577</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>44489</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>44671</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>44659</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>44852</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>44815</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>44648</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>44648</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>44617</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>44865</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44609</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>44609</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44671</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>44887</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>44721</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>44543</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>44530</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44648</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44473</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22228,7 +22228,7 @@
         <v>44734</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>44566</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>44566</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22447,7 +22447,7 @@
         <v>44600</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>44749</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>44722</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>44530</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44480</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>44565</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>44573</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>44566</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>44617</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23114,7 +23114,7 @@
         <v>44820</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23192,7 +23192,7 @@
         <v>44625</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23265,7 +23265,7 @@
         <v>44596</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>44831</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>44799</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>44799</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         <v>44743</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>44480</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>44529</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23796,7 +23796,7 @@
         <v>44565</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>44635</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>44797</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>44796</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>44796</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>44484</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>44489</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24317,7 +24317,7 @@
         <v>44795</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24395,7 +24395,7 @@
         <v>44812</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44671</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>45310</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>44552</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>45411</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>44833</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24838,7 +24838,7 @@
         <v>45022</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24911,7 +24911,7 @@
         <v>44609</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>45238</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>44880</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
         <v>44881</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25203,7 +25203,7 @@
         <v>45762</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25276,7 +25276,7 @@
         <v>44783</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>45125</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25427,7 +25427,7 @@
         <v>45635</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>44489</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>45600</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>45600</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>45419</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>45210</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25870,7 +25870,7 @@
         <v>45161</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25948,7 +25948,7 @@
         <v>45537</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>45763</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>45149</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>45254</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>45786</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>44881</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>46001</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26469,7 +26469,7 @@
         <v>45237</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26542,7 +26542,7 @@
         <v>45345</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>46003</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>46003</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>46001</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26834,7 +26834,7 @@
         <v>45643</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>45884</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>45512</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>44558</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>45766</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>46009</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>46009</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>46008</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>45994</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>45539</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>46009</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>45902</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>46012</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27803,7 +27803,7 @@
         <v>46012</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>44529</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         <v>45791</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>45379</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>45764</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28173,7 +28173,7 @@
         <v>45649</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28246,7 +28246,7 @@
         <v>46020</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28319,7 +28319,7 @@
         <v>45891</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28392,7 +28392,7 @@
         <v>46066</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44970</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28538,7 +28538,7 @@
         <v>46066</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28611,7 +28611,7 @@
         <v>45764</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28684,7 +28684,7 @@
         <v>46029</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>45897</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28830,7 +28830,7 @@
         <v>45897</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>46030</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         <v>46030</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>45285</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29132,7 +29132,7 @@
         <v>46030</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29210,7 +29210,7 @@
         <v>45604</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>45901</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29361,7 +29361,7 @@
         <v>46020</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>45397</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>45397</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>45902</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29658,7 +29658,7 @@
         <v>45764</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29731,7 +29731,7 @@
         <v>44983</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29804,7 +29804,7 @@
         <v>46042</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -29877,7 +29877,7 @@
         <v>45907</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>46042</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>45793</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>45911</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>45910</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30257,7 +30257,7 @@
         <v>45590</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30330,7 +30330,7 @@
         <v>45590</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>44474</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30476,7 +30476,7 @@
         <v>45910</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>45758</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30627,7 +30627,7 @@
         <v>45797</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>45912</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>45915</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30861,7 +30861,7 @@
         <v>45915</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30934,7 +30934,7 @@
         <v>45912</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>45912</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>45915</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>45799</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31236,7 +31236,7 @@
         <v>46048</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>45798</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>45798</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31465,7 +31465,7 @@
         <v>44862</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31538,7 +31538,7 @@
         <v>45798</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31616,7 +31616,7 @@
         <v>45803</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>46050</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>45919</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>45919</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31918,7 +31918,7 @@
         <v>45608</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>45608</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>45590</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>45260</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>45922</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>45527</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>45922</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>45922</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>44484</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>46052</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45264</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>45264</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32809,7 +32809,7 @@
         <v>45925</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>45925</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>46056</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>46056</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>45924</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>45926</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33252,7 +33252,7 @@
         <v>45926</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33325,7 +33325,7 @@
         <v>45926</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>46057</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>45429</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>46059</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>45516</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33695,7 +33695,7 @@
         <v>45516</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33773,7 +33773,7 @@
         <v>45464</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>44935</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>45931</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -34002,7 +34002,7 @@
         <v>46058</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34075,7 +34075,7 @@
         <v>45930</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>45589</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34231,7 +34231,7 @@
         <v>45930</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34309,7 +34309,7 @@
         <v>46062</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34382,7 +34382,7 @@
         <v>46063</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34455,7 +34455,7 @@
         <v>46063</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34528,7 +34528,7 @@
         <v>45933</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>45906</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>46065</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34757,7 +34757,7 @@
         <v>45543</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>45933</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>45933</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34986,7 +34986,7 @@
         <v>45709</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>45645</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35137,7 +35137,7 @@
         <v>45560</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35215,7 +35215,7 @@
         <v>45246</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>45938</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35366,7 +35366,7 @@
         <v>45937</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>45938</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35512,7 +35512,7 @@
         <v>45938</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>45939</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>45763</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>45194</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>45943</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35892,7 +35892,7 @@
         <v>45244</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>45945</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>45945</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36121,7 +36121,7 @@
         <v>45748</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36194,7 +36194,7 @@
         <v>45944</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>45944</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36345,7 +36345,7 @@
         <v>46078</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36418,7 +36418,7 @@
         <v>46076</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>45944</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>45944</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36642,7 +36642,7 @@
         <v>45945</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36715,7 +36715,7 @@
         <v>46076</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>45944</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36866,7 +36866,7 @@
         <v>45546</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36944,7 +36944,7 @@
         <v>46076</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -37017,7 +37017,7 @@
         <v>45110</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>45947</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>45243</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>45950</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>45813</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>46084</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37465,7 +37465,7 @@
         <v>46084</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37538,7 +37538,7 @@
         <v>44490</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>45953</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -37694,7 +37694,7 @@
         <v>45103</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37767,7 +37767,7 @@
         <v>45953</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37840,7 +37840,7 @@
         <v>46084</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>45953</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>45070</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -38064,7 +38064,7 @@
         <v>46084</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38137,7 +38137,7 @@
         <v>46084</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>46086</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>45950</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38356,7 +38356,7 @@
         <v>45955</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>45955</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>46087</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>45960</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>45813</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38736,7 +38736,7 @@
         <v>45672</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38809,7 +38809,7 @@
         <v>45764</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38882,7 +38882,7 @@
         <v>45961</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38955,7 +38955,7 @@
         <v>45316</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39028,7 +39028,7 @@
         <v>45965</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -39101,7 +39101,7 @@
         <v>45965</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39174,7 +39174,7 @@
         <v>45254</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39247,7 +39247,7 @@
         <v>45965</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>45965</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>45481</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39471,7 +39471,7 @@
         <v>45964</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         <v>45463</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39617,7 +39617,7 @@
         <v>45966</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -39690,7 +39690,7 @@
         <v>46097</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39768,7 +39768,7 @@
         <v>45971</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>45922</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45667</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39987,7 +39987,7 @@
         <v>46100</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -40060,7 +40060,7 @@
         <v>45972</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40133,7 +40133,7 @@
         <v>45761</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>46099</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>45766</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>45975</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>45975</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40523,7 +40523,7 @@
         <v>45975</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>46104</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>44628</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>45161</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40825,7 +40825,7 @@
         <v>45161</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40903,7 +40903,7 @@
         <v>45818</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>45427</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41054,7 +41054,7 @@
         <v>45978</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>45718</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41200,7 +41200,7 @@
         <v>46105</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>45978</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41351,7 +41351,7 @@
         <v>45246</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>45818</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>45981</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
         <v>45981</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>45356</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41731,7 +41731,7 @@
         <v>45358</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45574</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>45818</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41960,7 +41960,7 @@
         <v>45102</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42033,7 +42033,7 @@
         <v>45984</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42106,7 +42106,7 @@
         <v>45985</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42179,7 +42179,7 @@
         <v>45316</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>45770</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         <v>45985</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>44529</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>44648</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42554,7 +42554,7 @@
         <v>45212</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>45986</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -42700,7 +42700,7 @@
         <v>45988</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>45988</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42846,7 +42846,7 @@
         <v>45980</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42919,7 +42919,7 @@
         <v>45476</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42992,7 +42992,7 @@
         <v>44474</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>44566</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -43138,7 +43138,7 @@
         <v>45551</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>46122</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43294,7 +43294,7 @@
         <v>46122</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43367,7 +43367,7 @@
         <v>46126</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43440,7 +43440,7 @@
         <v>45995</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>45995</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43586,7 +43586,7 @@
         <v>45994</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43659,7 +43659,7 @@
         <v>45994</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43732,7 +43732,7 @@
         <v>46126</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43805,7 +43805,7 @@
         <v>45995</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43878,7 +43878,7 @@
         <v>45995</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43951,7 +43951,7 @@
         <v>45995</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44024,7 +44024,7 @@
         <v>44477</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44097,7 +44097,7 @@
         <v>45994</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45994</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44243,7 +44243,7 @@
         <v>45994</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44316,7 +44316,7 @@
         <v>46127</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44389,7 +44389,7 @@
         <v>45996</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44462,7 +44462,7 @@
         <v>45132</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44535,7 +44535,7 @@
         <v>45826</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44613,7 +44613,7 @@
         <v>45649</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -44686,7 +44686,7 @@
         <v>45649</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44759,7 +44759,7 @@
         <v>45999</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>45906</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44905,7 +44905,7 @@
         <v>46000</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>46132</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>46001</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45129,7 +45129,7 @@
         <v>46132</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45202,7 +45202,7 @@
         <v>46132</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>46132</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>45105</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45431,7 +45431,7 @@
         <v>46007</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>45201</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45577,7 +45577,7 @@
         <v>45099</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>44994</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45723,7 +45723,7 @@
         <v>44486</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45796,7 +45796,7 @@
         <v>45728</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>45833</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45833</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46030,7 +46030,7 @@
         <v>45835</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>45583</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46186,7 +46186,7 @@
         <v>46136</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46264,7 +46264,7 @@
         <v>45803</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46337,7 +46337,7 @@
         <v>46076</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46410,7 +46410,7 @@
         <v>45341</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46488,7 +46488,7 @@
         <v>45561</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46561,7 +46561,7 @@
         <v>46003</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -46634,7 +46634,7 @@
         <v>44484</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46707,7 +46707,7 @@
         <v>46029</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>45257</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46853,7 +46853,7 @@
         <v>45840</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>44522</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -47004,7 +47004,7 @@
         <v>45840</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -47082,7 +47082,7 @@
         <v>45747</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -47155,7 +47155,7 @@
         <v>45596</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47228,7 +47228,7 @@
         <v>45587</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47301,7 +47301,7 @@
         <v>45843</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47379,7 +47379,7 @@
         <v>45999</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47452,7 +47452,7 @@
         <v>46003</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47530,7 +47530,7 @@
         <v>45685</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>45408</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>44994</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>45944</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47822,7 +47822,7 @@
         <v>45603</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>45860</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47973,7 +47973,7 @@
         <v>45512</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         <v>44889</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -48119,7 +48119,7 @@
         <v>45406</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -48192,7 +48192,7 @@
         <v>45771</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>44881</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48343,7 +48343,7 @@
         <v>45935</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -48416,7 +48416,7 @@
         <v>45587</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -48489,7 +48489,7 @@
         <v>45248</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -48562,7 +48562,7 @@
         <v>45796</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>45674</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -48713,7 +48713,7 @@
         <v>45839</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48786,7 +48786,7 @@
         <v>45596</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48859,7 +48859,7 @@
         <v>45691</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48937,7 +48937,7 @@
         <v>44648</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -49015,7 +49015,7 @@
         <v>44565</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -49088,7 +49088,7 @@
         <v>46029</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -49161,7 +49161,7 @@
         <v>45863</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -49234,7 +49234,7 @@
         <v>45649</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -49307,7 +49307,7 @@
         <v>45586</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>45574</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -49463,7 +49463,7 @@
         <v>45301</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>45761</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -49614,7 +49614,7 @@
         <v>45750</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -49692,7 +49692,7 @@
         <v>46084</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>46076</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49838,7 +49838,7 @@
         <v>45832</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49911,7 +49911,7 @@
         <v>45456</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49984,7 +49984,7 @@
         <v>45818</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -50057,7 +50057,7 @@
         <v>45645</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -50135,7 +50135,7 @@
         <v>45264</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>45369</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -50281,7 +50281,7 @@
         <v>45692</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -50354,7 +50354,7 @@
         <v>46147</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45893</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -50505,7 +50505,7 @@
         <v>45841</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -50578,7 +50578,7 @@
         <v>46148</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -50656,7 +50656,7 @@
         <v>44903</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45770</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -50802,7 +50802,7 @@
         <v>45838</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50875,7 +50875,7 @@
         <v>46149</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50948,7 +50948,7 @@
         <v>45672</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>46149</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -51094,7 +51094,7 @@
         <v>46150</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -51167,7 +51167,7 @@
         <v>45590</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -51245,7 +51245,7 @@
         <v>45591</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -51323,7 +51323,7 @@
         <v>45591</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -51401,7 +51401,7 @@
         <v>46150</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -51474,7 +51474,7 @@
         <v>45425</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>46150</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -51620,7 +51620,7 @@
         <v>45408</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -51693,7 +51693,7 @@
         <v>46154</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -51766,7 +51766,7 @@
         <v>45646</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51839,7 +51839,7 @@
         <v>44657</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51912,7 +51912,7 @@
         <v>46155</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51985,7 +51985,7 @@
         <v>45639</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -52058,7 +52058,7 @@
         <v>46154</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -52136,7 +52136,7 @@
         <v>45988</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>45427</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -52282,7 +52282,7 @@
         <v>45440</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -52355,7 +52355,7 @@
         <v>44847</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -52428,7 +52428,7 @@
         <v>45210</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -52506,7 +52506,7 @@
         <v>45818</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -52584,7 +52584,7 @@
         <v>45744</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -52657,7 +52657,7 @@
         <v>45691</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -52730,7 +52730,7 @@
         <v>44573</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52808,7 +52808,7 @@
         <v>45868</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52886,7 +52886,7 @@
         <v>44859</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>45544</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -53037,7 +53037,7 @@
         <v>45875</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -53110,7 +53110,7 @@
         <v>45314</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -53183,7 +53183,7 @@
         <v>45429</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -53256,7 +53256,7 @@
         <v>44963</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -53329,7 +53329,7 @@
         <v>45674</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -53402,7 +53402,7 @@
         <v>45894</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -53480,7 +53480,7 @@
         <v>45877</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -53558,7 +53558,7 @@
         <v>45505</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -53636,7 +53636,7 @@
         <v>46164</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53714,7 +53714,7 @@
         <v>46164</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -53792,7 +53792,7 @@
         <v>46164</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53870,7 +53870,7 @@
         <v>44979</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53948,7 +53948,7 @@
         <v>46164</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -54026,7 +54026,7 @@
         <v>45880</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -54104,7 +54104,7 @@
         <v>46168</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -54177,7 +54177,7 @@
         <v>46168</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -54250,7 +54250,7 @@
         <v>45470</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -54328,7 +54328,7 @@
         <v>46168</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -54401,7 +54401,7 @@
         <v>46168</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>46168</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -54547,7 +54547,7 @@
         <v>46172</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -54625,7 +54625,7 @@
         <v>46171</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -54698,7 +54698,7 @@
         <v>45881</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -54771,7 +54771,7 @@
         <v>46174</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54844,7 +54844,7 @@
         <v>44529</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54917,7 +54917,7 @@
         <v>45882</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54990,7 +54990,7 @@
         <v>45882</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -55063,7 +55063,7 @@
         <v>45574</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -55141,7 +55141,7 @@
         <v>45764</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -55214,7 +55214,7 @@
         <v>46175</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -55287,7 +55287,7 @@
         <v>45884</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -55365,7 +55365,7 @@
         <v>46178</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -55443,7 +55443,7 @@
         <v>45446</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -55516,7 +55516,7 @@
         <v>45356</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -55589,7 +55589,7 @@
         <v>46177</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -55667,7 +55667,7 @@
         <v>45649</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55740,7 +55740,7 @@
         <v>45764</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -55813,7 +55813,7 @@
         <v>46177</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55891,7 +55891,7 @@
         <v>46170</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -55969,7 +55969,7 @@
         <v>46181</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -56047,7 +56047,7 @@
         <v>46182</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -56125,7 +56125,7 @@
         <v>45014</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -56198,7 +56198,7 @@
         <v>46183</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -56271,7 +56271,7 @@
         <v>46184</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -56349,7 +56349,7 @@
         <v>46184</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -56447,7 +56447,7 @@
         <v>46183</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -56525,7 +56525,7 @@
         <v>46184</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -56603,7 +56603,7 @@
         <v>44964</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -56681,7 +56681,7 @@
         <v>45770</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -56754,7 +56754,7 @@
         <v>45254</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>46185</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56900,7 +56900,7 @@
         <v>44796</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -56973,7 +56973,7 @@
         <v>45694</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -57051,7 +57051,7 @@
         <v>45523</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -57129,7 +57129,7 @@
         <v>45149</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -57202,7 +57202,7 @@
         <v>46191</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -57275,7 +57275,7 @@
         <v>45054</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -57348,7 +57348,7 @@
         <v>45429</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -57421,7 +57421,7 @@
         <v>46196</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -57494,7 +57494,7 @@
         <v>45085</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -57567,7 +57567,7 @@
         <v>45643</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -57640,7 +57640,7 @@
         <v>46197</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -57718,7 +57718,7 @@
         <v>45281</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -57796,7 +57796,7 @@
         <v>46198</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57869,7 +57869,7 @@
         <v>46197</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57942,7 +57942,7 @@
         <v>46197</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -58015,7 +58015,7 @@
         <v>46197</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -58088,7 +58088,7 @@
         <v>46202</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -58166,7 +58166,7 @@
         <v>46202</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -58244,7 +58244,7 @@
         <v>44903</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -58317,7 +58317,7 @@
         <v>46202</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -58395,7 +58395,7 @@
         <v>45210</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -58473,7 +58473,7 @@
         <v>46203</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -58546,7 +58546,7 @@
         <v>46204</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -58619,7 +58619,7 @@
         <v>46204</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -58692,7 +58692,7 @@
         <v>46204</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58765,7 +58765,7 @@
         <v>44524</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -58838,7 +58838,7 @@
         <v>45212</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58916,7 +58916,7 @@
         <v>46206</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58994,7 +58994,7 @@
         <v>46206</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -59072,7 +59072,7 @@
         <v>44706</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -59145,7 +59145,7 @@
         <v>46208</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -59218,7 +59218,7 @@
         <v>46206</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -59296,7 +59296,7 @@
         <v>44747</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -59369,7 +59369,7 @@
         <v>46211</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -59442,7 +59442,7 @@
         <v>44673</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59515,7 +59515,7 @@
         <v>46209</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -59593,7 +59593,7 @@
         <v>46209</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -59671,7 +59671,7 @@
         <v>46209</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59749,7 +59749,7 @@
         <v>45548</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -59822,7 +59822,7 @@
         <v>44657</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59895,7 +59895,7 @@
         <v>44657</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59968,7 +59968,7 @@
         <v>46259</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -60046,7 +60046,7 @@
         <v>46259</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -60124,7 +60124,7 @@
         <v>44966</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -60202,7 +60202,7 @@
         <v>46259</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -60280,7 +60280,7 @@
         <v>46261</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -60358,7 +60358,7 @@
         <v>45924</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -60431,7 +60431,7 @@
         <v>46261</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -60504,7 +60504,7 @@
         <v>46261</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -60577,7 +60577,7 @@
         <v>46261</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -60650,7 +60650,7 @@
         <v>46217</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60728,7 +60728,7 @@
         <v>45894</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -60801,7 +60801,7 @@
         <v>46261</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60894,7 +60894,7 @@
         <v>45593</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60972,7 +60972,7 @@
         <v>46217</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -61050,7 +61050,7 @@
         <v>46217</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -61128,7 +61128,7 @@
         <v>46217</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -61206,7 +61206,7 @@
         <v>46168</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -61279,7 +61279,7 @@
         <v>45429</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -61352,7 +61352,7 @@
         <v>45429</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -61425,7 +61425,7 @@
         <v>46266</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -61503,7 +61503,7 @@
         <v>45085</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -61576,7 +61576,7 @@
         <v>46267</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -61649,7 +61649,7 @@
         <v>45483</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -61722,7 +61722,7 @@
         <v>45153</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -61795,7 +61795,7 @@
         <v>45509</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -61868,7 +61868,7 @@
         <v>46269</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -61946,7 +61946,7 @@
         <v>46268</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -62019,7 +62019,7 @@
         <v>46225</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -62097,7 +62097,7 @@
         <v>46268</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -62175,7 +62175,7 @@
         <v>46029</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -62248,7 +62248,7 @@
         <v>45256</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -62321,7 +62321,7 @@
         <v>45562</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -62399,7 +62399,7 @@
         <v>45653</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -62472,7 +62472,7 @@
         <v>46272</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -62550,7 +62550,7 @@
         <v>46273</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -62628,7 +62628,7 @@
         <v>46268</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -62706,7 +62706,7 @@
         <v>45247</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -62779,7 +62779,7 @@
         <v>46270</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -62852,7 +62852,7 @@
         <v>46274</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -62925,7 +62925,7 @@
         <v>46274</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -62998,7 +62998,7 @@
         <v>46275</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -63071,7 +63071,7 @@
         <v>46275</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -63144,7 +63144,7 @@
         <v>45499</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -63217,7 +63217,7 @@
         <v>46274</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -63290,7 +63290,7 @@
         <v>46274</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -63368,7 +63368,7 @@
         <v>46275</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -63446,7 +63446,7 @@
         <v>46275</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -63519,7 +63519,7 @@
         <v>46275</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -63592,7 +63592,7 @@
         <v>46234</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -63670,7 +63670,7 @@
         <v>46276</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -63743,7 +63743,7 @@
         <v>46276</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -63816,7 +63816,7 @@
         <v>46234</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -63894,7 +63894,7 @@
         <v>46234</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -63972,7 +63972,7 @@
         <v>45156</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -64045,7 +64045,7 @@
         <v>46281</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -64123,7 +64123,7 @@
         <v>46281</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -64201,7 +64201,7 @@
         <v>44642</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -64279,7 +64279,7 @@
         <v>45070</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -64352,7 +64352,7 @@
         <v>46238</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -64430,7 +64430,7 @@
         <v>44901</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -64503,7 +64503,7 @@
         <v>46281</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -64576,7 +64576,7 @@
         <v>46238</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -64654,7 +64654,7 @@
         <v>46281</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -64732,7 +64732,7 @@
         <v>45195</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -64810,7 +64810,7 @@
         <v>46283</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -64888,7 +64888,7 @@
         <v>45649</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -64961,7 +64961,7 @@
         <v>46239</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -65039,7 +65039,7 @@
         <v>46240</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -65112,7 +65112,7 @@
         <v>45589</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -65190,7 +65190,7 @@
         <v>45589</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -65268,7 +65268,7 @@
         <v>46240</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -65346,7 +65346,7 @@
         <v>46283</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -65424,7 +65424,7 @@
         <v>45460</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -65502,7 +65502,7 @@
         <v>45832</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -65575,7 +65575,7 @@
         <v>45350</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -65648,7 +65648,7 @@
         <v>46287</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -65726,7 +65726,7 @@
         <v>46202</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -65799,7 +65799,7 @@
         <v>44732</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -65872,7 +65872,7 @@
         <v>45856</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -65950,7 +65950,7 @@
         <v>45677</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -66028,7 +66028,7 @@
         <v>44908</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -66101,7 +66101,7 @@
         <v>45216</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -66179,7 +66179,7 @@
         <v>46197</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -66252,7 +66252,7 @@
         <v>44726</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -66325,7 +66325,7 @@
         <v>44566</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -66398,7 +66398,7 @@
         <v>46287</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -66476,7 +66476,7 @@
         <v>44841</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -66554,7 +66554,7 @@
         <v>46246</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -66627,7 +66627,7 @@
         <v>45356</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -66700,7 +66700,7 @@
         <v>46289</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -66773,7 +66773,7 @@
         <v>46293</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -66851,7 +66851,7 @@
         <v>44734</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -66924,7 +66924,7 @@
         <v>45653</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -66997,7 +66997,7 @@
         <v>45770</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -67070,7 +67070,7 @@
         <v>45544</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -67143,7 +67143,7 @@
         <v>46290</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -67221,7 +67221,7 @@
         <v>46293</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -67294,7 +67294,7 @@
         <v>44795</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -67367,7 +67367,7 @@
         <v>45161</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -67440,7 +67440,7 @@
         <v>46293</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -67518,7 +67518,7 @@
         <v>46248</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -67591,7 +67591,7 @@
         <v>46293</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -67669,7 +67669,7 @@
         <v>46252</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -67747,7 +67747,7 @@
         <v>45194</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -67825,7 +67825,7 @@
         <v>44908</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -67898,7 +67898,7 @@
         <v>45358</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -67971,7 +67971,7 @@
         <v>46251</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -68049,7 +68049,7 @@
         <v>45680</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -68127,7 +68127,7 @@
         <v>45187</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -68205,7 +68205,7 @@
         <v>46294</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -68283,7 +68283,7 @@
         <v>44887</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -68361,7 +68361,7 @@
         <v>45166</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -68439,7 +68439,7 @@
         <v>45653</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -68512,7 +68512,7 @@
         <v>45174</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -68585,7 +68585,7 @@
         <v>45323</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -68658,7 +68658,7 @@
         <v>46253</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -68731,7 +68731,7 @@
         <v>46251</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -68804,7 +68804,7 @@
         <v>44931</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -68877,7 +68877,7 @@
         <v>45001</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -68950,7 +68950,7 @@
         <v>46254</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -69023,7 +69023,7 @@
         <v>46254</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -69096,7 +69096,7 @@
         <v>45772</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -69169,7 +69169,7 @@
         <v>45770</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -69242,7 +69242,7 @@
         <v>45813</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -69320,7 +69320,7 @@
         <v>46297</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -69398,7 +69398,7 @@
         <v>44964</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -69476,7 +69476,7 @@
         <v>46254</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -69554,7 +69554,7 @@
         <v>46296</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -69632,7 +69632,7 @@
         <v>46296</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -69710,7 +69710,7 @@
         <v>46029</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -69788,7 +69788,7 @@
         <v>46255</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -69866,7 +69866,7 @@
         <v>45035</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -69939,7 +69939,7 @@
         <v>45476</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -70012,7 +70012,7 @@
         <v>45093</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -70090,7 +70090,7 @@
         <v>44883</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -70168,7 +70168,7 @@
         <v>45529</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -70241,7 +70241,7 @@
         <v>45099</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -70314,7 +70314,7 @@
         <v>44484</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -70387,7 +70387,7 @@
         <v>45454</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -70460,7 +70460,7 @@
         <v>44614</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -70533,7 +70533,7 @@
         <v>45079</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -70606,7 +70606,7 @@
         <v>45762</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -70679,7 +70679,7 @@
         <v>45646</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -70752,7 +70752,7 @@
         <v>45205</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -70825,7 +70825,7 @@
         <v>45233</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -70903,7 +70903,7 @@
         <v>45379</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -70976,7 +70976,7 @@
         <v>45773</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -71054,7 +71054,7 @@
         <v>44994</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -71127,7 +71127,7 @@
         <v>44568</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -71200,7 +71200,7 @@
         <v>45572</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -71278,7 +71278,7 @@
         <v>45764</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -71351,7 +71351,7 @@
         <v>45764</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -71424,7 +71424,7 @@
         <v>45618</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -71502,7 +71502,7 @@
         <v>45099</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -71575,7 +71575,7 @@
         <v>44812</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -71648,7 +71648,7 @@
         <v>44823</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -71726,7 +71726,7 @@
         <v>45625</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -71804,7 +71804,7 @@
         <v>44856</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -71877,7 +71877,7 @@
         <v>45013</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -71950,7 +71950,7 @@
         <v>44585</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -72023,7 +72023,7 @@
         <v>45204</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -72096,7 +72096,7 @@
         <v>45687</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -72169,7 +72169,7 @@
         <v>44935</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -72242,7 +72242,7 @@
         <v>45453</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -72315,7 +72315,7 @@
         <v>45646</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -72388,7 +72388,7 @@
         <v>45478</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -72461,7 +72461,7 @@
         <v>45391</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -72534,7 +72534,7 @@
         <v>45778</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -72612,7 +72612,7 @@
         <v>45782</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -72685,7 +72685,7 @@
         <v>45376</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -72763,7 +72763,7 @@
         <v>45013</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -72836,7 +72836,7 @@
         <v>45376</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -72914,7 +72914,7 @@
         <v>45667</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -72987,7 +72987,7 @@
         <v>44945</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -73065,7 +73065,7 @@
         <v>45743</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -73138,7 +73138,7 @@
         <v>45743</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -73211,7 +73211,7 @@
         <v>45789</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -73289,7 +73289,7 @@
         <v>45792</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -73362,7 +73362,7 @@
         <v>45799</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -73440,7 +73440,7 @@
         <v>45799</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -73518,7 +73518,7 @@
         <v>45799</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -73596,7 +73596,7 @@
         <v>45810</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -73674,7 +73674,7 @@
         <v>45818</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -73752,7 +73752,7 @@
         <v>45840</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -73830,7 +73830,7 @@
         <v>46018</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -73903,7 +73903,7 @@
         <v>46147</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -73976,7 +73976,7 @@
         <v>46147</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -74049,7 +74049,7 @@
         <v>46147</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -74127,7 +74127,7 @@
         <v>46152</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -74200,7 +74200,7 @@
         <v>46152</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -74273,7 +74273,7 @@
         <v>46148</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>

--- a/Översikt BODEN.xlsx
+++ b/Översikt BODEN.xlsx
@@ -601,7 +601,7 @@
         <v>45152</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45506</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>45152</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45068</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>45075</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45152</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>44853</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>46247</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>46168</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>45105</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>44964</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>45237</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>45212</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>45790</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>46149</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>44889</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>45684</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>45771</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>44859</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>44853</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45049</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>45295</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>46210</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>44869</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>46195</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>45418</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>45463</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>44795</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>44489</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>44904</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>45912</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>45912</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>45428</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>45832</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>45893</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>45512</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>45964</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>46149</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>46209</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>45835</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>45307</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>45988</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45980</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>46148</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>46196</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>46261</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>45077</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>44833</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>45155</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>45933</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>45818</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>45952</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>44755</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>45981</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>45791</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>45698</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>46073</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>46181</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         <v>46184</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>46205</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>46217</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>46267</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>46240</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>46286</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>46258</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>44487</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>44648</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         <v>44804</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         <v>44796</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>44735</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>44573</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44678</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>45072</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>45803</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>45341</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>45910</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>45922</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>45645</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44573</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>45517</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>45701</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>45526</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>45594</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>45820</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>45714</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>45137</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>45875</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>45638</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>46066</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>46066</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>45999</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>45834</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>44830</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
         <v>46149</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>46164</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>46184</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>46205</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>46205</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>46205</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>46217</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>46225</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>46267</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>46270</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>46286</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>46245</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>46247</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>45301</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>46258</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>46304</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>46261</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>46184</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>46261</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>45376</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>44648</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>44840</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>45763</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>44529</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>45211</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14201,7 +14201,7 @@
         <v>45901</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         <v>45905</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>45448</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>44648</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>44529</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>45559</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>45513</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>45406</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>45936</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         <v>45944</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>45947</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>45949</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>45950</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>45952</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>45958</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>45960</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>44692</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>45975</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>46100</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>44642</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45994</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>45999</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>46003</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>44925</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>45313</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>46048</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>45538</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>45884</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>46147</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>46168</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17459,7 +17459,7 @@
         <v>46178</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>46178</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>46178</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>46183</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>46184</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>46205</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>46272</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>46267</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18347,7 +18347,7 @@
         <v>46272</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>46236</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>46282</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>46240</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>45966</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>46241</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>46134</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>46251</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>46037</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>46255</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>46302</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>46261</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>46261</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>46261</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>46261</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>44944</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>45418</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20212,7 +20212,7 @@
         <v>45028</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20322,7 +20322,7 @@
         <v>45643</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>45799</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>45901</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>45952</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>44509</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>44677</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>44577</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>44489</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>44659</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>44671</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>44852</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21282,7 +21282,7 @@
         <v>44815</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>44648</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>44617</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44648</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44865</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>44609</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>44609</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>44648</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>44530</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>44480</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>44480</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22110,7 +22110,7 @@
         <v>44529</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44565</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22256,7 +22256,7 @@
         <v>44573</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>44565</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>44671</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>44566</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>44734</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>44617</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>44820</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>44635</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22855,7 +22855,7 @@
         <v>44625</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>44596</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>44566</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23079,7 +23079,7 @@
         <v>44566</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
         <v>44600</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>44831</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23308,7 +23308,7 @@
         <v>44797</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23381,7 +23381,7 @@
         <v>44887</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>44721</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23532,7 +23532,7 @@
         <v>44543</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23605,7 +23605,7 @@
         <v>44796</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>44796</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>44484</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>44799</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>44799</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44749</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24058,7 +24058,7 @@
         <v>44530</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24131,7 +24131,7 @@
         <v>44722</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
         <v>44743</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24277,7 +24277,7 @@
         <v>44529</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>45070</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>44795</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>44489</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>45453</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>44812</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>45358</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24793,7 +24793,7 @@
         <v>45356</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         <v>44671</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24939,7 +24939,7 @@
         <v>45763</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         <v>45099</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>45646</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>44812</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>45079</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>45102</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>45593</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25455,7 +25455,7 @@
         <v>45770</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>45454</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>45770</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
         <v>45677</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>45425</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>45771</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25898,7 +25898,7 @@
         <v>45125</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>44935</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26049,7 +26049,7 @@
         <v>45646</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>45301</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>45254</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>45766</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>45463</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>45406</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26497,7 +26497,7 @@
         <v>45093</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>45572</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>44734</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>45635</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26799,7 +26799,7 @@
         <v>44489</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>45429</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -26945,7 +26945,7 @@
         <v>45099</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>44657</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27091,7 +27091,7 @@
         <v>45512</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27164,7 +27164,7 @@
         <v>44908</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27237,7 +27237,7 @@
         <v>45099</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27310,7 +27310,7 @@
         <v>45264</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>45350</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>44558</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>45379</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>45358</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>44484</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>44486</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>45884</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>45446</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45205</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>44883</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>45884</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>45035</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
         <v>45341</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>45419</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         <v>45649</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28508,7 +28508,7 @@
         <v>45653</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>45174</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>44833</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>45110</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>45254</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>44935</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28951,7 +28951,7 @@
         <v>45649</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>45516</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>45516</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29180,7 +29180,7 @@
         <v>45643</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>45764</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29331,7 +29331,7 @@
         <v>45551</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>45527</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>45764</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>45764</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
         <v>45891</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>45897</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29774,7 +29774,7 @@
         <v>45897</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29847,7 +29847,7 @@
         <v>45589</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -29925,7 +29925,7 @@
         <v>45902</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>45244</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         <v>45653</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30154,7 +30154,7 @@
         <v>45901</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>45672</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>45544</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30378,7 +30378,7 @@
         <v>45770</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>45574</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>45476</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>45574</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>45281</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
         <v>45764</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>45764</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>44529</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>45907</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>44881</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>44908</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>45397</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>45397</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>45910</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31425,7 +31425,7 @@
         <v>45429</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>45429</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>45910</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31649,7 +31649,7 @@
         <v>45391</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31722,7 +31722,7 @@
         <v>45911</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31795,7 +31795,7 @@
         <v>45912</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31868,7 +31868,7 @@
         <v>45912</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31941,7 +31941,7 @@
         <v>45912</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>45156</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32092,7 +32092,7 @@
         <v>45778</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44994</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>44983</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>45782</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>45590</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>45618</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32545,7 +32545,7 @@
         <v>45204</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32618,7 +32618,7 @@
         <v>45604</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32691,7 +32691,7 @@
         <v>45915</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>45915</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>45915</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44889</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32993,7 +32993,7 @@
         <v>44901</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -33066,7 +33066,7 @@
         <v>44903</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33139,7 +33139,7 @@
         <v>45772</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>44529</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33285,7 +33285,7 @@
         <v>44522</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33358,7 +33358,7 @@
         <v>45691</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33436,7 +33436,7 @@
         <v>45591</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33514,7 +33514,7 @@
         <v>45919</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>45919</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>44609</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>45922</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>45922</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33889,7 +33889,7 @@
         <v>45922</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>44881</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>44966</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>45786</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>45149</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>45161</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>45161</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>45758</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>45750</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>45924</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>45132</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>45926</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>45926</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34868,7 +34868,7 @@
         <v>45013</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34941,7 +34941,7 @@
         <v>45926</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         <v>44795</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35087,7 +35087,7 @@
         <v>45264</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>45379</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>45925</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>45925</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>45791</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>45216</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>45596</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>45600</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -35681,7 +35681,7 @@
         <v>45600</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>45653</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>44566</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>45930</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35978,7 +35978,7 @@
         <v>45930</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>45523</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36134,7 +36134,7 @@
         <v>45793</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>45590</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>45590</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>45587</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>45583</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36509,7 +36509,7 @@
         <v>45798</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>45478</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36660,7 +36660,7 @@
         <v>45649</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>45649</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>45798</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45931</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36962,7 +36962,7 @@
         <v>45797</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -37040,7 +37040,7 @@
         <v>45798</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -37118,7 +37118,7 @@
         <v>44862</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37191,7 +37191,7 @@
         <v>44726</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>45933</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37342,7 +37342,7 @@
         <v>45411</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37415,7 +37415,7 @@
         <v>45799</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>45906</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>45310</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37644,7 +37644,7 @@
         <v>44642</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>45933</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37800,7 +37800,7 @@
         <v>45548</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37873,7 +37873,7 @@
         <v>45803</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>45933</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -38024,7 +38024,7 @@
         <v>45054</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -38097,7 +38097,7 @@
         <v>44963</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38170,7 +38170,7 @@
         <v>45238</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38243,7 +38243,7 @@
         <v>44628</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>45561</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         <v>45590</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38462,7 +38462,7 @@
         <v>45512</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>45608</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38608,7 +38608,7 @@
         <v>45608</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>45937</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45938</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38832,7 +38832,7 @@
         <v>45763</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38905,7 +38905,7 @@
         <v>45938</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38983,7 +38983,7 @@
         <v>45764</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45764</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -39129,7 +39129,7 @@
         <v>45546</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39207,7 +39207,7 @@
         <v>45938</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39280,7 +39280,7 @@
         <v>45464</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39358,7 +39358,7 @@
         <v>45770</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>45243</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>44859</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>45645</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39655,7 +39655,7 @@
         <v>44657</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -39728,7 +39728,7 @@
         <v>45212</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39806,7 +39806,7 @@
         <v>45429</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39879,7 +39879,7 @@
         <v>44657</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>45687</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>44994</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45939</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40176,7 +40176,7 @@
         <v>45944</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40249,7 +40249,7 @@
         <v>44673</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40322,7 +40322,7 @@
         <v>45944</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40395,7 +40395,7 @@
         <v>45562</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45560</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>45944</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40629,7 +40629,7 @@
         <v>45770</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -40702,7 +40702,7 @@
         <v>45944</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>45943</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40853,7 +40853,7 @@
         <v>45944</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>45945</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>45589</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>45589</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -41160,7 +41160,7 @@
         <v>45813</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41238,7 +41238,7 @@
         <v>45945</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>45945</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>45813</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41462,7 +41462,7 @@
         <v>45766</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41540,7 +41540,7 @@
         <v>45818</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>45818</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41696,7 +41696,7 @@
         <v>45316</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>45427</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>45574</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41920,7 +41920,7 @@
         <v>45481</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41998,7 +41998,7 @@
         <v>45950</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42071,7 +42071,7 @@
         <v>45818</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42149,7 +42149,7 @@
         <v>45947</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42227,7 +42227,7 @@
         <v>45505</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>45826</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42383,7 +42383,7 @@
         <v>45625</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42461,7 +42461,7 @@
         <v>44490</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42539,7 +42539,7 @@
         <v>45460</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42617,7 +42617,7 @@
         <v>44903</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>45237</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -42763,7 +42763,7 @@
         <v>45953</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42836,7 +42836,7 @@
         <v>45953</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42914,7 +42914,7 @@
         <v>45953</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42992,7 +42992,7 @@
         <v>45950</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>45955</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43138,7 +43138,7 @@
         <v>45955</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -43211,7 +43211,7 @@
         <v>45960</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>45212</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43362,7 +43362,7 @@
         <v>45833</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43440,7 +43440,7 @@
         <v>45961</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>45833</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43591,7 +43591,7 @@
         <v>45210</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>45803</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>45194</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43820,7 +43820,7 @@
         <v>45964</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>45835</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>45161</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>44994</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44122,7 +44122,7 @@
         <v>45965</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>45161</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>45965</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44341,7 +44341,7 @@
         <v>45966</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44414,7 +44414,7 @@
         <v>45840</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44492,7 +44492,7 @@
         <v>45965</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44565,7 +44565,7 @@
         <v>44783</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>45195</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44716,7 +44716,7 @@
         <v>45965</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -44789,7 +44789,7 @@
         <v>45747</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44862,7 +44862,7 @@
         <v>45840</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44940,7 +44940,7 @@
         <v>45201</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>44796</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45086,7 +45086,7 @@
         <v>45728</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>45971</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45237,7 +45237,7 @@
         <v>45843</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>45085</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45388,7 +45388,7 @@
         <v>45246</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45461,7 +45461,7 @@
         <v>45762</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>45153</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45607,7 +45607,7 @@
         <v>45166</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45685,7 +45685,7 @@
         <v>45972</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -45758,7 +45758,7 @@
         <v>45603</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45831,7 +45831,7 @@
         <v>45718</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45904,7 +45904,7 @@
         <v>45649</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45977,7 +45977,7 @@
         <v>45247</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>45314</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45149</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>45975</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>45256</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46347,7 +46347,7 @@
         <v>44484</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46420,7 +46420,7 @@
         <v>45978</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46498,7 +46498,7 @@
         <v>45680</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46576,7 +46576,7 @@
         <v>45674</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>45596</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -46722,7 +46722,7 @@
         <v>44856</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46795,7 +46795,7 @@
         <v>45796</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46873,7 +46873,7 @@
         <v>45863</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46946,7 +46946,7 @@
         <v>45254</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -47019,7 +47019,7 @@
         <v>45103</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -47092,7 +47092,7 @@
         <v>45257</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>44823</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>45975</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47321,7 +47321,7 @@
         <v>45975</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47399,7 +47399,7 @@
         <v>45978</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>44648</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47550,7 +47550,7 @@
         <v>45264</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45838</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47701,7 +47701,7 @@
         <v>44568</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47774,7 +47774,7 @@
         <v>45456</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45667</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47920,7 +47920,7 @@
         <v>44648</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47998,7 +47998,7 @@
         <v>45356</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -48071,7 +48071,7 @@
         <v>45499</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -48144,7 +48144,7 @@
         <v>45194</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -48222,7 +48222,7 @@
         <v>45649</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -48295,7 +48295,7 @@
         <v>45709</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48373,7 +48373,7 @@
         <v>45369</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48446,7 +48446,7 @@
         <v>45764</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -48519,7 +48519,7 @@
         <v>45694</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -48597,7 +48597,7 @@
         <v>45868</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -48675,7 +48675,7 @@
         <v>45773</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -48753,7 +48753,7 @@
         <v>45260</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45877</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48904,7 +48904,7 @@
         <v>45022</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48977,7 +48977,7 @@
         <v>45880</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -49055,7 +49055,7 @@
         <v>44573</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>45881</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>45981</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         <v>45981</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -49362,7 +49362,7 @@
         <v>45882</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -49435,7 +49435,7 @@
         <v>45882</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -49508,7 +49508,7 @@
         <v>45345</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>45483</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -49654,7 +49654,7 @@
         <v>46097</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -49732,7 +49732,7 @@
         <v>45672</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -49805,7 +49805,7 @@
         <v>45285</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -49878,7 +49878,7 @@
         <v>46099</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49956,7 +49956,7 @@
         <v>45985</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>45761</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
         <v>45529</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -50180,7 +50180,7 @@
         <v>44732</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -50253,7 +50253,7 @@
         <v>45323</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -50326,7 +50326,7 @@
         <v>46100</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>44970</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -50472,7 +50472,7 @@
         <v>46105</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -50545,7 +50545,7 @@
         <v>45748</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -50618,7 +50618,7 @@
         <v>45986</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -50691,7 +50691,7 @@
         <v>44524</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -50764,7 +50764,7 @@
         <v>45210</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -50842,7 +50842,7 @@
         <v>45761</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -50915,7 +50915,7 @@
         <v>44881</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>45984</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>45692</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -51139,7 +51139,7 @@
         <v>45248</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -51212,7 +51212,7 @@
         <v>45509</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -51285,7 +51285,7 @@
         <v>45988</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -51358,7 +51358,7 @@
         <v>45988</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45210</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -51509,7 +51509,7 @@
         <v>45537</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -51587,7 +51587,7 @@
         <v>44887</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -51665,7 +51665,7 @@
         <v>44565</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -51738,7 +51738,7 @@
         <v>44964</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -51816,7 +51816,7 @@
         <v>45233</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -51894,7 +51894,7 @@
         <v>45994</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51967,7 +51967,7 @@
         <v>45070</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>45085</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -52113,7 +52113,7 @@
         <v>45980</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -52186,7 +52186,7 @@
         <v>45994</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -52259,7 +52259,7 @@
         <v>45994</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -52332,7 +52332,7 @@
         <v>45539</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -52405,7 +52405,7 @@
         <v>45994</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -52478,7 +52478,7 @@
         <v>45994</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         <v>46122</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -52629,7 +52629,7 @@
         <v>46122</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -52702,7 +52702,7 @@
         <v>45995</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -52775,7 +52775,7 @@
         <v>45995</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -52848,7 +52848,7 @@
         <v>45995</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52921,7 +52921,7 @@
         <v>45995</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52994,7 +52994,7 @@
         <v>45996</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -53067,7 +53067,7 @@
         <v>46126</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -53140,7 +53140,7 @@
         <v>45995</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -53213,7 +53213,7 @@
         <v>45906</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -53286,7 +53286,7 @@
         <v>45999</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -53359,7 +53359,7 @@
         <v>46000</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -53432,7 +53432,7 @@
         <v>46001</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -53505,7 +53505,7 @@
         <v>46001</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -53578,7 +53578,7 @@
         <v>46126</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -53651,7 +53651,7 @@
         <v>46127</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -53724,7 +53724,7 @@
         <v>46132</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53797,7 +53797,7 @@
         <v>45429</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -53870,7 +53870,7 @@
         <v>46132</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53948,7 +53948,7 @@
         <v>46132</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -54026,7 +54026,7 @@
         <v>46132</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -54104,7 +54104,7 @@
         <v>46001</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -54177,7 +54177,7 @@
         <v>44747</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -54250,7 +54250,7 @@
         <v>44706</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -54323,7 +54323,7 @@
         <v>46003</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -54396,7 +54396,7 @@
         <v>44880</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -54469,7 +54469,7 @@
         <v>44979</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -54547,7 +54547,7 @@
         <v>44931</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -54620,7 +54620,7 @@
         <v>46003</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -54693,7 +54693,7 @@
         <v>46008</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -54766,7 +54766,7 @@
         <v>45187</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -54844,7 +54844,7 @@
         <v>45591</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54922,7 +54922,7 @@
         <v>46007</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54995,7 +54995,7 @@
         <v>46009</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -55068,7 +55068,7 @@
         <v>46009</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -55141,7 +55141,7 @@
         <v>45994</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -55214,7 +55214,7 @@
         <v>45014</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -55287,7 +55287,7 @@
         <v>46009</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -55360,7 +55360,7 @@
         <v>45544</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -55433,7 +55433,7 @@
         <v>45001</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -55506,7 +55506,7 @@
         <v>44964</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -55584,7 +55584,7 @@
         <v>46012</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -55657,7 +55657,7 @@
         <v>46012</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -55730,7 +55730,7 @@
         <v>45902</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55808,7 +55808,7 @@
         <v>46020</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -55881,7 +55881,7 @@
         <v>44484</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55954,7 +55954,7 @@
         <v>46076</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -56027,7 +56027,7 @@
         <v>46066</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -56100,7 +56100,7 @@
         <v>46066</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -56173,7 +56173,7 @@
         <v>45935</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -56246,7 +56246,7 @@
         <v>45105</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -56319,7 +56319,7 @@
         <v>44585</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -56392,7 +56392,7 @@
         <v>46030</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -56470,7 +56470,7 @@
         <v>46030</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -56548,7 +56548,7 @@
         <v>45586</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -56626,7 +56626,7 @@
         <v>44847</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -56699,7 +56699,7 @@
         <v>46029</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -56772,7 +56772,7 @@
         <v>46030</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -56850,7 +56850,7 @@
         <v>46136</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56928,7 +56928,7 @@
         <v>46020</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -57001,7 +57001,7 @@
         <v>45944</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -57074,7 +57074,7 @@
         <v>45832</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -57147,7 +57147,7 @@
         <v>46003</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -57225,7 +57225,7 @@
         <v>45316</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -57298,7 +57298,7 @@
         <v>44552</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -57371,7 +57371,7 @@
         <v>44614</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -57444,7 +57444,7 @@
         <v>45470</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>45839</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -57595,7 +57595,7 @@
         <v>46042</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -57668,7 +57668,7 @@
         <v>45587</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -57741,7 +57741,7 @@
         <v>46042</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -57814,7 +57814,7 @@
         <v>45860</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57892,7 +57892,7 @@
         <v>45818</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57965,7 +57965,7 @@
         <v>44566</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -58038,7 +58038,7 @@
         <v>45999</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -58111,7 +58111,7 @@
         <v>46029</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -58184,7 +58184,7 @@
         <v>45685</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -58257,7 +58257,7 @@
         <v>45645</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -58335,7 +58335,7 @@
         <v>45543</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -58408,7 +58408,7 @@
         <v>46029</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -58481,7 +58481,7 @@
         <v>45408</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -58554,7 +58554,7 @@
         <v>46048</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -58627,7 +58627,7 @@
         <v>46003</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -58700,7 +58700,7 @@
         <v>46076</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58773,7 +58773,7 @@
         <v>45246</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -58846,7 +58846,7 @@
         <v>44841</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58924,7 +58924,7 @@
         <v>45762</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58997,7 +58997,7 @@
         <v>45476</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -59070,7 +59070,7 @@
         <v>46050</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -59143,7 +59143,7 @@
         <v>46052</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -59216,7 +59216,7 @@
         <v>46056</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -59289,7 +59289,7 @@
         <v>46056</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -59362,7 +59362,7 @@
         <v>46057</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -59435,7 +59435,7 @@
         <v>46058</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59508,7 +59508,7 @@
         <v>46084</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -59581,7 +59581,7 @@
         <v>46062</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>46059</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59727,7 +59727,7 @@
         <v>45893</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -59805,7 +59805,7 @@
         <v>46063</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59878,7 +59878,7 @@
         <v>46063</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59951,7 +59951,7 @@
         <v>45841</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -60024,7 +60024,7 @@
         <v>46065</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -60102,7 +60102,7 @@
         <v>46148</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -60180,7 +60180,7 @@
         <v>46147</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -60253,7 +60253,7 @@
         <v>46150</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -60326,7 +60326,7 @@
         <v>46150</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -60399,7 +60399,7 @@
         <v>46150</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -60472,7 +60472,7 @@
         <v>46149</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -60545,7 +60545,7 @@
         <v>46149</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -60618,7 +60618,7 @@
         <v>46076</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60691,7 +60691,7 @@
         <v>46154</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -60769,7 +60769,7 @@
         <v>46076</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60842,7 +60842,7 @@
         <v>46076</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60915,7 +60915,7 @@
         <v>45408</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60988,7 +60988,7 @@
         <v>45427</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -61061,7 +61061,7 @@
         <v>46154</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -61134,7 +61134,7 @@
         <v>46078</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -61207,7 +61207,7 @@
         <v>45639</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -61280,7 +61280,7 @@
         <v>46084</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -61353,7 +61353,7 @@
         <v>46084</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -61426,7 +61426,7 @@
         <v>46084</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -61499,7 +61499,7 @@
         <v>46084</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -61572,7 +61572,7 @@
         <v>45988</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -61645,7 +61645,7 @@
         <v>45646</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -61718,7 +61718,7 @@
         <v>46084</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -61791,7 +61791,7 @@
         <v>46086</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -61864,7 +61864,7 @@
         <v>46155</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -61937,7 +61937,7 @@
         <v>45440</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -62010,7 +62010,7 @@
         <v>46087</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -62088,7 +62088,7 @@
         <v>45818</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -62166,7 +62166,7 @@
         <v>45922</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -62239,7 +62239,7 @@
         <v>45875</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -62312,7 +62312,7 @@
         <v>45744</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -62385,7 +62385,7 @@
         <v>45691</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -62458,7 +62458,7 @@
         <v>46164</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -62536,7 +62536,7 @@
         <v>46164</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -62614,7 +62614,7 @@
         <v>46164</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -62692,7 +62692,7 @@
         <v>46164</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -62770,7 +62770,7 @@
         <v>45674</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -62843,7 +62843,7 @@
         <v>46168</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -62916,7 +62916,7 @@
         <v>46168</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -62989,7 +62989,7 @@
         <v>45894</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -63067,7 +63067,7 @@
         <v>46168</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -63140,7 +63140,7 @@
         <v>46168</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -63213,7 +63213,7 @@
         <v>46168</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -63286,7 +63286,7 @@
         <v>46171</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -63359,7 +63359,7 @@
         <v>46172</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -63437,7 +63437,7 @@
         <v>46174</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -63510,7 +63510,7 @@
         <v>46175</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -63583,7 +63583,7 @@
         <v>46177</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -63661,7 +63661,7 @@
         <v>46177</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -63739,7 +63739,7 @@
         <v>45356</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -63812,7 +63812,7 @@
         <v>46178</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -63890,7 +63890,7 @@
         <v>46181</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -63968,7 +63968,7 @@
         <v>46170</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -64046,7 +64046,7 @@
         <v>46183</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -64124,7 +64124,7 @@
         <v>46182</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -64202,7 +64202,7 @@
         <v>46183</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -64275,7 +64275,7 @@
         <v>46185</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -64348,7 +64348,7 @@
         <v>46184</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -64446,7 +64446,7 @@
         <v>46184</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -64524,7 +64524,7 @@
         <v>46184</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -64602,7 +64602,7 @@
         <v>46191</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -64675,7 +64675,7 @@
         <v>46197</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -64753,7 +64753,7 @@
         <v>46197</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -64826,7 +64826,7 @@
         <v>46197</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -64899,7 +64899,7 @@
         <v>46198</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -64972,7 +64972,7 @@
         <v>46196</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -65045,7 +65045,7 @@
         <v>46197</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -65118,7 +65118,7 @@
         <v>45643</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -65191,7 +65191,7 @@
         <v>46203</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -65264,7 +65264,7 @@
         <v>46204</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -65337,7 +65337,7 @@
         <v>46202</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -65415,7 +65415,7 @@
         <v>46202</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -65493,7 +65493,7 @@
         <v>46202</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -65571,7 +65571,7 @@
         <v>46204</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -65644,7 +65644,7 @@
         <v>46204</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -65717,7 +65717,7 @@
         <v>46209</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -65795,7 +65795,7 @@
         <v>46206</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -65873,7 +65873,7 @@
         <v>46206</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -65951,7 +65951,7 @@
         <v>46206</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -66029,7 +66029,7 @@
         <v>46208</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -66102,7 +66102,7 @@
         <v>46209</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -66180,7 +66180,7 @@
         <v>46209</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -66258,7 +66258,7 @@
         <v>46211</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -66331,7 +66331,7 @@
         <v>46217</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -66409,7 +66409,7 @@
         <v>46217</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -66487,7 +66487,7 @@
         <v>46217</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -66565,7 +66565,7 @@
         <v>46217</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -66643,7 +66643,7 @@
         <v>45924</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -66716,7 +66716,7 @@
         <v>45894</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -66789,7 +66789,7 @@
         <v>46266</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -66867,7 +66867,7 @@
         <v>46168</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -66940,7 +66940,7 @@
         <v>46268</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -67013,7 +67013,7 @@
         <v>46225</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -67091,7 +67091,7 @@
         <v>46268</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -67169,7 +67169,7 @@
         <v>46267</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -67242,7 +67242,7 @@
         <v>46029</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -67315,7 +67315,7 @@
         <v>46272</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -67393,7 +67393,7 @@
         <v>46269</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -67471,7 +67471,7 @@
         <v>46270</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -67544,7 +67544,7 @@
         <v>46268</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -67622,7 +67622,7 @@
         <v>46274</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -67695,7 +67695,7 @@
         <v>46273</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -67773,7 +67773,7 @@
         <v>46274</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -67851,7 +67851,7 @@
         <v>46274</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -67924,7 +67924,7 @@
         <v>46274</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -67997,7 +67997,7 @@
         <v>46276</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -68070,7 +68070,7 @@
         <v>46275</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -68143,7 +68143,7 @@
         <v>46275</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -68221,7 +68221,7 @@
         <v>46276</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -68294,7 +68294,7 @@
         <v>46275</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -68367,7 +68367,7 @@
         <v>46275</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -68440,7 +68440,7 @@
         <v>46275</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -68513,7 +68513,7 @@
         <v>46234</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -68591,7 +68591,7 @@
         <v>46234</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -68669,7 +68669,7 @@
         <v>46234</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -68747,7 +68747,7 @@
         <v>46281</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -68820,7 +68820,7 @@
         <v>46281</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -68898,7 +68898,7 @@
         <v>46281</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -68976,7 +68976,7 @@
         <v>46281</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -69054,7 +69054,7 @@
         <v>46238</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -69132,7 +69132,7 @@
         <v>46238</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -69210,7 +69210,7 @@
         <v>46239</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -69288,7 +69288,7 @@
         <v>46240</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -69361,7 +69361,7 @@
         <v>46240</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -69439,7 +69439,7 @@
         <v>45856</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -69517,7 +69517,7 @@
         <v>46283</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -69595,7 +69595,7 @@
         <v>45832</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -69668,7 +69668,7 @@
         <v>46283</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -69746,7 +69746,7 @@
         <v>46197</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -69819,7 +69819,7 @@
         <v>46287</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -69897,7 +69897,7 @@
         <v>46202</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -69970,7 +69970,7 @@
         <v>46287</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -70048,7 +70048,7 @@
         <v>46290</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -70126,7 +70126,7 @@
         <v>46289</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -70199,7 +70199,7 @@
         <v>46246</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -70272,7 +70272,7 @@
         <v>46293</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -70345,7 +70345,7 @@
         <v>46293</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -70423,7 +70423,7 @@
         <v>46293</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -70501,7 +70501,7 @@
         <v>46294</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -70579,7 +70579,7 @@
         <v>46293</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -70657,7 +70657,7 @@
         <v>46248</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -70730,7 +70730,7 @@
         <v>46029</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -70808,7 +70808,7 @@
         <v>46296</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -70886,7 +70886,7 @@
         <v>46253</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -70959,7 +70959,7 @@
         <v>46296</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -71037,7 +71037,7 @@
         <v>46251</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -71115,7 +71115,7 @@
         <v>46252</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -71193,7 +71193,7 @@
         <v>45813</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -71271,7 +71271,7 @@
         <v>46254</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -71349,7 +71349,7 @@
         <v>46251</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -71422,7 +71422,7 @@
         <v>46297</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -71500,7 +71500,7 @@
         <v>46300</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -71578,7 +71578,7 @@
         <v>46254</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -71651,7 +71651,7 @@
         <v>46254</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -71724,7 +71724,7 @@
         <v>46300</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -71802,7 +71802,7 @@
         <v>46255</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -71880,7 +71880,7 @@
         <v>46299</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -71953,7 +71953,7 @@
         <v>46300</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -72031,7 +72031,7 @@
         <v>46300</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -72109,7 +72109,7 @@
         <v>46302</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -72182,7 +72182,7 @@
         <v>46259</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -72260,7 +72260,7 @@
         <v>46259</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -72338,7 +72338,7 @@
         <v>46259</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -72416,7 +72416,7 @@
         <v>46301</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -72494,7 +72494,7 @@
         <v>46261</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -72567,7 +72567,7 @@
         <v>46304</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -72645,7 +72645,7 @@
         <v>46261</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -72723,7 +72723,7 @@
         <v>46261</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -72796,7 +72796,7 @@
         <v>46261</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -72869,7 +72869,7 @@
         <v>46261</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -72962,7 +72962,7 @@
         <v>45376</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -73040,7 +73040,7 @@
         <v>45013</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -73113,7 +73113,7 @@
         <v>45376</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -73191,7 +73191,7 @@
         <v>45667</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -73264,7 +73264,7 @@
         <v>44945</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -73342,7 +73342,7 @@
         <v>45743</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -73415,7 +73415,7 @@
         <v>45743</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -73488,7 +73488,7 @@
         <v>45789</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -73566,7 +73566,7 @@
         <v>45792</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -73639,7 +73639,7 @@
         <v>45799</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -73717,7 +73717,7 @@
         <v>45799</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -73795,7 +73795,7 @@
         <v>45799</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -73873,7 +73873,7 @@
         <v>45810</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -73951,7 +73951,7 @@
         <v>45818</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -74029,7 +74029,7 @@
         <v>45840</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -74107,7 +74107,7 @@
         <v>46018</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -74180,7 +74180,7 @@
         <v>46147</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -74253,7 +74253,7 @@
         <v>46147</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -74326,7 +74326,7 @@
         <v>46147</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -74404,7 +74404,7 @@
         <v>46152</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -74477,7 +74477,7 @@
         <v>46152</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -74550,7 +74550,7 @@
         <v>46148</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>

--- a/Översikt BODEN.xlsx
+++ b/Översikt BODEN.xlsx
@@ -601,7 +601,7 @@
         <v>45152</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45506</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>45152</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45068</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>45075</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45152</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>44853</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>46247</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>46168</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>45105</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>44964</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>45237</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>45212</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>45790</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>46149</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>44889</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>45684</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>45771</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>44859</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>44853</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45049</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>45295</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>46210</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>44869</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>46195</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>45418</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>45463</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>44795</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>44489</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>44904</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>45912</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>45912</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>45428</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>45832</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>45893</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>45512</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>45964</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>46149</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>46209</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>45835</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>45307</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>45988</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45980</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>46148</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>46196</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>46261</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>45077</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>44833</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>45155</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>45933</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>45818</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>45952</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>44755</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>45981</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>45791</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>45698</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>46073</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>46181</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         <v>46184</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>46205</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>46217</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>46267</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>46240</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>46286</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>46258</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>44487</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>44648</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         <v>44804</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         <v>44796</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>44735</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>44573</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44678</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>45072</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>45803</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>45341</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>45910</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>45922</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>45645</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44573</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>45517</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>45701</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>45526</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>45594</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>45820</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>45714</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>45137</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>45875</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>45638</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>46066</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>46066</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>45999</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>45834</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>44830</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
         <v>46149</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>46164</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>46184</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>46205</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>46205</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>46205</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>46217</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>46225</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>46267</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>46270</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>46286</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>46245</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>46247</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>45301</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>46258</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>46304</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>46261</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>46184</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>46261</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>45376</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>44648</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>44840</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>45763</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>44529</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>45211</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14201,7 +14201,7 @@
         <v>45901</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         <v>45905</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>45448</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>44648</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>44529</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>45559</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>45513</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>45406</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>45936</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         <v>45944</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>45947</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>45949</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>45950</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>45952</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>45958</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>45960</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>44692</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>45975</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>46100</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>44642</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45994</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>45999</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>46003</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>44925</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>45313</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>46048</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>45538</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>45884</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>46147</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>46168</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17459,7 +17459,7 @@
         <v>46178</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>46178</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>46178</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>46183</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>46184</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>46205</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>46272</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>46267</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18347,7 +18347,7 @@
         <v>46272</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>46236</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>46282</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>46240</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>45966</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>46241</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>46134</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>46251</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>46037</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>46255</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>46302</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>46261</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>46261</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>46261</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>46261</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>44944</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>45418</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20212,7 +20212,7 @@
         <v>45028</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20322,7 +20322,7 @@
         <v>45643</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>45799</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>45901</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>45952</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>44509</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>44677</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>44577</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>44489</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>44659</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>44671</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>44852</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21282,7 +21282,7 @@
         <v>44815</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>44648</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>44617</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44648</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44865</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>44609</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>44609</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>44648</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>44530</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>44480</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>44480</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22110,7 +22110,7 @@
         <v>44529</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44565</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22256,7 +22256,7 @@
         <v>44573</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>44565</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>44671</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>44566</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>44734</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>44617</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>44820</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>44635</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22855,7 +22855,7 @@
         <v>44625</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>44596</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>44566</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23079,7 +23079,7 @@
         <v>44566</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
         <v>44600</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>44831</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23308,7 +23308,7 @@
         <v>44797</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23381,7 +23381,7 @@
         <v>44887</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>44721</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23532,7 +23532,7 @@
         <v>44543</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23605,7 +23605,7 @@
         <v>44796</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>44796</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>44484</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>44799</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>44799</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44749</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24058,7 +24058,7 @@
         <v>44530</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24131,7 +24131,7 @@
         <v>44722</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
         <v>44743</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24277,7 +24277,7 @@
         <v>44529</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>45070</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>44795</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>44489</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>45453</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>44812</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>45358</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24793,7 +24793,7 @@
         <v>45356</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         <v>44671</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24939,7 +24939,7 @@
         <v>45763</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         <v>45099</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>45646</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>44812</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>45079</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>45102</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>45593</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25455,7 +25455,7 @@
         <v>45770</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>45454</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>45770</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
         <v>45677</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>45425</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>45771</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25898,7 +25898,7 @@
         <v>45125</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>44935</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26049,7 +26049,7 @@
         <v>45646</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>45301</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>45254</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>45766</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>45463</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>45406</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26497,7 +26497,7 @@
         <v>45093</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>45572</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>44734</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>45635</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26799,7 +26799,7 @@
         <v>44489</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>45429</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -26945,7 +26945,7 @@
         <v>45099</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>44657</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27091,7 +27091,7 @@
         <v>45512</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27164,7 +27164,7 @@
         <v>44908</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27237,7 +27237,7 @@
         <v>45099</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27310,7 +27310,7 @@
         <v>45264</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>45350</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>44558</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>45379</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>45358</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>44484</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>44486</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>45884</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>45446</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45205</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>44883</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>45884</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>45035</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
         <v>45341</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>45419</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         <v>45649</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28508,7 +28508,7 @@
         <v>45653</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>45174</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>44833</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>45110</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>45254</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>44935</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28951,7 +28951,7 @@
         <v>45649</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>45516</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>45516</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29180,7 +29180,7 @@
         <v>45643</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>45764</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29331,7 +29331,7 @@
         <v>45551</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>45527</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>45764</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>45764</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
         <v>45891</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>45897</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29774,7 +29774,7 @@
         <v>45897</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29847,7 +29847,7 @@
         <v>45589</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -29925,7 +29925,7 @@
         <v>45902</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>45244</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         <v>45653</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30154,7 +30154,7 @@
         <v>45901</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>45672</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>45544</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30378,7 +30378,7 @@
         <v>45770</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>45574</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>45476</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>45574</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>45281</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
         <v>45764</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>45764</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>44529</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>45907</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>44881</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>44908</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>45397</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>45397</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>45910</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31425,7 +31425,7 @@
         <v>45429</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>45429</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>45910</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31649,7 +31649,7 @@
         <v>45391</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31722,7 +31722,7 @@
         <v>45911</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31795,7 +31795,7 @@
         <v>45912</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31868,7 +31868,7 @@
         <v>45912</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31941,7 +31941,7 @@
         <v>45912</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>45156</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32092,7 +32092,7 @@
         <v>45778</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44994</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>44983</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>45782</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>45590</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>45618</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32545,7 +32545,7 @@
         <v>45204</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32618,7 +32618,7 @@
         <v>45604</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32691,7 +32691,7 @@
         <v>45915</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>45915</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>45915</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44889</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32993,7 +32993,7 @@
         <v>44901</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -33066,7 +33066,7 @@
         <v>44903</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33139,7 +33139,7 @@
         <v>45772</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>44529</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33285,7 +33285,7 @@
         <v>44522</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33358,7 +33358,7 @@
         <v>45691</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33436,7 +33436,7 @@
         <v>45591</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33514,7 +33514,7 @@
         <v>45919</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>45919</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>44609</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>45922</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>45922</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33889,7 +33889,7 @@
         <v>45922</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>44881</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>44966</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>45786</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>45149</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>45161</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>45161</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>45758</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>45750</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>45924</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>45132</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>45926</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>45926</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34868,7 +34868,7 @@
         <v>45013</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34941,7 +34941,7 @@
         <v>45926</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         <v>44795</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35087,7 +35087,7 @@
         <v>45264</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>45379</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>45925</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>45925</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>45791</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>45216</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>45596</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>45600</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -35681,7 +35681,7 @@
         <v>45600</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>45653</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>44566</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>45930</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35978,7 +35978,7 @@
         <v>45930</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>45523</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36134,7 +36134,7 @@
         <v>45793</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>45590</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>45590</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>45587</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>45583</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36509,7 +36509,7 @@
         <v>45798</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>45478</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36660,7 +36660,7 @@
         <v>45649</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>45649</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>45798</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45931</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36962,7 +36962,7 @@
         <v>45797</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -37040,7 +37040,7 @@
         <v>45798</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -37118,7 +37118,7 @@
         <v>44862</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37191,7 +37191,7 @@
         <v>44726</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>45933</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37342,7 +37342,7 @@
         <v>45411</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37415,7 +37415,7 @@
         <v>45799</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>45906</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>45310</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37644,7 +37644,7 @@
         <v>44642</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>45933</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37800,7 +37800,7 @@
         <v>45548</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37873,7 +37873,7 @@
         <v>45803</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>45933</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -38024,7 +38024,7 @@
         <v>45054</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -38097,7 +38097,7 @@
         <v>44963</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38170,7 +38170,7 @@
         <v>45238</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38243,7 +38243,7 @@
         <v>44628</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>45561</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         <v>45590</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38462,7 +38462,7 @@
         <v>45512</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>45608</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38608,7 +38608,7 @@
         <v>45608</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>45937</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45938</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38832,7 +38832,7 @@
         <v>45763</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38905,7 +38905,7 @@
         <v>45938</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38983,7 +38983,7 @@
         <v>45764</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45764</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -39129,7 +39129,7 @@
         <v>45546</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39207,7 +39207,7 @@
         <v>45938</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39280,7 +39280,7 @@
         <v>45464</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39358,7 +39358,7 @@
         <v>45770</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>45243</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>44859</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>45645</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39655,7 +39655,7 @@
         <v>44657</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -39728,7 +39728,7 @@
         <v>45212</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39806,7 +39806,7 @@
         <v>45429</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39879,7 +39879,7 @@
         <v>44657</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>45687</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>44994</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45939</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40176,7 +40176,7 @@
         <v>45944</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40249,7 +40249,7 @@
         <v>44673</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40322,7 +40322,7 @@
         <v>45944</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40395,7 +40395,7 @@
         <v>45562</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45560</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>45944</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40629,7 +40629,7 @@
         <v>45770</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -40702,7 +40702,7 @@
         <v>45944</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>45943</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40853,7 +40853,7 @@
         <v>45944</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>45945</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         <v>45589</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>45589</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -41160,7 +41160,7 @@
         <v>45813</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41238,7 +41238,7 @@
         <v>45945</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>45945</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>45813</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41462,7 +41462,7 @@
         <v>45766</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41540,7 +41540,7 @@
         <v>45818</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>45818</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41696,7 +41696,7 @@
         <v>45316</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>45427</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>45574</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41920,7 +41920,7 @@
         <v>45481</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41998,7 +41998,7 @@
         <v>45950</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42071,7 +42071,7 @@
         <v>45818</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42149,7 +42149,7 @@
         <v>45947</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42227,7 +42227,7 @@
         <v>45505</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>45826</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42383,7 +42383,7 @@
         <v>45625</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42461,7 +42461,7 @@
         <v>44490</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42539,7 +42539,7 @@
         <v>45460</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42617,7 +42617,7 @@
         <v>44903</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>45237</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -42763,7 +42763,7 @@
         <v>45953</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42836,7 +42836,7 @@
         <v>45953</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42914,7 +42914,7 @@
         <v>45953</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42992,7 +42992,7 @@
         <v>45950</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>45955</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43138,7 +43138,7 @@
         <v>45955</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -43211,7 +43211,7 @@
         <v>45960</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>45212</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43362,7 +43362,7 @@
         <v>45833</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43440,7 +43440,7 @@
         <v>45961</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>45833</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43591,7 +43591,7 @@
         <v>45210</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>45803</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>45194</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43820,7 +43820,7 @@
         <v>45964</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>45835</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>45161</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>44994</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44122,7 +44122,7 @@
         <v>45965</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>45161</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>45965</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44341,7 +44341,7 @@
         <v>45966</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44414,7 +44414,7 @@
         <v>45840</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44492,7 +44492,7 @@
         <v>45965</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44565,7 +44565,7 @@
         <v>44783</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>45195</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44716,7 +44716,7 @@
         <v>45965</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -44789,7 +44789,7 @@
         <v>45747</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44862,7 +44862,7 @@
         <v>45840</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44940,7 +44940,7 @@
         <v>45201</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>44796</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45086,7 +45086,7 @@
         <v>45728</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>45971</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45237,7 +45237,7 @@
         <v>45843</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>45085</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45388,7 +45388,7 @@
         <v>45246</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45461,7 +45461,7 @@
         <v>45762</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>45153</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45607,7 +45607,7 @@
         <v>45166</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45685,7 +45685,7 @@
         <v>45972</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -45758,7 +45758,7 @@
         <v>45603</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45831,7 +45831,7 @@
         <v>45718</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45904,7 +45904,7 @@
         <v>45649</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45977,7 +45977,7 @@
         <v>45247</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>45314</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45149</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>45975</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>45256</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46347,7 +46347,7 @@
         <v>44484</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46420,7 +46420,7 @@
         <v>45978</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46498,7 +46498,7 @@
         <v>45680</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46576,7 +46576,7 @@
         <v>45674</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>45596</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -46722,7 +46722,7 @@
         <v>44856</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46795,7 +46795,7 @@
         <v>45796</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46873,7 +46873,7 @@
         <v>45863</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46946,7 +46946,7 @@
         <v>45254</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -47019,7 +47019,7 @@
         <v>45103</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -47092,7 +47092,7 @@
         <v>45257</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>44823</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>45975</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47321,7 +47321,7 @@
         <v>45975</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47399,7 +47399,7 @@
         <v>45978</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>44648</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47550,7 +47550,7 @@
         <v>45264</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45838</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47701,7 +47701,7 @@
         <v>44568</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47774,7 +47774,7 @@
         <v>45456</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45667</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47920,7 +47920,7 @@
         <v>44648</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47998,7 +47998,7 @@
         <v>45356</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -48071,7 +48071,7 @@
         <v>45499</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -48144,7 +48144,7 @@
         <v>45194</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -48222,7 +48222,7 @@
         <v>45649</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -48295,7 +48295,7 @@
         <v>45709</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48373,7 +48373,7 @@
         <v>45369</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48446,7 +48446,7 @@
         <v>45764</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -48519,7 +48519,7 @@
         <v>45694</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -48597,7 +48597,7 @@
         <v>45868</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -48675,7 +48675,7 @@
         <v>45773</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -48753,7 +48753,7 @@
         <v>45260</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45877</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48904,7 +48904,7 @@
         <v>45022</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48977,7 +48977,7 @@
         <v>45880</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -49055,7 +49055,7 @@
         <v>44573</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>45881</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>45981</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         <v>45981</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -49362,7 +49362,7 @@
         <v>45882</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -49435,7 +49435,7 @@
         <v>45882</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -49508,7 +49508,7 @@
         <v>45345</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>45483</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -49654,7 +49654,7 @@
         <v>46097</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -49732,7 +49732,7 @@
         <v>45672</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -49805,7 +49805,7 @@
         <v>45285</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -49878,7 +49878,7 @@
         <v>46099</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49956,7 +49956,7 @@
         <v>45985</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>45761</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
         <v>45529</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -50180,7 +50180,7 @@
         <v>44732</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -50253,7 +50253,7 @@
         <v>45323</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -50326,7 +50326,7 @@
         <v>46100</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>44970</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -50472,7 +50472,7 @@
         <v>46105</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -50545,7 +50545,7 @@
         <v>45748</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -50618,7 +50618,7 @@
         <v>45986</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -50691,7 +50691,7 @@
         <v>44524</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -50764,7 +50764,7 @@
         <v>45210</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -50842,7 +50842,7 @@
         <v>45761</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -50915,7 +50915,7 @@
         <v>44881</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>45984</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>45692</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -51139,7 +51139,7 @@
         <v>45248</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -51212,7 +51212,7 @@
         <v>45509</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -51285,7 +51285,7 @@
         <v>45988</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -51358,7 +51358,7 @@
         <v>45988</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45210</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -51509,7 +51509,7 @@
         <v>45537</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -51587,7 +51587,7 @@
         <v>44887</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -51665,7 +51665,7 @@
         <v>44565</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -51738,7 +51738,7 @@
         <v>44964</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -51816,7 +51816,7 @@
         <v>45233</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -51894,7 +51894,7 @@
         <v>45994</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51967,7 +51967,7 @@
         <v>45070</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>45085</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -52113,7 +52113,7 @@
         <v>45980</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -52186,7 +52186,7 @@
         <v>45994</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -52259,7 +52259,7 @@
         <v>45994</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -52332,7 +52332,7 @@
         <v>45539</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -52405,7 +52405,7 @@
         <v>45994</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -52478,7 +52478,7 @@
         <v>45994</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         <v>46122</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -52629,7 +52629,7 @@
         <v>46122</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -52702,7 +52702,7 @@
         <v>45995</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -52775,7 +52775,7 @@
         <v>45995</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -52848,7 +52848,7 @@
         <v>45995</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52921,7 +52921,7 @@
         <v>45995</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52994,7 +52994,7 @@
         <v>45996</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -53067,7 +53067,7 @@
         <v>46126</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -53140,7 +53140,7 @@
         <v>45995</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -53213,7 +53213,7 @@
         <v>45906</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -53286,7 +53286,7 @@
         <v>45999</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -53359,7 +53359,7 @@
         <v>46000</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -53432,7 +53432,7 @@
         <v>46001</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -53505,7 +53505,7 @@
         <v>46001</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -53578,7 +53578,7 @@
         <v>46126</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -53651,7 +53651,7 @@
         <v>46127</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -53724,7 +53724,7 @@
         <v>46132</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53797,7 +53797,7 @@
         <v>45429</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -53870,7 +53870,7 @@
         <v>46132</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53948,7 +53948,7 @@
         <v>46132</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -54026,7 +54026,7 @@
         <v>46132</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -54104,7 +54104,7 @@
         <v>46001</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -54177,7 +54177,7 @@
         <v>44747</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -54250,7 +54250,7 @@
         <v>44706</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -54323,7 +54323,7 @@
         <v>46003</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -54396,7 +54396,7 @@
         <v>44880</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -54469,7 +54469,7 @@
         <v>44979</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -54547,7 +54547,7 @@
         <v>44931</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -54620,7 +54620,7 @@
         <v>46003</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -54693,7 +54693,7 @@
         <v>46008</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -54766,7 +54766,7 @@
         <v>45187</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -54844,7 +54844,7 @@
         <v>45591</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54922,7 +54922,7 @@
         <v>46007</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54995,7 +54995,7 @@
         <v>46009</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -55068,7 +55068,7 @@
         <v>46009</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -55141,7 +55141,7 @@
         <v>45994</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -55214,7 +55214,7 @@
         <v>45014</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -55287,7 +55287,7 @@
         <v>46009</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -55360,7 +55360,7 @@
         <v>45544</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -55433,7 +55433,7 @@
         <v>45001</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -55506,7 +55506,7 @@
         <v>44964</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -55584,7 +55584,7 @@
         <v>46012</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -55657,7 +55657,7 @@
         <v>46012</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -55730,7 +55730,7 @@
         <v>45902</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55808,7 +55808,7 @@
         <v>46020</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -55881,7 +55881,7 @@
         <v>44484</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55954,7 +55954,7 @@
         <v>46076</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -56027,7 +56027,7 @@
         <v>46066</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -56100,7 +56100,7 @@
         <v>46066</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -56173,7 +56173,7 @@
         <v>45935</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -56246,7 +56246,7 @@
         <v>45105</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -56319,7 +56319,7 @@
         <v>44585</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -56392,7 +56392,7 @@
         <v>46030</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -56470,7 +56470,7 @@
         <v>46030</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -56548,7 +56548,7 @@
         <v>45586</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -56626,7 +56626,7 @@
         <v>44847</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -56699,7 +56699,7 @@
         <v>46029</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -56772,7 +56772,7 @@
         <v>46030</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -56850,7 +56850,7 @@
         <v>46136</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56928,7 +56928,7 @@
         <v>46020</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -57001,7 +57001,7 @@
         <v>45944</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -57074,7 +57074,7 @@
         <v>45832</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -57147,7 +57147,7 @@
         <v>46003</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -57225,7 +57225,7 @@
         <v>45316</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -57298,7 +57298,7 @@
         <v>44552</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -57371,7 +57371,7 @@
         <v>44614</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -57444,7 +57444,7 @@
         <v>45470</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>45839</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -57595,7 +57595,7 @@
         <v>46042</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -57668,7 +57668,7 @@
         <v>45587</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -57741,7 +57741,7 @@
         <v>46042</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -57814,7 +57814,7 @@
         <v>45860</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57892,7 +57892,7 @@
         <v>45818</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57965,7 +57965,7 @@
         <v>44566</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -58038,7 +58038,7 @@
         <v>45999</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -58111,7 +58111,7 @@
         <v>46029</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -58184,7 +58184,7 @@
         <v>45685</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -58257,7 +58257,7 @@
         <v>45645</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -58335,7 +58335,7 @@
         <v>45543</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -58408,7 +58408,7 @@
         <v>46029</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -58481,7 +58481,7 @@
         <v>45408</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -58554,7 +58554,7 @@
         <v>46048</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -58627,7 +58627,7 @@
         <v>46003</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -58700,7 +58700,7 @@
         <v>46076</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58773,7 +58773,7 @@
         <v>45246</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -58846,7 +58846,7 @@
         <v>44841</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58924,7 +58924,7 @@
         <v>45762</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58997,7 +58997,7 @@
         <v>45476</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -59070,7 +59070,7 @@
         <v>46050</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -59143,7 +59143,7 @@
         <v>46052</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -59216,7 +59216,7 @@
         <v>46056</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -59289,7 +59289,7 @@
         <v>46056</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -59362,7 +59362,7 @@
         <v>46057</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -59435,7 +59435,7 @@
         <v>46058</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59508,7 +59508,7 @@
         <v>46084</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -59581,7 +59581,7 @@
         <v>46062</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>46059</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59727,7 +59727,7 @@
         <v>45893</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -59805,7 +59805,7 @@
         <v>46063</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59878,7 +59878,7 @@
         <v>46063</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59951,7 +59951,7 @@
         <v>45841</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -60024,7 +60024,7 @@
         <v>46065</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -60102,7 +60102,7 @@
         <v>46148</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -60180,7 +60180,7 @@
         <v>46147</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -60253,7 +60253,7 @@
         <v>46150</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -60326,7 +60326,7 @@
         <v>46150</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -60399,7 +60399,7 @@
         <v>46150</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -60472,7 +60472,7 @@
         <v>46149</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -60545,7 +60545,7 @@
         <v>46149</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -60618,7 +60618,7 @@
         <v>46076</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60691,7 +60691,7 @@
         <v>46154</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -60769,7 +60769,7 @@
         <v>46076</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60842,7 +60842,7 @@
         <v>46076</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60915,7 +60915,7 @@
         <v>45408</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60988,7 +60988,7 @@
         <v>45427</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -61061,7 +61061,7 @@
         <v>46154</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -61134,7 +61134,7 @@
         <v>46078</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -61207,7 +61207,7 @@
         <v>45639</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -61280,7 +61280,7 @@
         <v>46084</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -61353,7 +61353,7 @@
         <v>46084</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -61426,7 +61426,7 @@
         <v>46084</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -61499,7 +61499,7 @@
         <v>46084</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -61572,7 +61572,7 @@
         <v>45988</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -61645,7 +61645,7 @@
         <v>45646</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -61718,7 +61718,7 @@
         <v>46084</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -61791,7 +61791,7 @@
         <v>46086</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -61864,7 +61864,7 @@
         <v>46155</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -61937,7 +61937,7 @@
         <v>45440</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -62010,7 +62010,7 @@
         <v>46087</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -62088,7 +62088,7 @@
         <v>45818</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -62166,7 +62166,7 @@
         <v>45922</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -62239,7 +62239,7 @@
         <v>45875</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -62312,7 +62312,7 @@
         <v>45744</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -62385,7 +62385,7 @@
         <v>45691</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -62458,7 +62458,7 @@
         <v>46164</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -62536,7 +62536,7 @@
         <v>46164</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -62614,7 +62614,7 @@
         <v>46164</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -62692,7 +62692,7 @@
         <v>46164</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -62770,7 +62770,7 @@
         <v>45674</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -62843,7 +62843,7 @@
         <v>46168</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -62916,7 +62916,7 @@
         <v>46168</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -62989,7 +62989,7 @@
         <v>45894</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -63067,7 +63067,7 @@
         <v>46168</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -63140,7 +63140,7 @@
         <v>46168</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -63213,7 +63213,7 @@
         <v>46168</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -63286,7 +63286,7 @@
         <v>46171</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -63359,7 +63359,7 @@
         <v>46172</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -63437,7 +63437,7 @@
         <v>46174</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -63510,7 +63510,7 @@
         <v>46175</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -63583,7 +63583,7 @@
         <v>46177</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -63661,7 +63661,7 @@
         <v>46177</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -63739,7 +63739,7 @@
         <v>45356</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -63812,7 +63812,7 @@
         <v>46178</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -63890,7 +63890,7 @@
         <v>46181</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -63968,7 +63968,7 @@
         <v>46170</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -64046,7 +64046,7 @@
         <v>46183</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -64124,7 +64124,7 @@
         <v>46182</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -64202,7 +64202,7 @@
         <v>46183</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -64275,7 +64275,7 @@
         <v>46185</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -64348,7 +64348,7 @@
         <v>46184</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -64446,7 +64446,7 @@
         <v>46184</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -64524,7 +64524,7 @@
         <v>46184</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -64602,7 +64602,7 @@
         <v>46191</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -64675,7 +64675,7 @@
         <v>46197</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -64753,7 +64753,7 @@
         <v>46197</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -64826,7 +64826,7 @@
         <v>46197</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -64899,7 +64899,7 @@
         <v>46198</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -64972,7 +64972,7 @@
         <v>46196</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -65045,7 +65045,7 @@
         <v>46197</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -65118,7 +65118,7 @@
         <v>45643</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -65191,7 +65191,7 @@
         <v>46203</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -65264,7 +65264,7 @@
         <v>46204</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -65337,7 +65337,7 @@
         <v>46202</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -65415,7 +65415,7 @@
         <v>46202</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -65493,7 +65493,7 @@
         <v>46202</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -65571,7 +65571,7 @@
         <v>46204</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -65644,7 +65644,7 @@
         <v>46204</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -65717,7 +65717,7 @@
         <v>46209</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -65795,7 +65795,7 @@
         <v>46206</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -65873,7 +65873,7 @@
         <v>46206</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -65951,7 +65951,7 @@
         <v>46206</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -66029,7 +66029,7 @@
         <v>46208</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -66102,7 +66102,7 @@
         <v>46209</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -66180,7 +66180,7 @@
         <v>46209</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -66258,7 +66258,7 @@
         <v>46211</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -66331,7 +66331,7 @@
         <v>46217</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -66409,7 +66409,7 @@
         <v>46217</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -66487,7 +66487,7 @@
         <v>46217</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -66565,7 +66565,7 @@
         <v>46217</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -66643,7 +66643,7 @@
         <v>45924</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -66716,7 +66716,7 @@
         <v>45894</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -66789,7 +66789,7 @@
         <v>46266</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -66867,7 +66867,7 @@
         <v>46168</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -66940,7 +66940,7 @@
         <v>46268</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -67013,7 +67013,7 @@
         <v>46225</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -67091,7 +67091,7 @@
         <v>46268</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -67169,7 +67169,7 @@
         <v>46267</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -67242,7 +67242,7 @@
         <v>46029</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -67315,7 +67315,7 @@
         <v>46272</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -67393,7 +67393,7 @@
         <v>46269</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -67471,7 +67471,7 @@
         <v>46270</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -67544,7 +67544,7 @@
         <v>46268</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -67622,7 +67622,7 @@
         <v>46274</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -67695,7 +67695,7 @@
         <v>46273</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -67773,7 +67773,7 @@
         <v>46274</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -67851,7 +67851,7 @@
         <v>46274</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -67924,7 +67924,7 @@
         <v>46274</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -67997,7 +67997,7 @@
         <v>46276</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -68070,7 +68070,7 @@
         <v>46275</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -68143,7 +68143,7 @@
         <v>46275</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -68221,7 +68221,7 @@
         <v>46276</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -68294,7 +68294,7 @@
         <v>46275</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -68367,7 +68367,7 @@
         <v>46275</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -68440,7 +68440,7 @@
         <v>46275</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -68513,7 +68513,7 @@
         <v>46234</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -68591,7 +68591,7 @@
         <v>46234</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -68669,7 +68669,7 @@
         <v>46234</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -68747,7 +68747,7 @@
         <v>46281</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -68820,7 +68820,7 @@
         <v>46281</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -68898,7 +68898,7 @@
         <v>46281</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -68976,7 +68976,7 @@
         <v>46281</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -69054,7 +69054,7 @@
         <v>46238</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -69132,7 +69132,7 @@
         <v>46238</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -69210,7 +69210,7 @@
         <v>46239</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -69288,7 +69288,7 @@
         <v>46240</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -69361,7 +69361,7 @@
         <v>46240</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -69439,7 +69439,7 @@
         <v>45856</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -69517,7 +69517,7 @@
         <v>46283</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -69595,7 +69595,7 @@
         <v>45832</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -69668,7 +69668,7 @@
         <v>46283</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -69746,7 +69746,7 @@
         <v>46197</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -69819,7 +69819,7 @@
         <v>46287</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -69897,7 +69897,7 @@
         <v>46202</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -69970,7 +69970,7 @@
         <v>46287</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -70048,7 +70048,7 @@
         <v>46290</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -70126,7 +70126,7 @@
         <v>46289</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -70199,7 +70199,7 @@
         <v>46246</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -70272,7 +70272,7 @@
         <v>46293</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -70345,7 +70345,7 @@
         <v>46293</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -70423,7 +70423,7 @@
         <v>46293</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -70501,7 +70501,7 @@
         <v>46294</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -70579,7 +70579,7 @@
         <v>46293</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -70657,7 +70657,7 @@
         <v>46248</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -70730,7 +70730,7 @@
         <v>46029</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -70808,7 +70808,7 @@
         <v>46296</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -70886,7 +70886,7 @@
         <v>46253</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -70959,7 +70959,7 @@
         <v>46296</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -71037,7 +71037,7 @@
         <v>46251</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -71115,7 +71115,7 @@
         <v>46252</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -71193,7 +71193,7 @@
         <v>45813</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -71271,7 +71271,7 @@
         <v>46254</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -71349,7 +71349,7 @@
         <v>46251</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -71422,7 +71422,7 @@
         <v>46297</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -71500,7 +71500,7 @@
         <v>46300</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -71578,7 +71578,7 @@
         <v>46254</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -71651,7 +71651,7 @@
         <v>46254</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -71724,7 +71724,7 @@
         <v>46300</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -71802,7 +71802,7 @@
         <v>46255</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -71880,7 +71880,7 @@
         <v>46299</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -71953,7 +71953,7 @@
         <v>46300</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -72031,7 +72031,7 @@
         <v>46300</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -72109,7 +72109,7 @@
         <v>46302</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -72182,7 +72182,7 @@
         <v>46259</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -72260,7 +72260,7 @@
         <v>46259</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -72338,7 +72338,7 @@
         <v>46259</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -72416,7 +72416,7 @@
         <v>46301</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -72494,7 +72494,7 @@
         <v>46261</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -72567,7 +72567,7 @@
         <v>46304</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -72645,7 +72645,7 @@
         <v>46261</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -72723,7 +72723,7 @@
         <v>46261</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -72796,7 +72796,7 @@
         <v>46261</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -72869,7 +72869,7 @@
         <v>46261</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -72962,7 +72962,7 @@
         <v>45376</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -73040,7 +73040,7 @@
         <v>45013</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -73113,7 +73113,7 @@
         <v>45376</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -73191,7 +73191,7 @@
         <v>45667</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -73264,7 +73264,7 @@
         <v>44945</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -73342,7 +73342,7 @@
         <v>45743</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -73415,7 +73415,7 @@
         <v>45743</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -73488,7 +73488,7 @@
         <v>45789</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -73566,7 +73566,7 @@
         <v>45792</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -73639,7 +73639,7 @@
         <v>45799</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -73717,7 +73717,7 @@
         <v>45799</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -73795,7 +73795,7 @@
         <v>45799</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -73873,7 +73873,7 @@
         <v>45810</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -73951,7 +73951,7 @@
         <v>45818</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -74029,7 +74029,7 @@
         <v>45840</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -74107,7 +74107,7 @@
         <v>46018</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -74180,7 +74180,7 @@
         <v>46147</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -74253,7 +74253,7 @@
         <v>46147</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -74326,7 +74326,7 @@
         <v>46147</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -74404,7 +74404,7 @@
         <v>46152</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -74477,7 +74477,7 @@
         <v>46152</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -74550,7 +74550,7 @@
         <v>46148</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>

--- a/Översikt BODEN.xlsx
+++ b/Översikt BODEN.xlsx
@@ -601,7 +601,7 @@
         <v>45152</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45506</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>45152</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45068</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>45075</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45152</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>44853</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>46247</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>46168</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>44964</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>45105</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>45212</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>45790</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>46149</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>44889</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>45771</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>45684</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>44859</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>44853</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45295</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>46210</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45049</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>44869</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>46195</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>45418</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>45463</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>44489</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>44795</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>45964</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>45912</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>45912</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>46149</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>45893</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>44904</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>45512</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>46209</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45835</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>45428</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>46309</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>45832</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>45980</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>46148</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>45988</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>45307</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>46196</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>46261</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>45980</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>45791</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>45933</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>45952</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>45981</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>45077</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>46181</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>45698</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>46184</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>46073</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>44833</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>45155</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>44755</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>46205</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>46217</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>46286</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>46258</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>46240</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>45818</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>46267</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>44487</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>44648</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>44804</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>44796</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>44735</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         <v>45341</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>45517</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>45701</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>44573</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>45803</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>45834</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         <v>45910</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>45594</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         <v>45645</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>45922</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>46149</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>45714</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>45526</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>46164</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>45638</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>46066</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>46066</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>45137</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10987,7 +10987,7 @@
         <v>46184</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>46205</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>45999</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>46205</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11430,7 +11430,7 @@
         <v>46205</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
         <v>46217</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>44830</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>46225</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>46270</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
         <v>46286</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>44573</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12205,7 +12205,7 @@
         <v>46245</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         <v>45072</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>46247</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>45301</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12647,7 +12647,7 @@
         <v>44678</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>46258</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>46261</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>46304</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         <v>46261</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>46267</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>46184</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>46311</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>45820</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>45875</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>45376</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>44648</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>44840</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>45313</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>45763</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>44529</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         <v>44529</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>45448</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>44648</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>45211</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>45901</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>45905</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>46147</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>45936</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>45944</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>45947</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>45950</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>45949</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>45952</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>45958</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>45960</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>45538</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>45513</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>45975</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>44925</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>46168</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>45994</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>45999</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
         <v>46003</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>44642</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>46178</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>46178</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>46178</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>46048</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>46183</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>45884</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>46184</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         <v>45559</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>46100</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>46205</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>44692</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>46272</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18352,7 +18352,7 @@
         <v>46272</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>46236</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>46240</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>46282</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18787,7 +18787,7 @@
         <v>46241</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>45966</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>46134</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>46251</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19217,7 +19217,7 @@
         <v>46037</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>46255</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>46302</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>46261</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>46261</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45406</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>46261</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>46261</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>46311</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>46267</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>44944</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>45418</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>45028</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>45643</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>45799</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>45901</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>45952</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>44509</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21163,7 +21163,7 @@
         <v>44677</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>44577</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>44671</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>44659</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>44489</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>44852</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>44815</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>44648</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>44617</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>44648</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44865</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
         <v>44609</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>44609</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>44671</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
         <v>44887</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>44721</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44543</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>44530</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>44648</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>44734</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>44566</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>44566</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>44600</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>44749</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22960,7 +22960,7 @@
         <v>44722</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>44530</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>44565</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23179,7 +23179,7 @@
         <v>44573</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44566</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>44617</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23403,7 +23403,7 @@
         <v>44820</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>44625</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23554,7 +23554,7 @@
         <v>44596</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23632,7 +23632,7 @@
         <v>44831</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23710,7 +23710,7 @@
         <v>44799</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>44799</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23866,7 +23866,7 @@
         <v>44743</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23939,7 +23939,7 @@
         <v>44529</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>44565</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         <v>44635</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         <v>44797</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44796</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>44796</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
         <v>44489</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>44795</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>44812</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>44671</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>44552</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24752,7 +24752,7 @@
         <v>45310</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>45022</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>45411</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>44833</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>44880</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>45762</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25195,7 +25195,7 @@
         <v>44609</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25268,7 +25268,7 @@
         <v>44881</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25341,7 +25341,7 @@
         <v>45238</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>44783</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>45125</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25565,7 +25565,7 @@
         <v>45635</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>45210</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>45763</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>45419</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>44489</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         <v>45600</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>45600</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>45161</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26159,7 +26159,7 @@
         <v>45537</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>45254</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>44881</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>45237</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>45345</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>45512</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26602,7 +26602,7 @@
         <v>44558</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>45766</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>45539</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>44529</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>45285</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26972,7 +26972,7 @@
         <v>44970</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -27045,7 +27045,7 @@
         <v>45604</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -27118,7 +27118,7 @@
         <v>45764</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>44983</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27264,7 +27264,7 @@
         <v>45397</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27337,7 +27337,7 @@
         <v>45397</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>45758</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27483,7 +27483,7 @@
         <v>45260</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         <v>45527</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27629,7 +27629,7 @@
         <v>45264</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>45264</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         <v>44935</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         <v>45516</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27936,7 +27936,7 @@
         <v>45516</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -28014,7 +28014,7 @@
         <v>45543</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -28087,7 +28087,7 @@
         <v>45560</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28165,7 +28165,7 @@
         <v>45589</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>45246</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28316,7 +28316,7 @@
         <v>45194</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28394,7 +28394,7 @@
         <v>45748</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>45244</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>45103</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>45110</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>45070</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28769,7 +28769,7 @@
         <v>45672</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28842,7 +28842,7 @@
         <v>45764</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28915,7 +28915,7 @@
         <v>45254</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>45463</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>45667</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -29134,7 +29134,7 @@
         <v>44628</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29207,7 +29207,7 @@
         <v>45161</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>45161</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29363,7 +29363,7 @@
         <v>45246</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29436,7 +29436,7 @@
         <v>45718</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>45358</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>45102</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29655,7 +29655,7 @@
         <v>45770</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
         <v>44529</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29801,7 +29801,7 @@
         <v>45356</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29874,7 +29874,7 @@
         <v>45316</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>45643</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>45999</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>45884</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30176,7 +30176,7 @@
         <v>46003</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30254,7 +30254,7 @@
         <v>45764</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30327,7 +30327,7 @@
         <v>44648</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>45212</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>45408</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>45884</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30629,7 +30629,7 @@
         <v>45476</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>45944</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30775,7 +30775,7 @@
         <v>44566</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30848,7 +30848,7 @@
         <v>45551</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>45860</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -31004,7 +31004,7 @@
         <v>45764</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -31077,7 +31077,7 @@
         <v>45446</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -31150,7 +31150,7 @@
         <v>45649</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31223,7 +31223,7 @@
         <v>45132</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31296,7 +31296,7 @@
         <v>45649</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31369,7 +31369,7 @@
         <v>45891</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31442,7 +31442,7 @@
         <v>45649</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31515,7 +31515,7 @@
         <v>45649</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>45935</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31661,7 +31661,7 @@
         <v>45764</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31734,7 +31734,7 @@
         <v>45897</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>45897</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>45105</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31953,7 +31953,7 @@
         <v>45201</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -32026,7 +32026,7 @@
         <v>45099</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -32099,7 +32099,7 @@
         <v>45839</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32172,7 +32172,7 @@
         <v>44994</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32245,7 +32245,7 @@
         <v>44486</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>45728</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32396,7 +32396,7 @@
         <v>46029</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>45586</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>45901</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>45902</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32703,7 +32703,7 @@
         <v>46084</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32776,7 +32776,7 @@
         <v>45583</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32854,7 +32854,7 @@
         <v>46076</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>45832</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>45818</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>45341</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>45645</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>45561</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33302,7 +33302,7 @@
         <v>45907</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>45911</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>45257</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>45910</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33604,7 +33604,7 @@
         <v>45910</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>44522</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>45912</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33833,7 +33833,7 @@
         <v>45915</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33911,7 +33911,7 @@
         <v>45915</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>45912</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -34057,7 +34057,7 @@
         <v>45912</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -34130,7 +34130,7 @@
         <v>45915</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>45596</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>45587</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34354,7 +34354,7 @@
         <v>46147</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>45893</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>45919</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34583,7 +34583,7 @@
         <v>45919</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34661,7 +34661,7 @@
         <v>45685</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34734,7 +34734,7 @@
         <v>45922</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>45841</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34880,7 +34880,7 @@
         <v>45922</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>45922</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -35026,7 +35026,7 @@
         <v>45925</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>45925</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>46148</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>44994</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>45924</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>46149</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35469,7 +35469,7 @@
         <v>45926</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35547,7 +35547,7 @@
         <v>45926</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35620,7 +35620,7 @@
         <v>45926</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35693,7 +35693,7 @@
         <v>46149</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -35766,7 +35766,7 @@
         <v>45931</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>46150</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>45930</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35995,7 +35995,7 @@
         <v>45930</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -36073,7 +36073,7 @@
         <v>45933</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>45906</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>46150</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36297,7 +36297,7 @@
         <v>45933</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36375,7 +36375,7 @@
         <v>45933</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36453,7 +36453,7 @@
         <v>45512</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36526,7 +36526,7 @@
         <v>46150</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36599,7 +36599,7 @@
         <v>44889</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>45938</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36750,7 +36750,7 @@
         <v>45937</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36823,7 +36823,7 @@
         <v>45406</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>45771</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36969,7 +36969,7 @@
         <v>45408</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -37042,7 +37042,7 @@
         <v>45938</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -37115,7 +37115,7 @@
         <v>44881</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -37193,7 +37193,7 @@
         <v>45938</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>45939</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37349,7 +37349,7 @@
         <v>45943</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37422,7 +37422,7 @@
         <v>45587</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37495,7 +37495,7 @@
         <v>45945</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37573,7 +37573,7 @@
         <v>45945</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37646,7 +37646,7 @@
         <v>45944</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37724,7 +37724,7 @@
         <v>45248</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -37797,7 +37797,7 @@
         <v>45944</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>46154</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37943,7 +37943,7 @@
         <v>45646</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -38016,7 +38016,7 @@
         <v>45944</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -38094,7 +38094,7 @@
         <v>45944</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>45945</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38240,7 +38240,7 @@
         <v>46155</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>45944</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38391,7 +38391,7 @@
         <v>45639</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>45691</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>44648</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38620,7 +38620,7 @@
         <v>45947</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38698,7 +38698,7 @@
         <v>44565</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38771,7 +38771,7 @@
         <v>46154</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>45950</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38922,7 +38922,7 @@
         <v>45988</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38995,7 +38995,7 @@
         <v>44490</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -39073,7 +39073,7 @@
         <v>45953</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>45953</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -39224,7 +39224,7 @@
         <v>45427</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39297,7 +39297,7 @@
         <v>45953</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39375,7 +39375,7 @@
         <v>45649</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45440</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39521,7 +39521,7 @@
         <v>45574</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39599,7 +39599,7 @@
         <v>45950</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>45955</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>45955</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>45301</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39896,7 +39896,7 @@
         <v>45761</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39969,7 +39969,7 @@
         <v>45960</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -40047,7 +40047,7 @@
         <v>45818</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -40125,7 +40125,7 @@
         <v>45744</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -40198,7 +40198,7 @@
         <v>45750</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
         <v>45691</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40349,7 +40349,7 @@
         <v>45961</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40422,7 +40422,7 @@
         <v>45965</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40495,7 +40495,7 @@
         <v>45965</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40568,7 +40568,7 @@
         <v>45965</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40641,7 +40641,7 @@
         <v>45965</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45964</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -40787,7 +40787,7 @@
         <v>45966</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40860,7 +40860,7 @@
         <v>45264</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40933,7 +40933,7 @@
         <v>45875</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -41006,7 +41006,7 @@
         <v>45971</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -41079,7 +41079,7 @@
         <v>45692</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41152,7 +41152,7 @@
         <v>45972</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -41225,7 +41225,7 @@
         <v>45975</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41303,7 +41303,7 @@
         <v>45975</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41381,7 +41381,7 @@
         <v>45975</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41459,7 +41459,7 @@
         <v>44903</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41532,7 +41532,7 @@
         <v>45770</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41605,7 +41605,7 @@
         <v>45978</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41678,7 +41678,7 @@
         <v>45672</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41751,7 +41751,7 @@
         <v>45978</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41829,7 +41829,7 @@
         <v>45590</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41907,7 +41907,7 @@
         <v>45591</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>45591</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>45981</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42141,7 +42141,7 @@
         <v>45981</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>45425</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42292,7 +42292,7 @@
         <v>45674</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42365,7 +42365,7 @@
         <v>45894</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42443,7 +42443,7 @@
         <v>45984</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>45985</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>44657</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42662,7 +42662,7 @@
         <v>46164</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42740,7 +42740,7 @@
         <v>46164</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -42818,7 +42818,7 @@
         <v>46164</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42896,7 +42896,7 @@
         <v>44847</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45986</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -43042,7 +43042,7 @@
         <v>45988</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -43115,7 +43115,7 @@
         <v>45210</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43193,7 +43193,7 @@
         <v>46164</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -43271,7 +43271,7 @@
         <v>45988</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>44573</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43422,7 +43422,7 @@
         <v>44859</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43500,7 +43500,7 @@
         <v>45544</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43573,7 +43573,7 @@
         <v>45314</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43646,7 +43646,7 @@
         <v>45429</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>46168</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43792,7 +43792,7 @@
         <v>46168</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43865,7 +43865,7 @@
         <v>45995</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45995</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -44011,7 +44011,7 @@
         <v>45994</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -44084,7 +44084,7 @@
         <v>45994</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44157,7 +44157,7 @@
         <v>46168</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44230,7 +44230,7 @@
         <v>46168</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44303,7 +44303,7 @@
         <v>45995</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44376,7 +44376,7 @@
         <v>45995</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44449,7 +44449,7 @@
         <v>45995</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45994</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44595,7 +44595,7 @@
         <v>45994</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44668,7 +44668,7 @@
         <v>45994</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44741,7 +44741,7 @@
         <v>45996</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -44814,7 +44814,7 @@
         <v>46168</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44887,7 +44887,7 @@
         <v>44963</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44960,7 +44960,7 @@
         <v>45999</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -45033,7 +45033,7 @@
         <v>45505</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45111,7 +45111,7 @@
         <v>45906</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45184,7 +45184,7 @@
         <v>46000</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>46001</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>44979</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>46001</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45481,7 +45481,7 @@
         <v>46003</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>46172</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>46003</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>46001</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -45778,7 +45778,7 @@
         <v>45470</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>46171</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45929,7 +45929,7 @@
         <v>46009</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -46002,7 +46002,7 @@
         <v>46009</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -46075,7 +46075,7 @@
         <v>46008</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>45994</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>46174</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>46009</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46367,7 +46367,7 @@
         <v>45902</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         <v>44529</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46518,7 +46518,7 @@
         <v>46012</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46591,7 +46591,7 @@
         <v>46012</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46664,7 +46664,7 @@
         <v>45574</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -46742,7 +46742,7 @@
         <v>45764</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46815,7 +46815,7 @@
         <v>46020</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46888,7 +46888,7 @@
         <v>46066</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46961,7 +46961,7 @@
         <v>46066</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -47034,7 +47034,7 @@
         <v>46029</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -47107,7 +47107,7 @@
         <v>45014</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -47180,7 +47180,7 @@
         <v>46030</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -47258,7 +47258,7 @@
         <v>46030</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47336,7 +47336,7 @@
         <v>46030</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47414,7 +47414,7 @@
         <v>44964</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47492,7 +47492,7 @@
         <v>45770</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47565,7 +47565,7 @@
         <v>46020</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47638,7 +47638,7 @@
         <v>45254</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47711,7 +47711,7 @@
         <v>46175</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>46178</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47862,7 +47862,7 @@
         <v>45356</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47935,7 +47935,7 @@
         <v>46177</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -48013,7 +48013,7 @@
         <v>44796</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>46042</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -48159,7 +48159,7 @@
         <v>46042</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -48232,7 +48232,7 @@
         <v>46177</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -48310,7 +48310,7 @@
         <v>46170</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48388,7 +48388,7 @@
         <v>45694</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48466,7 +48466,7 @@
         <v>46048</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -48539,7 +48539,7 @@
         <v>45523</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -48617,7 +48617,7 @@
         <v>45149</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -48690,7 +48690,7 @@
         <v>46181</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -48768,7 +48768,7 @@
         <v>46050</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -48841,7 +48841,7 @@
         <v>45054</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48914,7 +48914,7 @@
         <v>45429</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>46182</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>46052</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -49138,7 +49138,7 @@
         <v>45085</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -49211,7 +49211,7 @@
         <v>46056</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         <v>46056</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -49357,7 +49357,7 @@
         <v>46183</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -49430,7 +49430,7 @@
         <v>46057</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>46059</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -49576,7 +49576,7 @@
         <v>45281</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -49654,7 +49654,7 @@
         <v>46058</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -49727,7 +49727,7 @@
         <v>46184</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -49805,7 +49805,7 @@
         <v>46184</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -49903,7 +49903,7 @@
         <v>46062</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49976,7 +49976,7 @@
         <v>46063</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -50049,7 +50049,7 @@
         <v>46063</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -50122,7 +50122,7 @@
         <v>46183</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -50200,7 +50200,7 @@
         <v>46065</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -50278,7 +50278,7 @@
         <v>46184</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -50356,7 +50356,7 @@
         <v>44903</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -50429,7 +50429,7 @@
         <v>45210</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>46078</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>46076</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -50653,7 +50653,7 @@
         <v>46076</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -50726,7 +50726,7 @@
         <v>46076</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -50799,7 +50799,7 @@
         <v>46185</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -50872,7 +50872,7 @@
         <v>44524</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -50945,7 +50945,7 @@
         <v>45212</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -51023,7 +51023,7 @@
         <v>46084</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -51096,7 +51096,7 @@
         <v>46084</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -51169,7 +51169,7 @@
         <v>46084</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -51242,7 +51242,7 @@
         <v>46084</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -51315,7 +51315,7 @@
         <v>46084</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -51388,7 +51388,7 @@
         <v>44706</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -51461,7 +51461,7 @@
         <v>46086</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>44747</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>44673</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -51680,7 +51680,7 @@
         <v>46087</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -51758,7 +51758,7 @@
         <v>45548</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -51831,7 +51831,7 @@
         <v>44657</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>44657</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51977,7 +51977,7 @@
         <v>46191</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -52050,7 +52050,7 @@
         <v>46097</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -52128,7 +52128,7 @@
         <v>45922</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -52201,7 +52201,7 @@
         <v>44966</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -52279,7 +52279,7 @@
         <v>46100</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -52352,7 +52352,7 @@
         <v>45761</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -52430,7 +52430,7 @@
         <v>46099</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -52508,7 +52508,7 @@
         <v>46196</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -52581,7 +52581,7 @@
         <v>45593</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -52659,7 +52659,7 @@
         <v>46105</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -52732,7 +52732,7 @@
         <v>45643</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -52805,7 +52805,7 @@
         <v>46197</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -52883,7 +52883,7 @@
         <v>46198</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52956,7 +52956,7 @@
         <v>46197</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45429</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -53102,7 +53102,7 @@
         <v>45429</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -53175,7 +53175,7 @@
         <v>46197</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -53248,7 +53248,7 @@
         <v>45085</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -53321,7 +53321,7 @@
         <v>46197</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -53394,7 +53394,7 @@
         <v>45980</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -53467,7 +53467,7 @@
         <v>46122</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -53545,7 +53545,7 @@
         <v>46202</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -53623,7 +53623,7 @@
         <v>46202</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         <v>45483</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -53774,7 +53774,7 @@
         <v>46122</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53847,7 +53847,7 @@
         <v>45153</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -53920,7 +53920,7 @@
         <v>46126</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53993,7 +53993,7 @@
         <v>45509</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -54066,7 +54066,7 @@
         <v>46126</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -54139,7 +54139,7 @@
         <v>46202</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -54217,7 +54217,7 @@
         <v>46127</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -54290,7 +54290,7 @@
         <v>45256</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -54363,7 +54363,7 @@
         <v>45562</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -54441,7 +54441,7 @@
         <v>45653</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -54514,7 +54514,7 @@
         <v>46132</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -54592,7 +54592,7 @@
         <v>45247</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -54665,7 +54665,7 @@
         <v>46203</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -54738,7 +54738,7 @@
         <v>46132</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -54811,7 +54811,7 @@
         <v>46132</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -54889,7 +54889,7 @@
         <v>46132</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54967,7 +54967,7 @@
         <v>46204</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -55040,7 +55040,7 @@
         <v>46007</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -55113,7 +55113,7 @@
         <v>45499</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -55186,7 +55186,7 @@
         <v>46204</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -55259,7 +55259,7 @@
         <v>46204</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -55332,7 +55332,7 @@
         <v>46136</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -55410,7 +55410,7 @@
         <v>45156</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -55483,7 +55483,7 @@
         <v>46076</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -55556,7 +55556,7 @@
         <v>44642</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -55634,7 +55634,7 @@
         <v>45070</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>44901</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -55780,7 +55780,7 @@
         <v>46003</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55853,7 +55853,7 @@
         <v>46029</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -55926,7 +55926,7 @@
         <v>45195</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -56004,7 +56004,7 @@
         <v>46206</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -56082,7 +56082,7 @@
         <v>46206</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -56160,7 +56160,7 @@
         <v>45649</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>46208</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -56306,7 +56306,7 @@
         <v>46206</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -56384,7 +56384,7 @@
         <v>45589</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -56462,7 +56462,7 @@
         <v>45589</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -56540,7 +56540,7 @@
         <v>46211</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -56613,7 +56613,7 @@
         <v>46209</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -56691,7 +56691,7 @@
         <v>46209</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -56769,7 +56769,7 @@
         <v>46209</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -56847,7 +56847,7 @@
         <v>45460</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -56925,7 +56925,7 @@
         <v>45350</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56998,7 +56998,7 @@
         <v>44732</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -57071,7 +57071,7 @@
         <v>45677</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -57149,7 +57149,7 @@
         <v>44908</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -57222,7 +57222,7 @@
         <v>45924</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -57295,7 +57295,7 @@
         <v>45216</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -57373,7 +57373,7 @@
         <v>44726</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -57446,7 +57446,7 @@
         <v>46217</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -57524,7 +57524,7 @@
         <v>44566</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -57597,7 +57597,7 @@
         <v>45894</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -57670,7 +57670,7 @@
         <v>46217</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -57748,7 +57748,7 @@
         <v>46217</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -57826,7 +57826,7 @@
         <v>46217</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -57904,7 +57904,7 @@
         <v>44841</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57982,7 +57982,7 @@
         <v>46168</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -58055,7 +58055,7 @@
         <v>45356</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -58128,7 +58128,7 @@
         <v>46225</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -58206,7 +58206,7 @@
         <v>46029</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -58279,7 +58279,7 @@
         <v>46272</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -58357,7 +58357,7 @@
         <v>46273</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -58435,7 +58435,7 @@
         <v>44734</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -58508,7 +58508,7 @@
         <v>45653</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -58581,7 +58581,7 @@
         <v>46270</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -58654,7 +58654,7 @@
         <v>45770</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -58727,7 +58727,7 @@
         <v>45544</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -58800,7 +58800,7 @@
         <v>46274</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58873,7 +58873,7 @@
         <v>46274</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -58946,7 +58946,7 @@
         <v>46275</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -59019,7 +59019,7 @@
         <v>46275</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -59092,7 +59092,7 @@
         <v>46274</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -59165,7 +59165,7 @@
         <v>46274</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -59243,7 +59243,7 @@
         <v>44795</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -59316,7 +59316,7 @@
         <v>46275</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -59394,7 +59394,7 @@
         <v>45161</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -59467,7 +59467,7 @@
         <v>46275</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -59540,7 +59540,7 @@
         <v>46275</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59613,7 +59613,7 @@
         <v>46234</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -59691,7 +59691,7 @@
         <v>46276</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -59764,7 +59764,7 @@
         <v>46276</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59837,7 +59837,7 @@
         <v>46234</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -59915,7 +59915,7 @@
         <v>46234</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59993,7 +59993,7 @@
         <v>45194</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -60071,7 +60071,7 @@
         <v>44908</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -60144,7 +60144,7 @@
         <v>45358</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -60217,7 +60217,7 @@
         <v>46281</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -60295,7 +60295,7 @@
         <v>46281</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -60373,7 +60373,7 @@
         <v>45680</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -60451,7 +60451,7 @@
         <v>45187</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -60529,7 +60529,7 @@
         <v>46238</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -60607,7 +60607,7 @@
         <v>46281</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -60680,7 +60680,7 @@
         <v>46238</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -60758,7 +60758,7 @@
         <v>46281</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60836,7 +60836,7 @@
         <v>44887</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -60914,7 +60914,7 @@
         <v>45166</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60992,7 +60992,7 @@
         <v>45653</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -61065,7 +61065,7 @@
         <v>45174</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -61138,7 +61138,7 @@
         <v>46283</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -61216,7 +61216,7 @@
         <v>45323</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -61289,7 +61289,7 @@
         <v>46239</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -61367,7 +61367,7 @@
         <v>46240</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -61440,7 +61440,7 @@
         <v>44931</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -61513,7 +61513,7 @@
         <v>45001</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -61586,7 +61586,7 @@
         <v>46240</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -61664,7 +61664,7 @@
         <v>46283</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -61742,7 +61742,7 @@
         <v>45772</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -61815,7 +61815,7 @@
         <v>45770</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -61888,7 +61888,7 @@
         <v>44964</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -61966,7 +61966,7 @@
         <v>45832</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -62039,7 +62039,7 @@
         <v>46287</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -62117,7 +62117,7 @@
         <v>46202</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -62190,7 +62190,7 @@
         <v>45035</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -62263,7 +62263,7 @@
         <v>45856</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -62341,7 +62341,7 @@
         <v>45476</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -62414,7 +62414,7 @@
         <v>45093</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -62492,7 +62492,7 @@
         <v>44883</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -62570,7 +62570,7 @@
         <v>45529</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -62643,7 +62643,7 @@
         <v>45099</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -62716,7 +62716,7 @@
         <v>46197</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -62789,7 +62789,7 @@
         <v>46287</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -62867,7 +62867,7 @@
         <v>45454</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -62940,7 +62940,7 @@
         <v>44614</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -63013,7 +63013,7 @@
         <v>45079</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -63086,7 +63086,7 @@
         <v>45762</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -63159,7 +63159,7 @@
         <v>46246</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -63232,7 +63232,7 @@
         <v>45646</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -63305,7 +63305,7 @@
         <v>45205</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -63378,7 +63378,7 @@
         <v>45233</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -63456,7 +63456,7 @@
         <v>46289</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -63529,7 +63529,7 @@
         <v>45379</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -63602,7 +63602,7 @@
         <v>46293</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -63680,7 +63680,7 @@
         <v>45773</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -63758,7 +63758,7 @@
         <v>44994</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -63831,7 +63831,7 @@
         <v>46290</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -63909,7 +63909,7 @@
         <v>46293</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -63982,7 +63982,7 @@
         <v>44568</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -64055,7 +64055,7 @@
         <v>45572</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -64133,7 +64133,7 @@
         <v>45764</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -64206,7 +64206,7 @@
         <v>45764</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -64279,7 +64279,7 @@
         <v>45618</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -64357,7 +64357,7 @@
         <v>46293</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -64435,7 +64435,7 @@
         <v>45099</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -64508,7 +64508,7 @@
         <v>46248</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -64581,7 +64581,7 @@
         <v>44812</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -64654,7 +64654,7 @@
         <v>46293</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -64732,7 +64732,7 @@
         <v>44823</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -64810,7 +64810,7 @@
         <v>45625</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -64888,7 +64888,7 @@
         <v>46252</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -64966,7 +64966,7 @@
         <v>44856</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -65039,7 +65039,7 @@
         <v>46251</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -65117,7 +65117,7 @@
         <v>45013</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -65190,7 +65190,7 @@
         <v>44585</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -65263,7 +65263,7 @@
         <v>46294</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -65341,7 +65341,7 @@
         <v>45204</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -65414,7 +65414,7 @@
         <v>45687</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -65487,7 +65487,7 @@
         <v>46253</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -65560,7 +65560,7 @@
         <v>46251</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -65633,7 +65633,7 @@
         <v>46254</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -65706,7 +65706,7 @@
         <v>46254</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -65779,7 +65779,7 @@
         <v>45813</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -65857,7 +65857,7 @@
         <v>46297</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -65935,7 +65935,7 @@
         <v>46254</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -66013,7 +66013,7 @@
         <v>46296</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -66091,7 +66091,7 @@
         <v>46296</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -66169,7 +66169,7 @@
         <v>46029</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -66247,7 +66247,7 @@
         <v>44935</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -66320,7 +66320,7 @@
         <v>46299</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -66393,7 +66393,7 @@
         <v>45453</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -66466,7 +66466,7 @@
         <v>45646</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -66539,7 +66539,7 @@
         <v>45478</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -66612,7 +66612,7 @@
         <v>45391</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -66685,7 +66685,7 @@
         <v>45778</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -66763,7 +66763,7 @@
         <v>45782</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -66836,7 +66836,7 @@
         <v>46300</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -66914,7 +66914,7 @@
         <v>46301</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -66992,7 +66992,7 @@
         <v>46300</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -67070,7 +67070,7 @@
         <v>46300</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -67148,7 +67148,7 @@
         <v>46300</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -67226,7 +67226,7 @@
         <v>46255</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -67304,7 +67304,7 @@
         <v>46259</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -67382,7 +67382,7 @@
         <v>45149</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -67455,7 +67455,7 @@
         <v>45786</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -67533,7 +67533,7 @@
         <v>46259</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -67611,7 +67611,7 @@
         <v>45791</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -67689,7 +67689,7 @@
         <v>45379</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -67762,7 +67762,7 @@
         <v>46302</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -67835,7 +67835,7 @@
         <v>46259</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -67913,7 +67913,7 @@
         <v>46305</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -67991,7 +67991,7 @@
         <v>45793</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -68069,7 +68069,7 @@
         <v>46261</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -68142,7 +68142,7 @@
         <v>46261</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -68215,7 +68215,7 @@
         <v>46305</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -68293,7 +68293,7 @@
         <v>45590</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -68366,7 +68366,7 @@
         <v>45590</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -68439,7 +68439,7 @@
         <v>46261</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -68532,7 +68532,7 @@
         <v>45797</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -68610,7 +68610,7 @@
         <v>46306</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -68688,7 +68688,7 @@
         <v>46304</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -68766,7 +68766,7 @@
         <v>46261</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -68839,7 +68839,7 @@
         <v>46261</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -68917,7 +68917,7 @@
         <v>45799</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -68995,7 +68995,7 @@
         <v>46307</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -69073,7 +69073,7 @@
         <v>46307</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -69151,7 +69151,7 @@
         <v>45798</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -69229,7 +69229,7 @@
         <v>45798</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -69307,7 +69307,7 @@
         <v>44862</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -69380,7 +69380,7 @@
         <v>45798</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -69458,7 +69458,7 @@
         <v>45709</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -69536,7 +69536,7 @@
         <v>45803</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -69609,7 +69609,7 @@
         <v>45608</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -69682,7 +69682,7 @@
         <v>45608</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -69755,7 +69755,7 @@
         <v>45590</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -69828,7 +69828,7 @@
         <v>46266</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -69906,7 +69906,7 @@
         <v>45429</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -69979,7 +69979,7 @@
         <v>45464</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -70057,7 +70057,7 @@
         <v>45645</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -70130,7 +70130,7 @@
         <v>46309</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -70203,7 +70203,7 @@
         <v>45763</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -70276,7 +70276,7 @@
         <v>45546</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -70354,7 +70354,7 @@
         <v>45243</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -70427,7 +70427,7 @@
         <v>45813</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -70500,7 +70500,7 @@
         <v>46268</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -70578,7 +70578,7 @@
         <v>45813</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -70656,7 +70656,7 @@
         <v>46269</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -70734,7 +70734,7 @@
         <v>45316</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -70807,7 +70807,7 @@
         <v>45481</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -70885,7 +70885,7 @@
         <v>46268</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -70958,7 +70958,7 @@
         <v>45766</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -71036,7 +71036,7 @@
         <v>46306</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -71114,7 +71114,7 @@
         <v>46267</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -71187,7 +71187,7 @@
         <v>45818</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -71265,7 +71265,7 @@
         <v>45427</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -71338,7 +71338,7 @@
         <v>45818</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -71416,7 +71416,7 @@
         <v>45574</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -71494,7 +71494,7 @@
         <v>45818</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -71572,7 +71572,7 @@
         <v>46310</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -71650,7 +71650,7 @@
         <v>46268</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -71728,7 +71728,7 @@
         <v>46311</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -71801,7 +71801,7 @@
         <v>46311</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -71874,7 +71874,7 @@
         <v>46311</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -71952,7 +71952,7 @@
         <v>46311</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -72025,7 +72025,7 @@
         <v>46311</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -72098,7 +72098,7 @@
         <v>45826</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -72176,7 +72176,7 @@
         <v>45833</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -72254,7 +72254,7 @@
         <v>45833</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -72332,7 +72332,7 @@
         <v>45835</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -72410,7 +72410,7 @@
         <v>45803</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -72483,7 +72483,7 @@
         <v>45840</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -72561,7 +72561,7 @@
         <v>45840</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -72639,7 +72639,7 @@
         <v>45747</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -72712,7 +72712,7 @@
         <v>45843</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -72790,7 +72790,7 @@
         <v>45603</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -72863,7 +72863,7 @@
         <v>45796</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -72941,7 +72941,7 @@
         <v>45674</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -73014,7 +73014,7 @@
         <v>45596</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -73087,7 +73087,7 @@
         <v>45863</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -73160,7 +73160,7 @@
         <v>45456</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -73233,7 +73233,7 @@
         <v>45369</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -73306,7 +73306,7 @@
         <v>45838</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -73379,7 +73379,7 @@
         <v>45868</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -73457,7 +73457,7 @@
         <v>45877</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -73535,7 +73535,7 @@
         <v>45880</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -73613,7 +73613,7 @@
         <v>45881</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -73686,7 +73686,7 @@
         <v>45882</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -73759,7 +73759,7 @@
         <v>45882</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -73832,7 +73832,7 @@
         <v>45376</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -73910,7 +73910,7 @@
         <v>45013</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -73983,7 +73983,7 @@
         <v>45376</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -74061,7 +74061,7 @@
         <v>45667</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -74134,7 +74134,7 @@
         <v>44945</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -74212,7 +74212,7 @@
         <v>45743</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -74285,7 +74285,7 @@
         <v>45743</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -74358,7 +74358,7 @@
         <v>45789</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -74436,7 +74436,7 @@
         <v>45792</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -74509,7 +74509,7 @@
         <v>45799</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -74587,7 +74587,7 @@
         <v>45799</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -74665,7 +74665,7 @@
         <v>45799</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -74743,7 +74743,7 @@
         <v>45810</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -74821,7 +74821,7 @@
         <v>45818</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -74899,7 +74899,7 @@
         <v>45840</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -74977,7 +74977,7 @@
         <v>46018</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -75050,7 +75050,7 @@
         <v>46147</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -75123,7 +75123,7 @@
         <v>46147</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -75196,7 +75196,7 @@
         <v>46147</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -75274,7 +75274,7 @@
         <v>46152</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -75347,7 +75347,7 @@
         <v>46152</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -75420,7 +75420,7 @@
         <v>46148</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>

--- a/Översikt BODEN.xlsx
+++ b/Översikt BODEN.xlsx
@@ -601,7 +601,7 @@
         <v>45152</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45506</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>46315</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>45152</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>45068</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>45075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>46247</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>44853</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45152</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>46168</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>45105</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>44964</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>45790</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>45212</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>46149</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>44889</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45684</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>45771</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>44859</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>44853</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>46210</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45049</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45295</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>46195</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>44869</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>45418</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>45463</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>44795</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>45912</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>45912</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>44904</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>46209</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>45835</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>45893</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>45428</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>46309</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>45512</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>45964</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>46149</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>45912</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>46196</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>45988</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>46261</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>46315</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>46148</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>45307</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>45980</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>44833</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>45933</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>46181</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>45952</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>46184</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>45981</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>46205</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         <v>46217</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>46286</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>45698</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>45818</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>46073</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>46258</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>46240</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>46267</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>45791</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>46317</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>45077</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>45155</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         <v>44755</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>44648</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>44804</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>44796</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>44735</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         <v>44573</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>45803</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>45910</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         <v>46164</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>45922</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>44830</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>46184</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>45072</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>46205</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>46205</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>46205</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>45341</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>46217</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>46225</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>45638</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         <v>46066</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>46066</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>46286</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>46245</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>46247</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>45301</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>45820</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>46258</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>46304</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>46261</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>46261</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>45875</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>46184</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>46267</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>46311</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>46270</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         <v>45999</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>45834</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>45701</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>46149</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>45526</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45137</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>44678</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         <v>45645</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>44573</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
         <v>45517</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>45594</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>45376</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>44648</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>44840</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>45211</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>44925</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>45313</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>45901</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14784,7 +14784,7 @@
         <v>45905</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>45912</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>46168</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>45763</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>45936</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>45538</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>45944</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>46178</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>45947</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15762,7 +15762,7 @@
         <v>46178</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         <v>45949</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>45950</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>46178</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>45952</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>46183</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>45958</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>46184</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>45960</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>44529</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>45975</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>46205</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>45994</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>45999</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>46003</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>46236</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>46282</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>46240</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>45966</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>46241</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>45406</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>46048</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>46134</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45884</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>46251</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>46037</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>46255</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>46100</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>46302</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>46261</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>46261</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>46261</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>46261</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>45448</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>44648</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44529</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>46267</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>45559</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>45513</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>46311</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>46272</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>46272</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>46147</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20464,7 +20464,7 @@
         <v>44642</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>44692</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         <v>44944</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>45418</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20903,7 +20903,7 @@
         <v>45028</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21013,7 +21013,7 @@
         <v>45643</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21118,7 +21118,7 @@
         <v>45799</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>45901</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>45952</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>44509</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>44677</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>44577</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>44659</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>44671</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44852</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>44815</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21973,7 +21973,7 @@
         <v>44648</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>44617</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22124,7 +22124,7 @@
         <v>44648</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>44865</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>44609</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>44609</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>44671</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>44887</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>44721</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>44543</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22723,7 +22723,7 @@
         <v>44530</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>44648</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22874,7 +22874,7 @@
         <v>44734</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
         <v>44566</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>44566</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>44600</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -23171,7 +23171,7 @@
         <v>44749</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>44722</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23317,7 +23317,7 @@
         <v>44530</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23390,7 +23390,7 @@
         <v>44565</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23463,7 +23463,7 @@
         <v>44573</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>44566</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>44617</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>44820</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23765,7 +23765,7 @@
         <v>44625</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23838,7 +23838,7 @@
         <v>44596</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>44831</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>44799</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>44743</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>44799</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>44529</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24296,7 +24296,7 @@
         <v>44565</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>44635</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>44797</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>44796</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24593,7 +24593,7 @@
         <v>44796</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24666,7 +24666,7 @@
         <v>44795</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24744,7 +24744,7 @@
         <v>44931</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>44812</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>45649</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>44671</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>45649</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -25109,7 +25109,7 @@
         <v>45643</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>45764</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>45764</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>45187</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>45764</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>45891</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>45884</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>45591</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>45572</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>44734</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45897</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>45897</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>45014</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>45544</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>45001</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44964</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26307,7 +26307,7 @@
         <v>45902</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>45901</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>45907</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>45105</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>45910</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>44585</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>45910</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>45911</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26916,7 +26916,7 @@
         <v>45818</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>44847</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>45912</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>45875</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>45744</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -27291,7 +27291,7 @@
         <v>45691</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>45358</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>45356</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>46164</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         <v>46164</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27666,7 +27666,7 @@
         <v>45915</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27744,7 +27744,7 @@
         <v>45915</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>45915</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>46164</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27973,7 +27973,7 @@
         <v>46164</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -28051,7 +28051,7 @@
         <v>45674</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -28124,7 +28124,7 @@
         <v>45316</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
         <v>44552</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -28270,7 +28270,7 @@
         <v>44614</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28343,7 +28343,7 @@
         <v>46168</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28416,7 +28416,7 @@
         <v>45919</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>45919</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>45470</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>45922</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28723,7 +28723,7 @@
         <v>45922</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>46168</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>45922</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28942,7 +28942,7 @@
         <v>45894</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>45587</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -29093,7 +29093,7 @@
         <v>46168</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>45924</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>45926</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>45926</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29390,7 +29390,7 @@
         <v>46168</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44566</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>46168</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>45685</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>45926</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29755,7 +29755,7 @@
         <v>45925</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29828,7 +29828,7 @@
         <v>45925</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>45543</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>45930</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>45930</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>45763</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>46171</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>46172</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>45931</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>45246</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>44841</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>45933</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>46174</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30734,7 +30734,7 @@
         <v>45762</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>46175</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30880,7 +30880,7 @@
         <v>45906</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>45933</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -31031,7 +31031,7 @@
         <v>45476</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>45933</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -31182,7 +31182,7 @@
         <v>45937</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>45938</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>45938</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>45938</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31484,7 +31484,7 @@
         <v>45453</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>45939</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31635,7 +31635,7 @@
         <v>45944</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>45944</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31781,7 +31781,7 @@
         <v>45944</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31859,7 +31859,7 @@
         <v>45944</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31937,7 +31937,7 @@
         <v>45943</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>45944</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -32088,7 +32088,7 @@
         <v>46177</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>46177</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>45945</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
         <v>44935</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>45301</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>45254</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>45463</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45093</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32692,7 +32692,7 @@
         <v>45099</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>45646</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32838,7 +32838,7 @@
         <v>45945</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32911,7 +32911,7 @@
         <v>45945</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>45429</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -33062,7 +33062,7 @@
         <v>45356</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>46178</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>46181</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -33291,7 +33291,7 @@
         <v>45950</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -33364,7 +33364,7 @@
         <v>45947</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33442,7 +33442,7 @@
         <v>45770</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>45454</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33588,7 +33588,7 @@
         <v>45770</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33661,7 +33661,7 @@
         <v>45953</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33734,7 +33734,7 @@
         <v>45953</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>45953</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33890,7 +33890,7 @@
         <v>46170</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>46183</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>46182</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -34124,7 +34124,7 @@
         <v>45677</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -34202,7 +34202,7 @@
         <v>45950</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -34275,7 +34275,7 @@
         <v>45425</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -34348,7 +34348,7 @@
         <v>45771</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>45512</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34494,7 +34494,7 @@
         <v>45125</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34572,7 +34572,7 @@
         <v>46183</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34645,7 +34645,7 @@
         <v>45646</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34718,7 +34718,7 @@
         <v>45955</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34791,7 +34791,7 @@
         <v>45955</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         <v>46185</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34937,7 +34937,7 @@
         <v>45766</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -35015,7 +35015,7 @@
         <v>46184</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -35113,7 +35113,7 @@
         <v>46184</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -35191,7 +35191,7 @@
         <v>45960</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>46184</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45635</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>45961</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>45964</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>45099</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>45965</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>44657</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35785,7 +35785,7 @@
         <v>45965</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>45966</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>45965</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -36004,7 +36004,7 @@
         <v>45965</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>45264</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -36155,7 +36155,7 @@
         <v>46191</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>45350</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -36301,7 +36301,7 @@
         <v>45379</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>45205</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>46197</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36525,7 +36525,7 @@
         <v>45971</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36598,7 +36598,7 @@
         <v>46197</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>44558</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36744,7 +36744,7 @@
         <v>46197</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>46198</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36890,7 +36890,7 @@
         <v>46196</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36963,7 +36963,7 @@
         <v>46197</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -37036,7 +37036,7 @@
         <v>45643</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>45972</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -37182,7 +37182,7 @@
         <v>45975</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -37260,7 +37260,7 @@
         <v>45978</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -37338,7 +37338,7 @@
         <v>45035</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -37411,7 +37411,7 @@
         <v>45975</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37489,7 +37489,7 @@
         <v>45975</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>45978</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         <v>45341</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>46203</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>45653</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>46204</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37937,7 +37937,7 @@
         <v>46202</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>45174</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>46202</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>46202</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -38244,7 +38244,7 @@
         <v>44833</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>45254</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -38390,7 +38390,7 @@
         <v>44935</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>45981</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>45981</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>45985</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>46204</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38765,7 +38765,7 @@
         <v>46204</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38838,7 +38838,7 @@
         <v>45986</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>45984</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38984,7 +38984,7 @@
         <v>46209</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>46206</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -39140,7 +39140,7 @@
         <v>45988</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -39213,7 +39213,7 @@
         <v>45244</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>45653</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39364,7 +39364,7 @@
         <v>46206</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -39442,7 +39442,7 @@
         <v>45988</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>46206</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39593,7 +39593,7 @@
         <v>46208</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>46209</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39744,7 +39744,7 @@
         <v>46209</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39822,7 +39822,7 @@
         <v>46211</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>45672</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>45994</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>44883</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -40119,7 +40119,7 @@
         <v>45994</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -40192,7 +40192,7 @@
         <v>45994</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -40265,7 +40265,7 @@
         <v>45994</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>45994</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45770</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40484,7 +40484,7 @@
         <v>45476</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>45995</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>45995</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>45995</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45995</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>45996</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40922,7 +40922,7 @@
         <v>46217</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>45995</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>45764</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>45764</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -41219,7 +41219,7 @@
         <v>46217</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>46217</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>46217</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -41453,7 +41453,7 @@
         <v>45906</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41526,7 +41526,7 @@
         <v>45924</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41599,7 +41599,7 @@
         <v>45894</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>44881</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>45999</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41818,7 +41818,7 @@
         <v>45397</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
         <v>45397</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41964,7 +41964,7 @@
         <v>46000</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -42037,7 +42037,7 @@
         <v>46001</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>45391</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>46001</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -42256,7 +42256,7 @@
         <v>46168</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42329,7 +42329,7 @@
         <v>45778</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42407,7 +42407,7 @@
         <v>46001</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>46225</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>46003</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>45782</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42704,7 +42704,7 @@
         <v>46003</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42777,7 +42777,7 @@
         <v>46008</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>46234</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>46009</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>46009</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -43074,7 +43074,7 @@
         <v>45994</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>46009</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>46234</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -43298,7 +43298,7 @@
         <v>46012</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>46012</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>45902</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>46234</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>46281</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43673,7 +43673,7 @@
         <v>45786</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43751,7 +43751,7 @@
         <v>46020</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45149</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>46281</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43975,7 +43975,7 @@
         <v>46281</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -44053,7 +44053,7 @@
         <v>46281</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>46238</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>46238</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -44287,7 +44287,7 @@
         <v>46066</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44360,7 +44360,7 @@
         <v>46066</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>46239</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44511,7 +44511,7 @@
         <v>46030</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44589,7 +44589,7 @@
         <v>46030</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44667,7 +44667,7 @@
         <v>46029</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44740,7 +44740,7 @@
         <v>46030</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44818,7 +44818,7 @@
         <v>46240</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44891,7 +44891,7 @@
         <v>46240</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44969,7 +44969,7 @@
         <v>45379</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -45042,7 +45042,7 @@
         <v>46020</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -45115,7 +45115,7 @@
         <v>45791</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>45856</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -45271,7 +45271,7 @@
         <v>46283</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45349,7 +45349,7 @@
         <v>45419</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45422,7 +45422,7 @@
         <v>45832</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45495,7 +45495,7 @@
         <v>46283</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>46042</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>46042</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>45793</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45797,7 +45797,7 @@
         <v>45590</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45870,7 +45870,7 @@
         <v>45590</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45943,7 +45943,7 @@
         <v>46197</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -46016,7 +46016,7 @@
         <v>45798</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -46094,7 +46094,7 @@
         <v>45798</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -46172,7 +46172,7 @@
         <v>45797</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45798</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -46328,7 +46328,7 @@
         <v>44862</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46401,7 +46401,7 @@
         <v>46287</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46479,7 +46479,7 @@
         <v>46048</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46552,7 +46552,7 @@
         <v>46202</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46625,7 +46625,7 @@
         <v>46287</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46703,7 +46703,7 @@
         <v>45799</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46781,7 +46781,7 @@
         <v>46050</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46854,7 +46854,7 @@
         <v>45803</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>46052</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -47000,7 +47000,7 @@
         <v>45590</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>46290</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -47151,7 +47151,7 @@
         <v>45608</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -47224,7 +47224,7 @@
         <v>46289</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>45608</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>46056</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -47443,7 +47443,7 @@
         <v>45763</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -47516,7 +47516,7 @@
         <v>46056</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47589,7 +47589,7 @@
         <v>45546</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47667,7 +47667,7 @@
         <v>46057</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47740,7 +47740,7 @@
         <v>46246</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>45464</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47891,7 +47891,7 @@
         <v>46058</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47964,7 +47964,7 @@
         <v>45243</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         <v>45645</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -48110,7 +48110,7 @@
         <v>45429</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -48183,7 +48183,7 @@
         <v>46062</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>46293</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -48329,7 +48329,7 @@
         <v>46059</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -48402,7 +48402,7 @@
         <v>46293</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -48480,7 +48480,7 @@
         <v>46063</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>46063</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48626,7 +48626,7 @@
         <v>45813</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48704,7 +48704,7 @@
         <v>45813</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         <v>45766</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -48855,7 +48855,7 @@
         <v>46293</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -48933,7 +48933,7 @@
         <v>46065</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45818</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -49089,7 +49089,7 @@
         <v>45818</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -49167,7 +49167,7 @@
         <v>45316</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -49240,7 +49240,7 @@
         <v>45427</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -49313,7 +49313,7 @@
         <v>45574</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -49391,7 +49391,7 @@
         <v>45481</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>46294</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -49547,7 +49547,7 @@
         <v>45818</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -49625,7 +49625,7 @@
         <v>45516</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>45516</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -49781,7 +49781,7 @@
         <v>46293</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>46248</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -49932,7 +49932,7 @@
         <v>46029</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -50010,7 +50010,7 @@
         <v>46296</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -50088,7 +50088,7 @@
         <v>46076</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>46076</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -50234,7 +50234,7 @@
         <v>46253</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>46296</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -50385,7 +50385,7 @@
         <v>46076</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -50458,7 +50458,7 @@
         <v>46251</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -50536,7 +50536,7 @@
         <v>45826</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -50614,7 +50614,7 @@
         <v>46078</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -50687,7 +50687,7 @@
         <v>46084</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -50760,7 +50760,7 @@
         <v>46252</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>46084</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -50911,7 +50911,7 @@
         <v>46084</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -50984,7 +50984,7 @@
         <v>46084</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -51057,7 +51057,7 @@
         <v>45813</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -51135,7 +51135,7 @@
         <v>46084</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -51208,7 +51208,7 @@
         <v>45833</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -51286,7 +51286,7 @@
         <v>46086</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -51359,7 +51359,7 @@
         <v>46254</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -51437,7 +51437,7 @@
         <v>46087</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -51515,7 +51515,7 @@
         <v>45833</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -51593,7 +51593,7 @@
         <v>46251</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -51666,7 +51666,7 @@
         <v>45803</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -51739,7 +51739,7 @@
         <v>46297</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -51817,7 +51817,7 @@
         <v>46300</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>45835</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -51973,7 +51973,7 @@
         <v>46254</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -52046,7 +52046,7 @@
         <v>46254</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -52119,7 +52119,7 @@
         <v>46300</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -52197,7 +52197,7 @@
         <v>45840</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -52275,7 +52275,7 @@
         <v>45922</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -52348,7 +52348,7 @@
         <v>46097</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -52426,7 +52426,7 @@
         <v>45747</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -52499,7 +52499,7 @@
         <v>45840</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -52577,7 +52577,7 @@
         <v>46099</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -52655,7 +52655,7 @@
         <v>46255</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -52733,7 +52733,7 @@
         <v>46299</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>45761</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -52884,7 +52884,7 @@
         <v>46300</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -52962,7 +52962,7 @@
         <v>45527</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -53035,7 +53035,7 @@
         <v>46300</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -53113,7 +53113,7 @@
         <v>46100</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -53186,7 +53186,7 @@
         <v>46302</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -53259,7 +53259,7 @@
         <v>45843</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>46105</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -53410,7 +53410,7 @@
         <v>46259</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -53488,7 +53488,7 @@
         <v>45589</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -53566,7 +53566,7 @@
         <v>46259</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -53644,7 +53644,7 @@
         <v>45603</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -53717,7 +53717,7 @@
         <v>46259</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -53795,7 +53795,7 @@
         <v>46301</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -53873,7 +53873,7 @@
         <v>45674</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -53946,7 +53946,7 @@
         <v>45596</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -54019,7 +54019,7 @@
         <v>45796</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -54097,7 +54097,7 @@
         <v>45863</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -54170,7 +54170,7 @@
         <v>46261</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -54243,7 +54243,7 @@
         <v>46304</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -54321,7 +54321,7 @@
         <v>46261</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -54399,7 +54399,7 @@
         <v>45980</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -54472,7 +54472,7 @@
         <v>46261</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -54545,7 +54545,7 @@
         <v>45838</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -54618,7 +54618,7 @@
         <v>45456</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -54691,7 +54691,7 @@
         <v>46122</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -54769,7 +54769,7 @@
         <v>46122</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -54842,7 +54842,7 @@
         <v>46261</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -54915,7 +54915,7 @@
         <v>46126</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -54988,7 +54988,7 @@
         <v>46261</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -55081,7 +55081,7 @@
         <v>45369</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -55154,7 +55154,7 @@
         <v>46126</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -55227,7 +55227,7 @@
         <v>45868</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -55305,7 +55305,7 @@
         <v>46127</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -55378,7 +55378,7 @@
         <v>46132</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -55451,7 +55451,7 @@
         <v>45877</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -55529,7 +55529,7 @@
         <v>46305</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -55607,7 +55607,7 @@
         <v>46132</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -55685,7 +55685,7 @@
         <v>45880</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -55763,7 +55763,7 @@
         <v>46132</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -55841,7 +55841,7 @@
         <v>45881</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -55914,7 +55914,7 @@
         <v>45882</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -55987,7 +55987,7 @@
         <v>45882</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         <v>46132</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -56138,7 +56138,7 @@
         <v>46307</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -56216,7 +56216,7 @@
         <v>44908</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -56289,7 +56289,7 @@
         <v>45429</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -56362,7 +56362,7 @@
         <v>45429</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -56435,7 +56435,7 @@
         <v>45884</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -56513,7 +56513,7 @@
         <v>45446</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -56586,7 +56586,7 @@
         <v>46306</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -56664,7 +56664,7 @@
         <v>44994</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -56737,7 +56737,7 @@
         <v>45590</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -56815,7 +56815,7 @@
         <v>46307</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -56893,7 +56893,7 @@
         <v>46305</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -56971,7 +56971,7 @@
         <v>45204</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -57044,7 +57044,7 @@
         <v>44889</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -57117,7 +57117,7 @@
         <v>44901</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -57190,7 +57190,7 @@
         <v>46007</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -57263,7 +57263,7 @@
         <v>45709</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -57341,7 +57341,7 @@
         <v>46310</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -57419,7 +57419,7 @@
         <v>44903</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -57492,7 +57492,7 @@
         <v>44529</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -57565,7 +57565,7 @@
         <v>46309</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>46266</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -57716,7 +57716,7 @@
         <v>46268</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -57794,7 +57794,7 @@
         <v>46267</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -57867,7 +57867,7 @@
         <v>45691</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -57945,7 +57945,7 @@
         <v>46076</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -58018,7 +58018,7 @@
         <v>46311</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -58091,7 +58091,7 @@
         <v>46311</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -58164,7 +58164,7 @@
         <v>45935</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -58237,7 +58237,7 @@
         <v>46314</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -58315,7 +58315,7 @@
         <v>46268</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -58393,7 +58393,7 @@
         <v>46311</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -58471,7 +58471,7 @@
         <v>46311</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -58544,7 +58544,7 @@
         <v>45586</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -58622,7 +58622,7 @@
         <v>46268</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -58695,7 +58695,7 @@
         <v>44881</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -58768,7 +58768,7 @@
         <v>44966</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -58846,7 +58846,7 @@
         <v>46306</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -58924,7 +58924,7 @@
         <v>46269</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45750</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -59080,7 +59080,7 @@
         <v>46136</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -59158,7 +59158,7 @@
         <v>46311</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -59231,7 +59231,7 @@
         <v>45944</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -59304,7 +59304,7 @@
         <v>45832</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -59377,7 +59377,7 @@
         <v>45132</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -59450,7 +59450,7 @@
         <v>46003</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -59528,7 +59528,7 @@
         <v>45013</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -59601,7 +59601,7 @@
         <v>46270</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -59674,7 +59674,7 @@
         <v>45264</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -59747,7 +59747,7 @@
         <v>46272</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -59825,7 +59825,7 @@
         <v>45839</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -59898,7 +59898,7 @@
         <v>45860</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59976,7 +59976,7 @@
         <v>45818</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -60049,7 +60049,7 @@
         <v>46316</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -60127,7 +60127,7 @@
         <v>45653</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -60200,7 +60200,7 @@
         <v>45999</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -60273,7 +60273,7 @@
         <v>46273</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -60351,7 +60351,7 @@
         <v>46029</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -60424,7 +60424,7 @@
         <v>45645</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -60502,7 +60502,7 @@
         <v>46029</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -60575,7 +60575,7 @@
         <v>46315</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -60648,7 +60648,7 @@
         <v>46315</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -60726,7 +60726,7 @@
         <v>45408</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -60799,7 +60799,7 @@
         <v>46003</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -60872,7 +60872,7 @@
         <v>46076</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -60945,7 +60945,7 @@
         <v>45523</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -61023,7 +61023,7 @@
         <v>45587</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -61096,7 +61096,7 @@
         <v>46029</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -61169,7 +61169,7 @@
         <v>45583</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -61247,7 +61247,7 @@
         <v>46275</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -61320,7 +61320,7 @@
         <v>46275</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -61398,7 +61398,7 @@
         <v>46276</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -61471,7 +61471,7 @@
         <v>46274</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -61544,7 +61544,7 @@
         <v>46317</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -61617,7 +61617,7 @@
         <v>46317</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -61695,7 +61695,7 @@
         <v>46276</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -61768,7 +61768,7 @@
         <v>45649</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -61841,7 +61841,7 @@
         <v>45649</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -61914,7 +61914,7 @@
         <v>46275</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -61987,7 +61987,7 @@
         <v>46275</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -62060,7 +62060,7 @@
         <v>46084</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -62133,7 +62133,7 @@
         <v>46274</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -62206,7 +62206,7 @@
         <v>44726</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -62279,7 +62279,7 @@
         <v>45893</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -62357,7 +62357,7 @@
         <v>46317</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -62435,7 +62435,7 @@
         <v>46274</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -62513,7 +62513,7 @@
         <v>46274</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -62586,7 +62586,7 @@
         <v>45841</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -62659,7 +62659,7 @@
         <v>44642</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -62737,7 +62737,7 @@
         <v>46275</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -62810,7 +62810,7 @@
         <v>45548</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -62883,7 +62883,7 @@
         <v>45054</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -62956,7 +62956,7 @@
         <v>46148</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -63034,7 +63034,7 @@
         <v>44963</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -63107,7 +63107,7 @@
         <v>45238</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -63180,7 +63180,7 @@
         <v>46147</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -63253,7 +63253,7 @@
         <v>46150</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -63326,7 +63326,7 @@
         <v>46150</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -63399,7 +63399,7 @@
         <v>46150</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -63472,7 +63472,7 @@
         <v>46149</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -63545,7 +63545,7 @@
         <v>46149</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -63618,7 +63618,7 @@
         <v>46154</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -63696,7 +63696,7 @@
         <v>45764</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -63769,7 +63769,7 @@
         <v>45764</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -63842,7 +63842,7 @@
         <v>45770</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -63915,7 +63915,7 @@
         <v>44657</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -63988,7 +63988,7 @@
         <v>45408</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -64061,7 +64061,7 @@
         <v>44657</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -64134,7 +64134,7 @@
         <v>44994</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -64207,7 +64207,7 @@
         <v>45427</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -64280,7 +64280,7 @@
         <v>44673</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -64353,7 +64353,7 @@
         <v>46154</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -64426,7 +64426,7 @@
         <v>45562</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -64504,7 +64504,7 @@
         <v>45639</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -64577,7 +64577,7 @@
         <v>45589</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -64655,7 +64655,7 @@
         <v>45589</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -64733,7 +64733,7 @@
         <v>45988</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -64806,7 +64806,7 @@
         <v>45646</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -64879,7 +64879,7 @@
         <v>46155</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -64952,7 +64952,7 @@
         <v>45440</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -65025,7 +65025,7 @@
         <v>45625</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -65103,7 +65103,7 @@
         <v>44903</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -65176,7 +65176,7 @@
         <v>45212</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -65249,7 +65249,7 @@
         <v>45161</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -65327,7 +65327,7 @@
         <v>44994</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -65400,7 +65400,7 @@
         <v>45195</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -65478,7 +65478,7 @@
         <v>44796</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -65551,7 +65551,7 @@
         <v>45085</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -65624,7 +65624,7 @@
         <v>45153</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -65697,7 +65697,7 @@
         <v>45649</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -65770,7 +65770,7 @@
         <v>45149</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -65843,7 +65843,7 @@
         <v>44856</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -65916,7 +65916,7 @@
         <v>45103</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -65989,7 +65989,7 @@
         <v>44823</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -66067,7 +66067,7 @@
         <v>44568</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -66140,7 +66140,7 @@
         <v>45667</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -66213,7 +66213,7 @@
         <v>44648</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -66291,7 +66291,7 @@
         <v>45499</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -66364,7 +66364,7 @@
         <v>45194</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -66442,7 +66442,7 @@
         <v>45649</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -66515,7 +66515,7 @@
         <v>45764</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -66588,7 +66588,7 @@
         <v>45773</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -66666,7 +66666,7 @@
         <v>45672</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -66739,7 +66739,7 @@
         <v>45748</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -66812,7 +66812,7 @@
         <v>44524</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -66885,7 +66885,7 @@
         <v>45761</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -66958,7 +66958,7 @@
         <v>44881</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -67036,7 +67036,7 @@
         <v>45248</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -67109,7 +67109,7 @@
         <v>45210</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -67187,7 +67187,7 @@
         <v>44887</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -67265,7 +67265,7 @@
         <v>44565</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -67338,7 +67338,7 @@
         <v>45233</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -67416,7 +67416,7 @@
         <v>45070</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -67489,7 +67489,7 @@
         <v>45085</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -67562,7 +67562,7 @@
         <v>44529</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -67635,7 +67635,7 @@
         <v>45070</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -67708,7 +67708,7 @@
         <v>44812</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -67781,7 +67781,7 @@
         <v>45079</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -67854,7 +67854,7 @@
         <v>45102</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -67927,7 +67927,7 @@
         <v>45593</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -68005,7 +68005,7 @@
         <v>45406</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -68078,7 +68078,7 @@
         <v>44908</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -68151,7 +68151,7 @@
         <v>45099</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -68224,7 +68224,7 @@
         <v>45358</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -68297,7 +68297,7 @@
         <v>45110</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -68375,7 +68375,7 @@
         <v>45551</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -68453,7 +68453,7 @@
         <v>45544</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -68526,7 +68526,7 @@
         <v>45574</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -68604,7 +68604,7 @@
         <v>45574</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -68682,7 +68682,7 @@
         <v>45281</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -68760,7 +68760,7 @@
         <v>44529</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -68833,7 +68833,7 @@
         <v>45156</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -68906,7 +68906,7 @@
         <v>44983</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -68979,7 +68979,7 @@
         <v>45618</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -69057,7 +69057,7 @@
         <v>45604</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -69130,7 +69130,7 @@
         <v>45772</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -69203,7 +69203,7 @@
         <v>44522</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -69276,7 +69276,7 @@
         <v>45591</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -69354,7 +69354,7 @@
         <v>44609</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -69427,7 +69427,7 @@
         <v>45161</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -69505,7 +69505,7 @@
         <v>45161</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -69583,7 +69583,7 @@
         <v>45758</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -69656,7 +69656,7 @@
         <v>44795</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -69729,7 +69729,7 @@
         <v>45216</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -69807,7 +69807,7 @@
         <v>45596</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -69880,7 +69880,7 @@
         <v>45600</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -69953,7 +69953,7 @@
         <v>45600</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -70026,7 +70026,7 @@
         <v>44566</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -70099,7 +70099,7 @@
         <v>45478</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -70172,7 +70172,7 @@
         <v>45411</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -70245,7 +70245,7 @@
         <v>45310</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -70323,7 +70323,7 @@
         <v>44628</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -70396,7 +70396,7 @@
         <v>45561</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -70469,7 +70469,7 @@
         <v>45512</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -70542,7 +70542,7 @@
         <v>44859</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -70620,7 +70620,7 @@
         <v>45212</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -70698,7 +70698,7 @@
         <v>45687</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -70771,7 +70771,7 @@
         <v>45560</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -70849,7 +70849,7 @@
         <v>45770</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -70922,7 +70922,7 @@
         <v>45505</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -71000,7 +71000,7 @@
         <v>45460</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -71078,7 +71078,7 @@
         <v>45237</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -71151,7 +71151,7 @@
         <v>45210</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -71229,7 +71229,7 @@
         <v>45194</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -71307,7 +71307,7 @@
         <v>45161</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -71380,7 +71380,7 @@
         <v>44783</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -71453,7 +71453,7 @@
         <v>45201</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -71526,7 +71526,7 @@
         <v>45728</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -71604,7 +71604,7 @@
         <v>45246</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -71677,7 +71677,7 @@
         <v>45762</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -71750,7 +71750,7 @@
         <v>45166</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -71828,7 +71828,7 @@
         <v>45718</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -71901,7 +71901,7 @@
         <v>45247</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -71974,7 +71974,7 @@
         <v>45314</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -72047,7 +72047,7 @@
         <v>45256</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -72120,7 +72120,7 @@
         <v>45680</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -72198,7 +72198,7 @@
         <v>45254</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -72271,7 +72271,7 @@
         <v>45257</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -72344,7 +72344,7 @@
         <v>44648</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -72422,7 +72422,7 @@
         <v>45264</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -72500,7 +72500,7 @@
         <v>45356</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -72573,7 +72573,7 @@
         <v>45694</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -72651,7 +72651,7 @@
         <v>45260</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -72724,7 +72724,7 @@
         <v>45022</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -72797,7 +72797,7 @@
         <v>44573</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -72875,7 +72875,7 @@
         <v>45345</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -72948,7 +72948,7 @@
         <v>45483</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -73021,7 +73021,7 @@
         <v>45285</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -73094,7 +73094,7 @@
         <v>45529</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -73167,7 +73167,7 @@
         <v>44732</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -73240,7 +73240,7 @@
         <v>45323</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -73313,7 +73313,7 @@
         <v>44970</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -73386,7 +73386,7 @@
         <v>45210</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -73464,7 +73464,7 @@
         <v>45692</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -73537,7 +73537,7 @@
         <v>45509</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -73610,7 +73610,7 @@
         <v>45537</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -73688,7 +73688,7 @@
         <v>44964</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -73766,7 +73766,7 @@
         <v>45539</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -73839,7 +73839,7 @@
         <v>45429</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -73912,7 +73912,7 @@
         <v>44747</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -73985,7 +73985,7 @@
         <v>44706</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -74058,7 +74058,7 @@
         <v>44880</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -74131,7 +74131,7 @@
         <v>44979</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -74209,7 +74209,7 @@
         <v>45376</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -74287,7 +74287,7 @@
         <v>45013</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -74360,7 +74360,7 @@
         <v>45376</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -74438,7 +74438,7 @@
         <v>45667</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -74511,7 +74511,7 @@
         <v>44945</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -74589,7 +74589,7 @@
         <v>45743</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -74662,7 +74662,7 @@
         <v>45743</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -74735,7 +74735,7 @@
         <v>45789</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -74813,7 +74813,7 @@
         <v>45792</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -74886,7 +74886,7 @@
         <v>45799</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -74964,7 +74964,7 @@
         <v>45799</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -75042,7 +75042,7 @@
         <v>45799</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -75120,7 +75120,7 @@
         <v>45810</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -75198,7 +75198,7 @@
         <v>45818</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -75276,7 +75276,7 @@
         <v>45840</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -75354,7 +75354,7 @@
         <v>46018</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -75427,7 +75427,7 @@
         <v>46147</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -75500,7 +75500,7 @@
         <v>46147</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -75573,7 +75573,7 @@
         <v>46147</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -75651,7 +75651,7 @@
         <v>46152</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -75724,7 +75724,7 @@
         <v>46152</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -75797,7 +75797,7 @@
         <v>46148</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>

--- a/Översikt BODEN.xlsx
+++ b/Översikt BODEN.xlsx
@@ -601,7 +601,7 @@
         <v>45152</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45506</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>46315</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>45152</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>45068</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>45075</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>46247</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>44853</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45152</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>46168</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>45105</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>44964</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>45790</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>45212</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>46149</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>44889</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45684</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>45771</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>44859</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>44853</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>46210</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45049</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45295</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>46195</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>44869</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>45418</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>45463</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>44795</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>45912</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>45912</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>44904</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>46209</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>45835</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>45893</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>45428</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>46309</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>45512</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>45964</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>46149</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>45912</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>46196</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>45988</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>46261</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>46315</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>45980</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>46148</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>45307</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>45980</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>44833</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>45933</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>46181</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>45952</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>46184</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>45981</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>46205</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         <v>46217</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>46286</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>45698</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>45818</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>46073</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>46258</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>46240</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>46267</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>45791</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>46317</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>45077</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>45155</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         <v>44755</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>44648</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>44804</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>44796</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>44735</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         <v>44573</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>45803</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>45910</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         <v>46164</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>45922</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>44830</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>46184</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>45072</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>46205</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>46205</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>46205</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>45341</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>46217</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>46225</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>45638</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         <v>46066</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>46066</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>46286</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>46245</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>46247</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>45301</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>45820</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>46258</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>46304</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>46261</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>46261</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>45875</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>46184</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>46267</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>46311</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>46270</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         <v>45999</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>45834</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>45701</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>46149</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>45526</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45137</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>44678</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         <v>45645</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>44573</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
         <v>45517</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>45594</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>45376</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>44648</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>44840</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>45211</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>44925</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>45313</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>45901</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14784,7 +14784,7 @@
         <v>45905</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>45912</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>46168</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>45763</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>45936</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>45538</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>45944</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>46178</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>45947</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15762,7 +15762,7 @@
         <v>46178</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         <v>45949</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>45950</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>46178</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>45952</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>46183</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>45958</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>46184</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>45960</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>44529</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>45975</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>46205</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>45994</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>45999</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>46003</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>46236</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>46282</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>46240</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>45966</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>46241</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>45406</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>46048</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>46134</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45884</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>46251</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>46037</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>46255</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>46100</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>46302</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>46261</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>46261</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>46261</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>46261</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>45448</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>44648</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44529</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>46267</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>45559</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>45513</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>46311</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>46272</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>46272</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>46147</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20464,7 +20464,7 @@
         <v>44642</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>44692</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         <v>44944</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>45418</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20903,7 +20903,7 @@
         <v>45028</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21013,7 +21013,7 @@
         <v>45643</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21118,7 +21118,7 @@
         <v>45799</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>45901</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>45952</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>44509</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>44677</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>44577</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>44659</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>44671</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44852</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>44815</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21973,7 +21973,7 @@
         <v>44648</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>44617</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -22124,7 +22124,7 @@
         <v>44648</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>44865</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>44609</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>44609</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>44671</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>44887</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>44721</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>44543</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22723,7 +22723,7 @@
         <v>44530</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>44648</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22874,7 +22874,7 @@
         <v>44734</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
         <v>44566</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>44566</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>44600</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -23171,7 +23171,7 @@
         <v>44749</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>44722</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23317,7 +23317,7 @@
         <v>44530</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23390,7 +23390,7 @@
         <v>44565</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23463,7 +23463,7 @@
         <v>44573</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>44566</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>44617</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>44820</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23765,7 +23765,7 @@
         <v>44625</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23838,7 +23838,7 @@
         <v>44596</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>44831</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>44799</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>44743</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>44799</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>44529</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24296,7 +24296,7 @@
         <v>44565</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>44635</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>44797</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>44796</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24593,7 +24593,7 @@
         <v>44796</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24666,7 +24666,7 @@
         <v>44795</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24744,7 +24744,7 @@
         <v>44931</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>44812</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>45649</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>44671</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>45649</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -25109,7 +25109,7 @@
         <v>45643</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>45764</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>45764</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>45187</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>45764</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>45891</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>45884</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>45591</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>45572</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>44734</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45897</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>45897</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>45014</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>45544</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>45001</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44964</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26307,7 +26307,7 @@
         <v>45902</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>45901</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>45907</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>45105</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>45910</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>44585</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>45910</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>45911</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26916,7 +26916,7 @@
         <v>45818</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>44847</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>45912</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>45875</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>45744</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -27291,7 +27291,7 @@
         <v>45691</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>45358</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>45356</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>46164</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         <v>46164</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27666,7 +27666,7 @@
         <v>45915</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27744,7 +27744,7 @@
         <v>45915</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>45915</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>46164</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27973,7 +27973,7 @@
         <v>46164</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -28051,7 +28051,7 @@
         <v>45674</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -28124,7 +28124,7 @@
         <v>45316</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
         <v>44552</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -28270,7 +28270,7 @@
         <v>44614</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28343,7 +28343,7 @@
         <v>46168</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28416,7 +28416,7 @@
         <v>45919</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>45919</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>45470</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>45922</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28723,7 +28723,7 @@
         <v>45922</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>46168</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>45922</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28942,7 +28942,7 @@
         <v>45894</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>45587</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -29093,7 +29093,7 @@
         <v>46168</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>45924</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>45926</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>45926</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29390,7 +29390,7 @@
         <v>46168</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44566</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>46168</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>45685</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>45926</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29755,7 +29755,7 @@
         <v>45925</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29828,7 +29828,7 @@
         <v>45925</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>45543</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>45930</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>45930</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>45763</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>46171</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>46172</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>45931</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>45246</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>44841</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>45933</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>46174</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30734,7 +30734,7 @@
         <v>45762</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>46175</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30880,7 +30880,7 @@
         <v>45906</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>45933</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -31031,7 +31031,7 @@
         <v>45476</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>45933</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -31182,7 +31182,7 @@
         <v>45937</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>45938</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>45938</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>45938</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31484,7 +31484,7 @@
         <v>45453</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>45939</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31635,7 +31635,7 @@
         <v>45944</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>45944</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31781,7 +31781,7 @@
         <v>45944</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31859,7 +31859,7 @@
         <v>45944</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31937,7 +31937,7 @@
         <v>45943</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>45944</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -32088,7 +32088,7 @@
         <v>46177</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>46177</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>45945</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
         <v>44935</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>45301</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>45254</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>45463</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45093</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32692,7 +32692,7 @@
         <v>45099</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>45646</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32838,7 +32838,7 @@
         <v>45945</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32911,7 +32911,7 @@
         <v>45945</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>45429</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -33062,7 +33062,7 @@
         <v>45356</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>46178</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>46181</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -33291,7 +33291,7 @@
         <v>45950</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -33364,7 +33364,7 @@
         <v>45947</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33442,7 +33442,7 @@
         <v>45770</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>45454</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33588,7 +33588,7 @@
         <v>45770</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33661,7 +33661,7 @@
         <v>45953</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33734,7 +33734,7 @@
         <v>45953</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>45953</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33890,7 +33890,7 @@
         <v>46170</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>46183</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>46182</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -34124,7 +34124,7 @@
         <v>45677</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -34202,7 +34202,7 @@
         <v>45950</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -34275,7 +34275,7 @@
         <v>45425</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -34348,7 +34348,7 @@
         <v>45771</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>45512</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34494,7 +34494,7 @@
         <v>45125</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34572,7 +34572,7 @@
         <v>46183</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34645,7 +34645,7 @@
         <v>45646</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34718,7 +34718,7 @@
         <v>45955</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34791,7 +34791,7 @@
         <v>45955</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         <v>46185</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34937,7 +34937,7 @@
         <v>45766</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -35015,7 +35015,7 @@
         <v>46184</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -35113,7 +35113,7 @@
         <v>46184</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -35191,7 +35191,7 @@
         <v>45960</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>46184</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45635</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>45961</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>45964</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>45099</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>45965</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>44657</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35785,7 +35785,7 @@
         <v>45965</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>45966</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>45965</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -36004,7 +36004,7 @@
         <v>45965</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>45264</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -36155,7 +36155,7 @@
         <v>46191</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>45350</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -36301,7 +36301,7 @@
         <v>45379</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>45205</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>46197</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36525,7 +36525,7 @@
         <v>45971</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36598,7 +36598,7 @@
         <v>46197</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>44558</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36744,7 +36744,7 @@
         <v>46197</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>46198</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36890,7 +36890,7 @@
         <v>46196</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36963,7 +36963,7 @@
         <v>46197</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -37036,7 +37036,7 @@
         <v>45643</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>45972</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -37182,7 +37182,7 @@
         <v>45975</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -37260,7 +37260,7 @@
         <v>45978</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -37338,7 +37338,7 @@
         <v>45035</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -37411,7 +37411,7 @@
         <v>45975</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37489,7 +37489,7 @@
         <v>45975</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>45978</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         <v>45341</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>46203</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>45653</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>46204</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37937,7 +37937,7 @@
         <v>46202</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>45174</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>46202</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>46202</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -38244,7 +38244,7 @@
         <v>44833</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>45254</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -38390,7 +38390,7 @@
         <v>44935</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>45981</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>45981</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>45985</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>46204</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38765,7 +38765,7 @@
         <v>46204</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38838,7 +38838,7 @@
         <v>45986</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>45984</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38984,7 +38984,7 @@
         <v>46209</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>46206</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -39140,7 +39140,7 @@
         <v>45988</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -39213,7 +39213,7 @@
         <v>45244</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>45653</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -39364,7 +39364,7 @@
         <v>46206</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -39442,7 +39442,7 @@
         <v>45988</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>46206</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39593,7 +39593,7 @@
         <v>46208</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>46209</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39744,7 +39744,7 @@
         <v>46209</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39822,7 +39822,7 @@
         <v>46211</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>45672</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>45994</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>44883</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -40119,7 +40119,7 @@
         <v>45994</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -40192,7 +40192,7 @@
         <v>45994</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -40265,7 +40265,7 @@
         <v>45994</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>45994</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45770</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40484,7 +40484,7 @@
         <v>45476</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>45995</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>45995</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>45995</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45995</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>45996</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40922,7 +40922,7 @@
         <v>46217</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>45995</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>45764</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>45764</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -41219,7 +41219,7 @@
         <v>46217</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>46217</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>46217</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -41453,7 +41453,7 @@
         <v>45906</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41526,7 +41526,7 @@
         <v>45924</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41599,7 +41599,7 @@
         <v>45894</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>44881</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>45999</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41818,7 +41818,7 @@
         <v>45397</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
         <v>45397</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41964,7 +41964,7 @@
         <v>46000</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -42037,7 +42037,7 @@
         <v>46001</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>45391</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>46001</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -42256,7 +42256,7 @@
         <v>46168</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -42329,7 +42329,7 @@
         <v>45778</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -42407,7 +42407,7 @@
         <v>46001</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>46225</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>46003</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>45782</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42704,7 +42704,7 @@
         <v>46003</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42777,7 +42777,7 @@
         <v>46008</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>46234</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>46009</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>46009</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -43074,7 +43074,7 @@
         <v>45994</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>46009</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>46234</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -43298,7 +43298,7 @@
         <v>46012</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>46012</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>45902</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>46234</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>46281</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43673,7 +43673,7 @@
         <v>45786</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43751,7 +43751,7 @@
         <v>46020</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45149</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>46281</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43975,7 +43975,7 @@
         <v>46281</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -44053,7 +44053,7 @@
         <v>46281</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>46238</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>46238</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -44287,7 +44287,7 @@
         <v>46066</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -44360,7 +44360,7 @@
         <v>46066</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>46239</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44511,7 +44511,7 @@
         <v>46030</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44589,7 +44589,7 @@
         <v>46030</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44667,7 +44667,7 @@
         <v>46029</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44740,7 +44740,7 @@
         <v>46030</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44818,7 +44818,7 @@
         <v>46240</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44891,7 +44891,7 @@
         <v>46240</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44969,7 +44969,7 @@
         <v>45379</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -45042,7 +45042,7 @@
         <v>46020</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -45115,7 +45115,7 @@
         <v>45791</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>45856</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -45271,7 +45271,7 @@
         <v>46283</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -45349,7 +45349,7 @@
         <v>45419</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -45422,7 +45422,7 @@
         <v>45832</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -45495,7 +45495,7 @@
         <v>46283</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>46042</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>46042</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>45793</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45797,7 +45797,7 @@
         <v>45590</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45870,7 +45870,7 @@
         <v>45590</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45943,7 +45943,7 @@
         <v>46197</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -46016,7 +46016,7 @@
         <v>45798</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -46094,7 +46094,7 @@
         <v>45798</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -46172,7 +46172,7 @@
         <v>45797</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45798</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -46328,7 +46328,7 @@
         <v>44862</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -46401,7 +46401,7 @@
         <v>46287</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -46479,7 +46479,7 @@
         <v>46048</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46552,7 +46552,7 @@
         <v>46202</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46625,7 +46625,7 @@
         <v>46287</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46703,7 +46703,7 @@
         <v>45799</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46781,7 +46781,7 @@
         <v>46050</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46854,7 +46854,7 @@
         <v>45803</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>46052</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -47000,7 +47000,7 @@
         <v>45590</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>46290</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -47151,7 +47151,7 @@
         <v>45608</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -47224,7 +47224,7 @@
         <v>46289</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>45608</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>46056</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -47443,7 +47443,7 @@
         <v>45763</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -47516,7 +47516,7 @@
         <v>46056</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47589,7 +47589,7 @@
         <v>45546</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47667,7 +47667,7 @@
         <v>46057</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47740,7 +47740,7 @@
         <v>46246</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>45464</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47891,7 +47891,7 @@
         <v>46058</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47964,7 +47964,7 @@
         <v>45243</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         <v>45645</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -48110,7 +48110,7 @@
         <v>45429</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -48183,7 +48183,7 @@
         <v>46062</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>46293</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -48329,7 +48329,7 @@
         <v>46059</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -48402,7 +48402,7 @@
         <v>46293</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -48480,7 +48480,7 @@
         <v>46063</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>46063</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48626,7 +48626,7 @@
         <v>45813</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48704,7 +48704,7 @@
         <v>45813</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -48777,7 +48777,7 @@
         <v>45766</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -48855,7 +48855,7 @@
         <v>46293</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -48933,7 +48933,7 @@
         <v>46065</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45818</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -49089,7 +49089,7 @@
         <v>45818</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -49167,7 +49167,7 @@
         <v>45316</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -49240,7 +49240,7 @@
         <v>45427</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -49313,7 +49313,7 @@
         <v>45574</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -49391,7 +49391,7 @@
         <v>45481</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>46294</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -49547,7 +49547,7 @@
         <v>45818</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -49625,7 +49625,7 @@
         <v>45516</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>45516</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -49781,7 +49781,7 @@
         <v>46293</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>46248</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -49932,7 +49932,7 @@
         <v>46029</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -50010,7 +50010,7 @@
         <v>46296</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -50088,7 +50088,7 @@
         <v>46076</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>46076</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -50234,7 +50234,7 @@
         <v>46253</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>46296</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -50385,7 +50385,7 @@
         <v>46076</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -50458,7 +50458,7 @@
         <v>46251</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -50536,7 +50536,7 @@
         <v>45826</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -50614,7 +50614,7 @@
         <v>46078</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -50687,7 +50687,7 @@
         <v>46084</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -50760,7 +50760,7 @@
         <v>46252</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>46084</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -50911,7 +50911,7 @@
         <v>46084</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -50984,7 +50984,7 @@
         <v>46084</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -51057,7 +51057,7 @@
         <v>45813</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -51135,7 +51135,7 @@
         <v>46084</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -51208,7 +51208,7 @@
         <v>45833</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -51286,7 +51286,7 @@
         <v>46086</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -51359,7 +51359,7 @@
         <v>46254</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -51437,7 +51437,7 @@
         <v>46087</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -51515,7 +51515,7 @@
         <v>45833</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -51593,7 +51593,7 @@
         <v>46251</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -51666,7 +51666,7 @@
         <v>45803</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -51739,7 +51739,7 @@
         <v>46297</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -51817,7 +51817,7 @@
         <v>46300</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>45835</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -51973,7 +51973,7 @@
         <v>46254</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -52046,7 +52046,7 @@
         <v>46254</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -52119,7 +52119,7 @@
         <v>46300</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -52197,7 +52197,7 @@
         <v>45840</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -52275,7 +52275,7 @@
         <v>45922</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -52348,7 +52348,7 @@
         <v>46097</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -52426,7 +52426,7 @@
         <v>45747</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -52499,7 +52499,7 @@
         <v>45840</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -52577,7 +52577,7 @@
         <v>46099</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -52655,7 +52655,7 @@
         <v>46255</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -52733,7 +52733,7 @@
         <v>46299</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>45761</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -52884,7 +52884,7 @@
         <v>46300</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -52962,7 +52962,7 @@
         <v>45527</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -53035,7 +53035,7 @@
         <v>46300</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -53113,7 +53113,7 @@
         <v>46100</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -53186,7 +53186,7 @@
         <v>46302</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -53259,7 +53259,7 @@
         <v>45843</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>46105</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -53410,7 +53410,7 @@
         <v>46259</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -53488,7 +53488,7 @@
         <v>45589</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -53566,7 +53566,7 @@
         <v>46259</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -53644,7 +53644,7 @@
         <v>45603</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -53717,7 +53717,7 @@
         <v>46259</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -53795,7 +53795,7 @@
         <v>46301</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -53873,7 +53873,7 @@
         <v>45674</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -53946,7 +53946,7 @@
         <v>45596</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -54019,7 +54019,7 @@
         <v>45796</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -54097,7 +54097,7 @@
         <v>45863</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -54170,7 +54170,7 @@
         <v>46261</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -54243,7 +54243,7 @@
         <v>46304</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -54321,7 +54321,7 @@
         <v>46261</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -54399,7 +54399,7 @@
         <v>45980</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -54472,7 +54472,7 @@
         <v>46261</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -54545,7 +54545,7 @@
         <v>45838</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -54618,7 +54618,7 @@
         <v>45456</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -54691,7 +54691,7 @@
         <v>46122</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -54769,7 +54769,7 @@
         <v>46122</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -54842,7 +54842,7 @@
         <v>46261</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -54915,7 +54915,7 @@
         <v>46126</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -54988,7 +54988,7 @@
         <v>46261</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -55081,7 +55081,7 @@
         <v>45369</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -55154,7 +55154,7 @@
         <v>46126</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -55227,7 +55227,7 @@
         <v>45868</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -55305,7 +55305,7 @@
         <v>46127</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -55378,7 +55378,7 @@
         <v>46132</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -55451,7 +55451,7 @@
         <v>45877</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -55529,7 +55529,7 @@
         <v>46305</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -55607,7 +55607,7 @@
         <v>46132</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -55685,7 +55685,7 @@
         <v>45880</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -55763,7 +55763,7 @@
         <v>46132</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -55841,7 +55841,7 @@
         <v>45881</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -55914,7 +55914,7 @@
         <v>45882</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -55987,7 +55987,7 @@
         <v>45882</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         <v>46132</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -56138,7 +56138,7 @@
         <v>46307</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -56216,7 +56216,7 @@
         <v>44908</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -56289,7 +56289,7 @@
         <v>45429</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -56362,7 +56362,7 @@
         <v>45429</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -56435,7 +56435,7 @@
         <v>45884</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -56513,7 +56513,7 @@
         <v>45446</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -56586,7 +56586,7 @@
         <v>46306</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -56664,7 +56664,7 @@
         <v>44994</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -56737,7 +56737,7 @@
         <v>45590</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -56815,7 +56815,7 @@
         <v>46307</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -56893,7 +56893,7 @@
         <v>46305</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -56971,7 +56971,7 @@
         <v>45204</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -57044,7 +57044,7 @@
         <v>44889</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -57117,7 +57117,7 @@
         <v>44901</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -57190,7 +57190,7 @@
         <v>46007</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -57263,7 +57263,7 @@
         <v>45709</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -57341,7 +57341,7 @@
         <v>46310</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -57419,7 +57419,7 @@
         <v>44903</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -57492,7 +57492,7 @@
         <v>44529</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -57565,7 +57565,7 @@
         <v>46309</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>46266</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -57716,7 +57716,7 @@
         <v>46268</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -57794,7 +57794,7 @@
         <v>46267</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -57867,7 +57867,7 @@
         <v>45691</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -57945,7 +57945,7 @@
         <v>46076</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -58018,7 +58018,7 @@
         <v>46311</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -58091,7 +58091,7 @@
         <v>46311</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -58164,7 +58164,7 @@
         <v>45935</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -58237,7 +58237,7 @@
         <v>46314</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -58315,7 +58315,7 @@
         <v>46268</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -58393,7 +58393,7 @@
         <v>46311</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -58471,7 +58471,7 @@
         <v>46311</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -58544,7 +58544,7 @@
         <v>45586</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -58622,7 +58622,7 @@
         <v>46268</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -58695,7 +58695,7 @@
         <v>44881</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -58768,7 +58768,7 @@
         <v>44966</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -58846,7 +58846,7 @@
         <v>46306</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -58924,7 +58924,7 @@
         <v>46269</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45750</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -59080,7 +59080,7 @@
         <v>46136</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -59158,7 +59158,7 @@
         <v>46311</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -59231,7 +59231,7 @@
         <v>45944</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -59304,7 +59304,7 @@
         <v>45832</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -59377,7 +59377,7 @@
         <v>45132</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -59450,7 +59450,7 @@
         <v>46003</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -59528,7 +59528,7 @@
         <v>45013</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -59601,7 +59601,7 @@
         <v>46270</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -59674,7 +59674,7 @@
         <v>45264</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -59747,7 +59747,7 @@
         <v>46272</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -59825,7 +59825,7 @@
         <v>45839</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -59898,7 +59898,7 @@
         <v>45860</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59976,7 +59976,7 @@
         <v>45818</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -60049,7 +60049,7 @@
         <v>46316</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -60127,7 +60127,7 @@
         <v>45653</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -60200,7 +60200,7 @@
         <v>45999</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -60273,7 +60273,7 @@
         <v>46273</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -60351,7 +60351,7 @@
         <v>46029</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -60424,7 +60424,7 @@
         <v>45645</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -60502,7 +60502,7 @@
         <v>46029</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -60575,7 +60575,7 @@
         <v>46315</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -60648,7 +60648,7 @@
         <v>46315</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -60726,7 +60726,7 @@
         <v>45408</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -60799,7 +60799,7 @@
         <v>46003</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -60872,7 +60872,7 @@
         <v>46076</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -60945,7 +60945,7 @@
         <v>45523</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -61023,7 +61023,7 @@
         <v>45587</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -61096,7 +61096,7 @@
         <v>46029</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -61169,7 +61169,7 @@
         <v>45583</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -61247,7 +61247,7 @@
         <v>46275</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -61320,7 +61320,7 @@
         <v>46275</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -61398,7 +61398,7 @@
         <v>46276</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -61471,7 +61471,7 @@
         <v>46274</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -61544,7 +61544,7 @@
         <v>46317</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -61617,7 +61617,7 @@
         <v>46317</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -61695,7 +61695,7 @@
         <v>46276</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -61768,7 +61768,7 @@
         <v>45649</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -61841,7 +61841,7 @@
         <v>45649</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -61914,7 +61914,7 @@
         <v>46275</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -61987,7 +61987,7 @@
         <v>46275</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -62060,7 +62060,7 @@
         <v>46084</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -62133,7 +62133,7 @@
         <v>46274</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -62206,7 +62206,7 @@
         <v>44726</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -62279,7 +62279,7 @@
         <v>45893</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -62357,7 +62357,7 @@
         <v>46317</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -62435,7 +62435,7 @@
         <v>46274</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -62513,7 +62513,7 @@
         <v>46274</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -62586,7 +62586,7 @@
         <v>45841</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -62659,7 +62659,7 @@
         <v>44642</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -62737,7 +62737,7 @@
         <v>46275</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -62810,7 +62810,7 @@
         <v>45548</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -62883,7 +62883,7 @@
         <v>45054</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -62956,7 +62956,7 @@
         <v>46148</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -63034,7 +63034,7 @@
         <v>44963</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -63107,7 +63107,7 @@
         <v>45238</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -63180,7 +63180,7 @@
         <v>46147</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -63253,7 +63253,7 @@
         <v>46150</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -63326,7 +63326,7 @@
         <v>46150</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -63399,7 +63399,7 @@
         <v>46150</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -63472,7 +63472,7 @@
         <v>46149</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -63545,7 +63545,7 @@
         <v>46149</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -63618,7 +63618,7 @@
         <v>46154</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -63696,7 +63696,7 @@
         <v>45764</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -63769,7 +63769,7 @@
         <v>45764</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -63842,7 +63842,7 @@
         <v>45770</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -63915,7 +63915,7 @@
         <v>44657</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -63988,7 +63988,7 @@
         <v>45408</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -64061,7 +64061,7 @@
         <v>44657</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -64134,7 +64134,7 @@
         <v>44994</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -64207,7 +64207,7 @@
         <v>45427</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -64280,7 +64280,7 @@
         <v>44673</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -64353,7 +64353,7 @@
         <v>46154</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -64426,7 +64426,7 @@
         <v>45562</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -64504,7 +64504,7 @@
         <v>45639</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -64577,7 +64577,7 @@
         <v>45589</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -64655,7 +64655,7 @@
         <v>45589</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -64733,7 +64733,7 @@
         <v>45988</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -64806,7 +64806,7 @@
         <v>45646</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -64879,7 +64879,7 @@
         <v>46155</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -64952,7 +64952,7 @@
         <v>45440</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -65025,7 +65025,7 @@
         <v>45625</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -65103,7 +65103,7 @@
         <v>44903</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -65176,7 +65176,7 @@
         <v>45212</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -65249,7 +65249,7 @@
         <v>45161</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -65327,7 +65327,7 @@
         <v>44994</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -65400,7 +65400,7 @@
         <v>45195</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -65478,7 +65478,7 @@
         <v>44796</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -65551,7 +65551,7 @@
         <v>45085</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -65624,7 +65624,7 @@
         <v>45153</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -65697,7 +65697,7 @@
         <v>45649</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -65770,7 +65770,7 @@
         <v>45149</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -65843,7 +65843,7 @@
         <v>44856</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -65916,7 +65916,7 @@
         <v>45103</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -65989,7 +65989,7 @@
         <v>44823</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -66067,7 +66067,7 @@
         <v>44568</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -66140,7 +66140,7 @@
         <v>45667</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -66213,7 +66213,7 @@
         <v>44648</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -66291,7 +66291,7 @@
         <v>45499</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -66364,7 +66364,7 @@
         <v>45194</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -66442,7 +66442,7 @@
         <v>45649</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -66515,7 +66515,7 @@
         <v>45764</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -66588,7 +66588,7 @@
         <v>45773</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -66666,7 +66666,7 @@
         <v>45672</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -66739,7 +66739,7 @@
         <v>45748</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -66812,7 +66812,7 @@
         <v>44524</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -66885,7 +66885,7 @@
         <v>45761</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -66958,7 +66958,7 @@
         <v>44881</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -67036,7 +67036,7 @@
         <v>45248</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -67109,7 +67109,7 @@
         <v>45210</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -67187,7 +67187,7 @@
         <v>44887</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -67265,7 +67265,7 @@
         <v>44565</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -67338,7 +67338,7 @@
         <v>45233</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -67416,7 +67416,7 @@
         <v>45070</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -67489,7 +67489,7 @@
         <v>45085</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -67562,7 +67562,7 @@
         <v>44529</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -67635,7 +67635,7 @@
         <v>45070</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -67708,7 +67708,7 @@
         <v>44812</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -67781,7 +67781,7 @@
         <v>45079</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -67854,7 +67854,7 @@
         <v>45102</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -67927,7 +67927,7 @@
         <v>45593</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -68005,7 +68005,7 @@
         <v>45406</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -68078,7 +68078,7 @@
         <v>44908</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -68151,7 +68151,7 @@
         <v>45099</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -68224,7 +68224,7 @@
         <v>45358</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -68297,7 +68297,7 @@
         <v>45110</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -68375,7 +68375,7 @@
         <v>45551</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -68453,7 +68453,7 @@
         <v>45544</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -68526,7 +68526,7 @@
         <v>45574</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -68604,7 +68604,7 @@
         <v>45574</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -68682,7 +68682,7 @@
         <v>45281</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -68760,7 +68760,7 @@
         <v>44529</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -68833,7 +68833,7 @@
         <v>45156</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -68906,7 +68906,7 @@
         <v>44983</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -68979,7 +68979,7 @@
         <v>45618</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -69057,7 +69057,7 @@
         <v>45604</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -69130,7 +69130,7 @@
         <v>45772</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -69203,7 +69203,7 @@
         <v>44522</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -69276,7 +69276,7 @@
         <v>45591</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -69354,7 +69354,7 @@
         <v>44609</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -69427,7 +69427,7 @@
         <v>45161</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -69505,7 +69505,7 @@
         <v>45161</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -69583,7 +69583,7 @@
         <v>45758</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -69656,7 +69656,7 @@
         <v>44795</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -69729,7 +69729,7 @@
         <v>45216</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -69807,7 +69807,7 @@
         <v>45596</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -69880,7 +69880,7 @@
         <v>45600</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -69953,7 +69953,7 @@
         <v>45600</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -70026,7 +70026,7 @@
         <v>44566</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -70099,7 +70099,7 @@
         <v>45478</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -70172,7 +70172,7 @@
         <v>45411</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -70245,7 +70245,7 @@
         <v>45310</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -70323,7 +70323,7 @@
         <v>44628</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -70396,7 +70396,7 @@
         <v>45561</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -70469,7 +70469,7 @@
         <v>45512</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -70542,7 +70542,7 @@
         <v>44859</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -70620,7 +70620,7 @@
         <v>45212</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -70698,7 +70698,7 @@
         <v>45687</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -70771,7 +70771,7 @@
         <v>45560</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -70849,7 +70849,7 @@
         <v>45770</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -70922,7 +70922,7 @@
         <v>45505</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -71000,7 +71000,7 @@
         <v>45460</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -71078,7 +71078,7 @@
         <v>45237</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -71151,7 +71151,7 @@
         <v>45210</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -71229,7 +71229,7 @@
         <v>45194</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -71307,7 +71307,7 @@
         <v>45161</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -71380,7 +71380,7 @@
         <v>44783</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -71453,7 +71453,7 @@
         <v>45201</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -71526,7 +71526,7 @@
         <v>45728</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -71604,7 +71604,7 @@
         <v>45246</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -71677,7 +71677,7 @@
         <v>45762</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -71750,7 +71750,7 @@
         <v>45166</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -71828,7 +71828,7 @@
         <v>45718</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -71901,7 +71901,7 @@
         <v>45247</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -71974,7 +71974,7 @@
         <v>45314</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -72047,7 +72047,7 @@
         <v>45256</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -72120,7 +72120,7 @@
         <v>45680</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -72198,7 +72198,7 @@
         <v>45254</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -72271,7 +72271,7 @@
         <v>45257</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -72344,7 +72344,7 @@
         <v>44648</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -72422,7 +72422,7 @@
         <v>45264</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -72500,7 +72500,7 @@
         <v>45356</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -72573,7 +72573,7 @@
         <v>45694</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -72651,7 +72651,7 @@
         <v>45260</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -72724,7 +72724,7 @@
         <v>45022</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -72797,7 +72797,7 @@
         <v>44573</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -72875,7 +72875,7 @@
         <v>45345</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -72948,7 +72948,7 @@
         <v>45483</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -73021,7 +73021,7 @@
         <v>45285</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -73094,7 +73094,7 @@
         <v>45529</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -73167,7 +73167,7 @@
         <v>44732</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -73240,7 +73240,7 @@
         <v>45323</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -73313,7 +73313,7 @@
         <v>44970</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -73386,7 +73386,7 @@
         <v>45210</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -73464,7 +73464,7 @@
         <v>45692</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -73537,7 +73537,7 @@
         <v>45509</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -73610,7 +73610,7 @@
         <v>45537</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -73688,7 +73688,7 @@
         <v>44964</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -73766,7 +73766,7 @@
         <v>45539</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -73839,7 +73839,7 @@
         <v>45429</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -73912,7 +73912,7 @@
         <v>44747</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -73985,7 +73985,7 @@
         <v>44706</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -74058,7 +74058,7 @@
         <v>44880</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -74131,7 +74131,7 @@
         <v>44979</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -74209,7 +74209,7 @@
         <v>45376</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -74287,7 +74287,7 @@
         <v>45013</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -74360,7 +74360,7 @@
         <v>45376</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -74438,7 +74438,7 @@
         <v>45667</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -74511,7 +74511,7 @@
         <v>44945</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -74589,7 +74589,7 @@
         <v>45743</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -74662,7 +74662,7 @@
         <v>45743</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -74735,7 +74735,7 @@
         <v>45789</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -74813,7 +74813,7 @@
         <v>45792</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -74886,7 +74886,7 @@
         <v>45799</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -74964,7 +74964,7 @@
         <v>45799</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -75042,7 +75042,7 @@
         <v>45799</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -75120,7 +75120,7 @@
         <v>45810</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -75198,7 +75198,7 @@
         <v>45818</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -75276,7 +75276,7 @@
         <v>45840</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -75354,7 +75354,7 @@
         <v>46018</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -75427,7 +75427,7 @@
         <v>46147</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -75500,7 +75500,7 @@
         <v>46147</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -75573,7 +75573,7 @@
         <v>46147</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -75651,7 +75651,7 @@
         <v>46152</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -75724,7 +75724,7 @@
         <v>46152</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -75797,7 +75797,7 @@
         <v>46148</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
